--- a/data/exports/final_predictions/lotto_ensemble_predictions.xlsx
+++ b/data/exports/final_predictions/lotto_ensemble_predictions.xlsx
@@ -603,7 +603,7 @@
         <v>49</v>
       </c>
       <c r="N2" t="n">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="O2" t="n">
         <v>156</v>
@@ -639,16 +639,16 @@
         <v>8</v>
       </c>
       <c r="Z2" t="n">
-        <v>73.72</v>
+        <v>73.81</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2|6|8|44|47|49|7</t>
+          <t>2|6|8|44|47|49|23</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:32</t>
+          <t>2026-05-24 05:37:12</t>
         </is>
       </c>
     </row>
@@ -733,7 +733,7 @@
         <v>5</v>
       </c>
       <c r="Z3" t="n">
-        <v>47.72</v>
+        <v>47.81</v>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
@@ -742,7 +742,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:32</t>
+          <t>2026-05-24 05:37:12</t>
         </is>
       </c>
     </row>
@@ -776,25 +776,25 @@
         <v>2</v>
       </c>
       <c r="I4" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="J4" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="K4" t="n">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="L4" t="n">
+        <v>40</v>
+      </c>
+      <c r="M4" t="n">
         <v>44</v>
       </c>
-      <c r="M4" t="n">
-        <v>49</v>
-      </c>
       <c r="N4" t="n">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="O4" t="n">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="P4" t="n">
         <v>3</v>
@@ -803,7 +803,7 @@
         <v>3</v>
       </c>
       <c r="R4" t="n">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -824,19 +824,19 @@
         <v>0.5</v>
       </c>
       <c r="Y4" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Z4" t="n">
-        <v>45.72</v>
+        <v>42.81</v>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2|8|29|33|44|49|19</t>
+          <t>2|17|23|27|40|44|32</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:32</t>
+          <t>2026-05-24 05:37:12</t>
         </is>
       </c>
     </row>
@@ -864,31 +864,31 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I5" t="n">
         <v>8</v>
       </c>
       <c r="J5" t="n">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="K5" t="n">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="L5" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="M5" t="n">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="N5" t="n">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="O5" t="n">
-        <v>129</v>
+        <v>153</v>
       </c>
       <c r="P5" t="n">
         <v>3</v>
@@ -897,7 +897,7 @@
         <v>3</v>
       </c>
       <c r="R5" t="n">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -906,7 +906,7 @@
         <v>1</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.25</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -918,19 +918,19 @@
         <v>0.5</v>
       </c>
       <c r="Y5" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Z5" t="n">
-        <v>40.72</v>
+        <v>40.31</v>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2|8|17|20|33|49|28</t>
+          <t>4|8|29|33|35|44|13</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:32</t>
+          <t>2026-05-24 05:37:12</t>
         </is>
       </c>
     </row>
@@ -958,13 +958,13 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I6" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J6" t="n">
         <v>29</v>
@@ -973,16 +973,16 @@
         <v>33</v>
       </c>
       <c r="L6" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="M6" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="N6" t="n">
         <v>13</v>
       </c>
       <c r="O6" t="n">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="P6" t="n">
         <v>3</v>
@@ -991,7 +991,7 @@
         <v>3</v>
       </c>
       <c r="R6" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1000,7 +1000,7 @@
         <v>1</v>
       </c>
       <c r="U6" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -1015,16 +1015,16 @@
         <v>5</v>
       </c>
       <c r="Z6" t="n">
-        <v>40.22</v>
+        <v>38.81</v>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>4|8|29|33|35|44|13</t>
+          <t>2|7|29|33|40|46|13</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:32</t>
+          <t>2026-05-24 05:37:12</t>
         </is>
       </c>
     </row>
@@ -1052,16 +1052,16 @@
         </is>
       </c>
       <c r="G7" t="n">
+        <v>5</v>
+      </c>
+      <c r="H7" t="n">
         <v>4</v>
       </c>
-      <c r="H7" t="n">
-        <v>1</v>
-      </c>
       <c r="I7" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="J7" t="n">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="K7" t="n">
         <v>33</v>
@@ -1070,13 +1070,13 @@
         <v>40</v>
       </c>
       <c r="M7" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="N7" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="O7" t="n">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="P7" t="n">
         <v>3</v>
@@ -1085,7 +1085,7 @@
         <v>3</v>
       </c>
       <c r="R7" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1094,7 +1094,7 @@
         <v>1</v>
       </c>
       <c r="U7" t="n">
-        <v>0.2</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1109,16 +1109,16 @@
         <v>5</v>
       </c>
       <c r="Z7" t="n">
-        <v>38.72</v>
+        <v>37.81</v>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>1|16|17|33|40|42|18</t>
+          <t>4|8|27|33|40|43|20</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:32</t>
+          <t>2026-05-24 05:37:12</t>
         </is>
       </c>
     </row>
@@ -1149,37 +1149,37 @@
         <v>6</v>
       </c>
       <c r="H8" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="I8" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="J8" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="K8" t="n">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="L8" t="n">
+        <v>40</v>
+      </c>
+      <c r="M8" t="n">
+        <v>42</v>
+      </c>
+      <c r="N8" t="n">
+        <v>18</v>
+      </c>
+      <c r="O8" t="n">
+        <v>149</v>
+      </c>
+      <c r="P8" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>3</v>
+      </c>
+      <c r="R8" t="n">
         <v>41</v>
-      </c>
-      <c r="M8" t="n">
-        <v>44</v>
-      </c>
-      <c r="N8" t="n">
-        <v>1</v>
-      </c>
-      <c r="O8" t="n">
-        <v>153</v>
-      </c>
-      <c r="P8" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>3</v>
-      </c>
-      <c r="R8" t="n">
-        <v>33</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1203,16 +1203,16 @@
         <v>5</v>
       </c>
       <c r="Z8" t="n">
-        <v>37.00571428571428</v>
+        <v>37.09571428571429</v>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>11|14|20|23|41|44|1</t>
+          <t>1|16|17|33|40|42|18</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:32</t>
+          <t>2026-05-24 05:37:12</t>
         </is>
       </c>
     </row>
@@ -1243,37 +1243,37 @@
         <v>7</v>
       </c>
       <c r="H9" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="I9" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="J9" t="n">
         <v>27</v>
       </c>
       <c r="K9" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="L9" t="n">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="M9" t="n">
+        <v>45</v>
+      </c>
+      <c r="N9" t="n">
+        <v>10</v>
+      </c>
+      <c r="O9" t="n">
+        <v>155</v>
+      </c>
+      <c r="P9" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>3</v>
+      </c>
+      <c r="R9" t="n">
         <v>44</v>
-      </c>
-      <c r="N9" t="n">
-        <v>7</v>
-      </c>
-      <c r="O9" t="n">
-        <v>163</v>
-      </c>
-      <c r="P9" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>3</v>
-      </c>
-      <c r="R9" t="n">
-        <v>33</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1297,16 +1297,16 @@
         <v>5</v>
       </c>
       <c r="Z9" t="n">
-        <v>36.47</v>
+        <v>36.56</v>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>11|20|27|30|31|44|7</t>
+          <t>1|8|27|32|42|45|10</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:32</t>
+          <t>2026-05-24 05:37:12</t>
         </is>
       </c>
     </row>
@@ -1340,34 +1340,34 @@
         <v>8</v>
       </c>
       <c r="I10" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="J10" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="K10" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="L10" t="n">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="M10" t="n">
+        <v>49</v>
+      </c>
+      <c r="N10" t="n">
+        <v>24</v>
+      </c>
+      <c r="O10" t="n">
+        <v>165</v>
+      </c>
+      <c r="P10" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>3</v>
+      </c>
+      <c r="R10" t="n">
         <v>41</v>
-      </c>
-      <c r="N10" t="n">
-        <v>11</v>
-      </c>
-      <c r="O10" t="n">
-        <v>167</v>
-      </c>
-      <c r="P10" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>3</v>
-      </c>
-      <c r="R10" t="n">
-        <v>33</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1391,16 +1391,16 @@
         <v>5</v>
       </c>
       <c r="Z10" t="n">
-        <v>36.05333333333333</v>
+        <v>36.14333333333333</v>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>8|23|26|32|37|41|11</t>
+          <t>8|17|19|30|42|49|24</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:32</t>
+          <t>2026-05-24 05:37:12</t>
         </is>
       </c>
     </row>
@@ -1431,28 +1431,28 @@
         <v>9</v>
       </c>
       <c r="H11" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="I11" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="J11" t="n">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="K11" t="n">
-        <v>30</v>
+        <v>43</v>
       </c>
       <c r="L11" t="n">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="M11" t="n">
-        <v>33</v>
+        <v>47</v>
       </c>
       <c r="N11" t="n">
-        <v>49</v>
+        <v>10</v>
       </c>
       <c r="O11" t="n">
-        <v>127</v>
+        <v>163</v>
       </c>
       <c r="P11" t="n">
         <v>3</v>
@@ -1461,7 +1461,7 @@
         <v>3</v>
       </c>
       <c r="R11" t="n">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1485,16 +1485,16 @@
         <v>5</v>
       </c>
       <c r="Z11" t="n">
-        <v>35.72</v>
+        <v>35.81</v>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>8|11|14|30|31|33|49</t>
+          <t>2|3|24|43|44|47|10</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:32</t>
+          <t>2026-05-24 05:37:12</t>
         </is>
       </c>
     </row>
@@ -1528,10 +1528,10 @@
         <v>1</v>
       </c>
       <c r="I12" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="J12" t="n">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="K12" t="n">
         <v>30</v>
@@ -1540,22 +1540,22 @@
         <v>32</v>
       </c>
       <c r="M12" t="n">
+        <v>47</v>
+      </c>
+      <c r="N12" t="n">
+        <v>21</v>
+      </c>
+      <c r="O12" t="n">
+        <v>137</v>
+      </c>
+      <c r="P12" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>3</v>
+      </c>
+      <c r="R12" t="n">
         <v>46</v>
-      </c>
-      <c r="N12" t="n">
-        <v>18</v>
-      </c>
-      <c r="O12" t="n">
-        <v>145</v>
-      </c>
-      <c r="P12" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>3</v>
-      </c>
-      <c r="R12" t="n">
-        <v>45</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1579,16 +1579,16 @@
         <v>5</v>
       </c>
       <c r="Z12" t="n">
-        <v>35.44727272727273</v>
+        <v>35.53727272727272</v>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>1|9|27|30|32|46|18</t>
+          <t>1|13|14|30|32|47|21</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:32</t>
+          <t>2026-05-24 05:37:12</t>
         </is>
       </c>
     </row>

--- a/data/exports/final_predictions/lotto_ensemble_predictions.xlsx
+++ b/data/exports/final_predictions/lotto_ensemble_predictions.xlsx
@@ -648,7 +648,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:12</t>
+          <t>2026-05-25 14:34:27</t>
         </is>
       </c>
     </row>
@@ -742,7 +742,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:12</t>
+          <t>2026-05-25 14:34:27</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:12</t>
+          <t>2026-05-25 14:34:27</t>
         </is>
       </c>
     </row>
@@ -930,7 +930,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:12</t>
+          <t>2026-05-25 14:34:27</t>
         </is>
       </c>
     </row>
@@ -1024,7 +1024,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:12</t>
+          <t>2026-05-25 14:34:27</t>
         </is>
       </c>
     </row>
@@ -1118,7 +1118,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:12</t>
+          <t>2026-05-25 14:34:27</t>
         </is>
       </c>
     </row>
@@ -1212,7 +1212,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:12</t>
+          <t>2026-05-25 14:34:27</t>
         </is>
       </c>
     </row>
@@ -1306,7 +1306,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:12</t>
+          <t>2026-05-25 14:34:27</t>
         </is>
       </c>
     </row>
@@ -1400,7 +1400,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:12</t>
+          <t>2026-05-25 14:34:27</t>
         </is>
       </c>
     </row>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:12</t>
+          <t>2026-05-25 14:34:27</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:12</t>
+          <t>2026-05-25 14:34:27</t>
         </is>
       </c>
     </row>

--- a/data/exports/final_predictions/lotto_ensemble_predictions.xlsx
+++ b/data/exports/final_predictions/lotto_ensemble_predictions.xlsx
@@ -648,7 +648,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:27</t>
+          <t>2026-05-26 14:23:44</t>
         </is>
       </c>
     </row>
@@ -742,7 +742,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:27</t>
+          <t>2026-05-26 14:23:44</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:27</t>
+          <t>2026-05-26 14:23:44</t>
         </is>
       </c>
     </row>
@@ -930,7 +930,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:27</t>
+          <t>2026-05-26 14:23:44</t>
         </is>
       </c>
     </row>
@@ -1024,7 +1024,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:27</t>
+          <t>2026-05-26 14:23:44</t>
         </is>
       </c>
     </row>
@@ -1118,7 +1118,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:27</t>
+          <t>2026-05-26 14:23:44</t>
         </is>
       </c>
     </row>
@@ -1212,7 +1212,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:27</t>
+          <t>2026-05-26 14:23:44</t>
         </is>
       </c>
     </row>
@@ -1306,7 +1306,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:27</t>
+          <t>2026-05-26 14:23:44</t>
         </is>
       </c>
     </row>
@@ -1400,7 +1400,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:27</t>
+          <t>2026-05-26 14:23:44</t>
         </is>
       </c>
     </row>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:27</t>
+          <t>2026-05-26 14:23:44</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:27</t>
+          <t>2026-05-26 14:23:44</t>
         </is>
       </c>
     </row>

--- a/data/exports/final_predictions/lotto_ensemble_predictions.xlsx
+++ b/data/exports/final_predictions/lotto_ensemble_predictions.xlsx
@@ -648,7 +648,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:44</t>
+          <t>2026-05-27 14:58:36</t>
         </is>
       </c>
     </row>
@@ -742,7 +742,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:44</t>
+          <t>2026-05-27 14:58:36</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:44</t>
+          <t>2026-05-27 14:58:36</t>
         </is>
       </c>
     </row>
@@ -930,7 +930,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:44</t>
+          <t>2026-05-27 14:58:36</t>
         </is>
       </c>
     </row>
@@ -1024,7 +1024,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:44</t>
+          <t>2026-05-27 14:58:36</t>
         </is>
       </c>
     </row>
@@ -1118,7 +1118,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:44</t>
+          <t>2026-05-27 14:58:36</t>
         </is>
       </c>
     </row>
@@ -1212,7 +1212,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:44</t>
+          <t>2026-05-27 14:58:36</t>
         </is>
       </c>
     </row>
@@ -1306,7 +1306,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:44</t>
+          <t>2026-05-27 14:58:36</t>
         </is>
       </c>
     </row>
@@ -1400,7 +1400,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:44</t>
+          <t>2026-05-27 14:58:36</t>
         </is>
       </c>
     </row>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:44</t>
+          <t>2026-05-27 14:58:36</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:44</t>
+          <t>2026-05-27 14:58:36</t>
         </is>
       </c>
     </row>

--- a/data/exports/final_predictions/lotto_ensemble_predictions.xlsx
+++ b/data/exports/final_predictions/lotto_ensemble_predictions.xlsx
@@ -585,28 +585,28 @@
         <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J2" t="n">
+        <v>44</v>
+      </c>
+      <c r="K2" t="n">
+        <v>49</v>
+      </c>
+      <c r="L2" t="n">
+        <v>52</v>
+      </c>
+      <c r="M2" t="n">
+        <v>56</v>
+      </c>
+      <c r="N2" t="n">
         <v>8</v>
       </c>
-      <c r="K2" t="n">
-        <v>44</v>
-      </c>
-      <c r="L2" t="n">
-        <v>47</v>
-      </c>
-      <c r="M2" t="n">
-        <v>49</v>
-      </c>
-      <c r="N2" t="n">
-        <v>23</v>
-      </c>
       <c r="O2" t="n">
-        <v>156</v>
+        <v>206</v>
       </c>
       <c r="P2" t="n">
         <v>2</v>
@@ -615,7 +615,7 @@
         <v>4</v>
       </c>
       <c r="R2" t="n">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -643,12 +643,12 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2|6|8|44|47|49|23</t>
+          <t>1|4|44|49|52|56|8</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:36</t>
+          <t>2026-05-28 08:54:41</t>
         </is>
       </c>
     </row>
@@ -679,37 +679,37 @@
         <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I3" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="J3" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="K3" t="n">
+        <v>31</v>
+      </c>
+      <c r="L3" t="n">
+        <v>37</v>
+      </c>
+      <c r="M3" t="n">
+        <v>49</v>
+      </c>
+      <c r="N3" t="n">
+        <v>28</v>
+      </c>
+      <c r="O3" t="n">
+        <v>157</v>
+      </c>
+      <c r="P3" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>3</v>
+      </c>
+      <c r="R3" t="n">
         <v>43</v>
-      </c>
-      <c r="L3" t="n">
-        <v>47</v>
-      </c>
-      <c r="M3" t="n">
-        <v>48</v>
-      </c>
-      <c r="N3" t="n">
-        <v>12</v>
-      </c>
-      <c r="O3" t="n">
-        <v>151</v>
-      </c>
-      <c r="P3" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>3</v>
-      </c>
-      <c r="R3" t="n">
-        <v>46</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -737,12 +737,12 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2|3|8|43|47|48|12</t>
+          <t>6|12|22|31|37|49|28</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:36</t>
+          <t>2026-05-28 08:54:41</t>
         </is>
       </c>
     </row>
@@ -773,28 +773,28 @@
         <v>2</v>
       </c>
       <c r="H4" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="I4" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="J4" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="K4" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="L4" t="n">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="M4" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="N4" t="n">
-        <v>32</v>
+        <v>6</v>
       </c>
       <c r="O4" t="n">
-        <v>153</v>
+        <v>169</v>
       </c>
       <c r="P4" t="n">
         <v>3</v>
@@ -803,7 +803,7 @@
         <v>3</v>
       </c>
       <c r="R4" t="n">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -831,12 +831,12 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2|17|23|27|40|44|32</t>
+          <t>13|14|29|32|35|46|6</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:36</t>
+          <t>2026-05-28 08:54:41</t>
         </is>
       </c>
     </row>
@@ -870,34 +870,34 @@
         <v>4</v>
       </c>
       <c r="I5" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J5" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="K5" t="n">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="L5" t="n">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="M5" t="n">
+        <v>48</v>
+      </c>
+      <c r="N5" t="n">
+        <v>17</v>
+      </c>
+      <c r="O5" t="n">
+        <v>169</v>
+      </c>
+      <c r="P5" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>3</v>
+      </c>
+      <c r="R5" t="n">
         <v>44</v>
-      </c>
-      <c r="N5" t="n">
-        <v>13</v>
-      </c>
-      <c r="O5" t="n">
-        <v>153</v>
-      </c>
-      <c r="P5" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>3</v>
-      </c>
-      <c r="R5" t="n">
-        <v>40</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -925,12 +925,12 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>4|8|29|33|35|44|13</t>
+          <t>4|7|27|39|44|48|17</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:36</t>
+          <t>2026-05-28 08:54:41</t>
         </is>
       </c>
     </row>
@@ -961,28 +961,28 @@
         <v>4</v>
       </c>
       <c r="H6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I6" t="n">
         <v>2</v>
-      </c>
-      <c r="I6" t="n">
-        <v>7</v>
       </c>
       <c r="J6" t="n">
         <v>29</v>
       </c>
       <c r="K6" t="n">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="L6" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="M6" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="N6" t="n">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="O6" t="n">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="P6" t="n">
         <v>3</v>
@@ -991,7 +991,7 @@
         <v>3</v>
       </c>
       <c r="R6" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1019,12 +1019,12 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2|7|29|33|40|46|13</t>
+          <t>1|2|29|40|42|49|34</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:36</t>
+          <t>2026-05-28 08:54:41</t>
         </is>
       </c>
     </row>
@@ -1055,13 +1055,13 @@
         <v>5</v>
       </c>
       <c r="H7" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="I7" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="J7" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="K7" t="n">
         <v>33</v>
@@ -1070,13 +1070,13 @@
         <v>40</v>
       </c>
       <c r="M7" t="n">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="N7" t="n">
-        <v>20</v>
+        <v>41</v>
       </c>
       <c r="O7" t="n">
-        <v>155</v>
+        <v>169</v>
       </c>
       <c r="P7" t="n">
         <v>3</v>
@@ -1113,12 +1113,12 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>4|8|27|33|40|43|20</t>
+          <t>8|12|29|33|40|47|41</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:36</t>
+          <t>2026-05-28 08:54:41</t>
         </is>
       </c>
     </row>
@@ -1149,28 +1149,28 @@
         <v>6</v>
       </c>
       <c r="H8" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="I8" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="J8" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="K8" t="n">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="L8" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="M8" t="n">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="N8" t="n">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="O8" t="n">
-        <v>149</v>
+        <v>173</v>
       </c>
       <c r="P8" t="n">
         <v>3</v>
@@ -1179,7 +1179,7 @@
         <v>3</v>
       </c>
       <c r="R8" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1207,12 +1207,12 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>1|16|17|33|40|42|18</t>
+          <t>11|12|22|37|42|49|43</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:36</t>
+          <t>2026-05-28 08:54:41</t>
         </is>
       </c>
     </row>
@@ -1243,28 +1243,28 @@
         <v>7</v>
       </c>
       <c r="H9" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="I9" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J9" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="K9" t="n">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="L9" t="n">
         <v>42</v>
       </c>
       <c r="M9" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="N9" t="n">
-        <v>10</v>
+        <v>55</v>
       </c>
       <c r="O9" t="n">
-        <v>155</v>
+        <v>169</v>
       </c>
       <c r="P9" t="n">
         <v>3</v>
@@ -1273,7 +1273,7 @@
         <v>3</v>
       </c>
       <c r="R9" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>1|8|27|32|42|45|10</t>
+          <t>9|10|22|37|42|49|55</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:36</t>
+          <t>2026-05-28 08:54:41</t>
         </is>
       </c>
     </row>
@@ -1337,28 +1337,28 @@
         <v>8</v>
       </c>
       <c r="H10" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I10" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="J10" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="K10" t="n">
         <v>30</v>
       </c>
       <c r="L10" t="n">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="M10" t="n">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="N10" t="n">
-        <v>24</v>
+        <v>55</v>
       </c>
       <c r="O10" t="n">
-        <v>165</v>
+        <v>147</v>
       </c>
       <c r="P10" t="n">
         <v>3</v>
@@ -1367,7 +1367,7 @@
         <v>3</v>
       </c>
       <c r="R10" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1395,12 +1395,12 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>8|17|19|30|42|49|24</t>
+          <t>7|9|22|30|33|46|55</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:36</t>
+          <t>2026-05-28 08:54:41</t>
         </is>
       </c>
     </row>
@@ -1431,28 +1431,28 @@
         <v>9</v>
       </c>
       <c r="H11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I11" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="J11" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="K11" t="n">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="L11" t="n">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="M11" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="N11" t="n">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="O11" t="n">
-        <v>163</v>
+        <v>151</v>
       </c>
       <c r="P11" t="n">
         <v>3</v>
@@ -1461,7 +1461,7 @@
         <v>3</v>
       </c>
       <c r="R11" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1489,12 +1489,12 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2|3|24|43|44|47|10</t>
+          <t>3|13|18|32|36|49|53</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:36</t>
+          <t>2026-05-28 08:54:41</t>
         </is>
       </c>
     </row>
@@ -1525,28 +1525,28 @@
         <v>10</v>
       </c>
       <c r="H12" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="I12" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J12" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="K12" t="n">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="L12" t="n">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="M12" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="N12" t="n">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="O12" t="n">
-        <v>137</v>
+        <v>163</v>
       </c>
       <c r="P12" t="n">
         <v>3</v>
@@ -1555,7 +1555,7 @@
         <v>3</v>
       </c>
       <c r="R12" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1583,12 +1583,12 @@
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>1|13|14|30|32|47|21</t>
+          <t>8|12|17|37|41|48|6</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:36</t>
+          <t>2026-05-28 08:54:41</t>
         </is>
       </c>
     </row>

--- a/data/exports/final_predictions/lotto_ensemble_predictions.xlsx
+++ b/data/exports/final_predictions/lotto_ensemble_predictions.xlsx
@@ -603,7 +603,7 @@
         <v>56</v>
       </c>
       <c r="N2" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="O2" t="n">
         <v>206</v>
@@ -639,16 +639,16 @@
         <v>8</v>
       </c>
       <c r="Z2" t="n">
-        <v>73.81</v>
+        <v>73.84999999999999</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1|4|44|49|52|56|8</t>
+          <t>1|4|44|49|52|56|14</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:41</t>
+          <t>2026-05-28 17:22:47</t>
         </is>
       </c>
     </row>
@@ -679,7 +679,7 @@
         <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="I3" t="n">
         <v>12</v>
@@ -688,7 +688,7 @@
         <v>22</v>
       </c>
       <c r="K3" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="L3" t="n">
         <v>37</v>
@@ -697,10 +697,10 @@
         <v>49</v>
       </c>
       <c r="N3" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="O3" t="n">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="P3" t="n">
         <v>3</v>
@@ -709,7 +709,7 @@
         <v>3</v>
       </c>
       <c r="R3" t="n">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -733,16 +733,16 @@
         <v>5</v>
       </c>
       <c r="Z3" t="n">
-        <v>47.81</v>
+        <v>47.85</v>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>6|12|22|31|37|49|28</t>
+          <t>11|12|22|32|37|49|21</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:41</t>
+          <t>2026-05-28 17:22:47</t>
         </is>
       </c>
     </row>
@@ -773,28 +773,28 @@
         <v>2</v>
       </c>
       <c r="H4" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="I4" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J4" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="K4" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="L4" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="M4" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="N4" t="n">
-        <v>6</v>
+        <v>42</v>
       </c>
       <c r="O4" t="n">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="P4" t="n">
         <v>3</v>
@@ -803,7 +803,7 @@
         <v>3</v>
       </c>
       <c r="R4" t="n">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -827,16 +827,16 @@
         <v>5</v>
       </c>
       <c r="Z4" t="n">
-        <v>42.81</v>
+        <v>42.85</v>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>13|14|29|32|35|46|6</t>
+          <t>7|12|23|33|40|48|42</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:41</t>
+          <t>2026-05-28 17:22:47</t>
         </is>
       </c>
     </row>
@@ -867,28 +867,28 @@
         <v>3</v>
       </c>
       <c r="H5" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="I5" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="J5" t="n">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="K5" t="n">
+        <v>32</v>
+      </c>
+      <c r="L5" t="n">
         <v>39</v>
       </c>
-      <c r="L5" t="n">
-        <v>44</v>
-      </c>
       <c r="M5" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N5" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O5" t="n">
-        <v>169</v>
+        <v>157</v>
       </c>
       <c r="P5" t="n">
         <v>3</v>
@@ -897,7 +897,7 @@
         <v>3</v>
       </c>
       <c r="R5" t="n">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -921,16 +921,16 @@
         <v>5</v>
       </c>
       <c r="Z5" t="n">
-        <v>40.31</v>
+        <v>40.35</v>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>4|7|27|39|44|48|17</t>
+          <t>8|13|18|32|39|47|16</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:41</t>
+          <t>2026-05-28 17:22:47</t>
         </is>
       </c>
     </row>
@@ -961,28 +961,28 @@
         <v>4</v>
       </c>
       <c r="H6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I6" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="J6" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="K6" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="L6" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="M6" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="N6" t="n">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="O6" t="n">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="P6" t="n">
         <v>3</v>
@@ -991,7 +991,7 @@
         <v>3</v>
       </c>
       <c r="R6" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1015,16 +1015,16 @@
         <v>5</v>
       </c>
       <c r="Z6" t="n">
-        <v>38.81</v>
+        <v>38.85</v>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>1|2|29|40|42|49|34</t>
+          <t>2|8|23|38|43|47|16</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:41</t>
+          <t>2026-05-28 17:22:47</t>
         </is>
       </c>
     </row>
@@ -1055,25 +1055,25 @@
         <v>5</v>
       </c>
       <c r="H7" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I7" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J7" t="n">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="K7" t="n">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="L7" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="M7" t="n">
         <v>47</v>
       </c>
       <c r="N7" t="n">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="O7" t="n">
         <v>169</v>
@@ -1085,7 +1085,7 @@
         <v>3</v>
       </c>
       <c r="R7" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1109,16 +1109,16 @@
         <v>5</v>
       </c>
       <c r="Z7" t="n">
-        <v>37.81</v>
+        <v>37.85</v>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>8|12|29|33|40|47|41</t>
+          <t>7|11|20|40|44|47|27</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:41</t>
+          <t>2026-05-28 17:22:47</t>
         </is>
       </c>
     </row>
@@ -1149,28 +1149,28 @@
         <v>6</v>
       </c>
       <c r="H8" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="I8" t="n">
         <v>12</v>
       </c>
       <c r="J8" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="K8" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="L8" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="M8" t="n">
         <v>49</v>
       </c>
       <c r="N8" t="n">
-        <v>43</v>
+        <v>9</v>
       </c>
       <c r="O8" t="n">
-        <v>173</v>
+        <v>153</v>
       </c>
       <c r="P8" t="n">
         <v>3</v>
@@ -1179,7 +1179,7 @@
         <v>3</v>
       </c>
       <c r="R8" t="n">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1203,16 +1203,16 @@
         <v>5</v>
       </c>
       <c r="Z8" t="n">
-        <v>37.09571428571429</v>
+        <v>37.13571428571429</v>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>11|12|22|37|42|49|43</t>
+          <t>1|12|15|36|40|49|9</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:41</t>
+          <t>2026-05-28 17:22:47</t>
         </is>
       </c>
     </row>
@@ -1243,28 +1243,28 @@
         <v>7</v>
       </c>
       <c r="H9" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="I9" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J9" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="K9" t="n">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="L9" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="M9" t="n">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="N9" t="n">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="O9" t="n">
-        <v>169</v>
+        <v>159</v>
       </c>
       <c r="P9" t="n">
         <v>3</v>
@@ -1273,7 +1273,7 @@
         <v>3</v>
       </c>
       <c r="R9" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1297,16 +1297,16 @@
         <v>5</v>
       </c>
       <c r="Z9" t="n">
-        <v>36.56</v>
+        <v>36.6</v>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>9|10|22|37|42|49|55</t>
+          <t>5|8|27|32|41|46|43</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:41</t>
+          <t>2026-05-28 17:22:47</t>
         </is>
       </c>
     </row>
@@ -1337,28 +1337,28 @@
         <v>8</v>
       </c>
       <c r="H10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I10" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="J10" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="K10" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="L10" t="n">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="M10" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="N10" t="n">
-        <v>55</v>
+        <v>28</v>
       </c>
       <c r="O10" t="n">
-        <v>147</v>
+        <v>161</v>
       </c>
       <c r="P10" t="n">
         <v>3</v>
@@ -1367,7 +1367,7 @@
         <v>3</v>
       </c>
       <c r="R10" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1391,16 +1391,16 @@
         <v>5</v>
       </c>
       <c r="Z10" t="n">
-        <v>36.14333333333333</v>
+        <v>36.18333333333334</v>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>7|9|22|30|33|46|55</t>
+          <t>8|11|15|36|42|49|28</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:41</t>
+          <t>2026-05-28 17:22:47</t>
         </is>
       </c>
     </row>
@@ -1431,13 +1431,13 @@
         <v>9</v>
       </c>
       <c r="H11" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="I11" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="J11" t="n">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="K11" t="n">
         <v>32</v>
@@ -1449,10 +1449,10 @@
         <v>49</v>
       </c>
       <c r="N11" t="n">
-        <v>53</v>
+        <v>12</v>
       </c>
       <c r="O11" t="n">
-        <v>151</v>
+        <v>167</v>
       </c>
       <c r="P11" t="n">
         <v>3</v>
@@ -1461,7 +1461,7 @@
         <v>3</v>
       </c>
       <c r="R11" t="n">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1485,16 +1485,16 @@
         <v>5</v>
       </c>
       <c r="Z11" t="n">
-        <v>35.81</v>
+        <v>35.85</v>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>3|13|18|32|36|49|53</t>
+          <t>8|15|27|32|36|49|12</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:41</t>
+          <t>2026-05-28 17:22:47</t>
         </is>
       </c>
     </row>
@@ -1525,28 +1525,28 @@
         <v>10</v>
       </c>
       <c r="H12" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="I12" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="J12" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="K12" t="n">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="L12" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="M12" t="n">
         <v>48</v>
       </c>
       <c r="N12" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="O12" t="n">
-        <v>163</v>
+        <v>151</v>
       </c>
       <c r="P12" t="n">
         <v>3</v>
@@ -1555,7 +1555,7 @@
         <v>3</v>
       </c>
       <c r="R12" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1579,16 +1579,16 @@
         <v>5</v>
       </c>
       <c r="Z12" t="n">
-        <v>35.53727272727272</v>
+        <v>35.57727272727273</v>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>8|12|17|37|41|48|6</t>
+          <t>3|7|21|32|40|48|15</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:41</t>
+          <t>2026-05-28 17:22:47</t>
         </is>
       </c>
     </row>

--- a/data/exports/final_predictions/lotto_ensemble_predictions.xlsx
+++ b/data/exports/final_predictions/lotto_ensemble_predictions.xlsx
@@ -648,7 +648,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:47</t>
+          <t>2026-05-28 19:50:08</t>
         </is>
       </c>
     </row>
@@ -742,7 +742,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:47</t>
+          <t>2026-05-28 19:50:08</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:47</t>
+          <t>2026-05-28 19:50:08</t>
         </is>
       </c>
     </row>
@@ -930,7 +930,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:47</t>
+          <t>2026-05-28 19:50:08</t>
         </is>
       </c>
     </row>
@@ -1024,7 +1024,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:47</t>
+          <t>2026-05-28 19:50:08</t>
         </is>
       </c>
     </row>
@@ -1118,7 +1118,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:47</t>
+          <t>2026-05-28 19:50:08</t>
         </is>
       </c>
     </row>
@@ -1212,7 +1212,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:47</t>
+          <t>2026-05-28 19:50:08</t>
         </is>
       </c>
     </row>
@@ -1306,7 +1306,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:47</t>
+          <t>2026-05-28 19:50:08</t>
         </is>
       </c>
     </row>
@@ -1400,7 +1400,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:47</t>
+          <t>2026-05-28 19:50:08</t>
         </is>
       </c>
     </row>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:47</t>
+          <t>2026-05-28 19:50:08</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:47</t>
+          <t>2026-05-28 19:50:08</t>
         </is>
       </c>
     </row>

--- a/data/exports/final_predictions/lotto_ensemble_predictions.xlsx
+++ b/data/exports/final_predictions/lotto_ensemble_predictions.xlsx
@@ -648,7 +648,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-05-28 22:50:46</t>
+          <t>2026-05-30 03:12:42</t>
         </is>
       </c>
     </row>
@@ -742,7 +742,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-05-28 22:50:46</t>
+          <t>2026-05-30 03:12:42</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-05-28 22:50:46</t>
+          <t>2026-05-30 03:12:42</t>
         </is>
       </c>
     </row>
@@ -930,7 +930,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-05-28 22:50:46</t>
+          <t>2026-05-30 03:12:42</t>
         </is>
       </c>
     </row>
@@ -1024,7 +1024,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-05-28 22:50:46</t>
+          <t>2026-05-30 03:12:42</t>
         </is>
       </c>
     </row>
@@ -1118,7 +1118,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-05-28 22:50:46</t>
+          <t>2026-05-30 03:12:42</t>
         </is>
       </c>
     </row>
@@ -1212,7 +1212,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-05-28 22:50:46</t>
+          <t>2026-05-30 03:12:42</t>
         </is>
       </c>
     </row>
@@ -1306,7 +1306,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-05-28 22:50:46</t>
+          <t>2026-05-30 03:12:42</t>
         </is>
       </c>
     </row>
@@ -1400,7 +1400,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-05-28 22:50:46</t>
+          <t>2026-05-30 03:12:42</t>
         </is>
       </c>
     </row>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-05-28 22:50:46</t>
+          <t>2026-05-30 03:12:42</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-05-28 22:50:46</t>
+          <t>2026-05-30 03:12:42</t>
         </is>
       </c>
     </row>

--- a/data/exports/final_predictions/lotto_ensemble_predictions.xlsx
+++ b/data/exports/final_predictions/lotto_ensemble_predictions.xlsx
@@ -648,7 +648,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-05-30 03:12:42</t>
+          <t>2026-05-30 10:41:38</t>
         </is>
       </c>
     </row>
@@ -742,7 +742,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-05-30 03:12:42</t>
+          <t>2026-05-30 10:41:38</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-05-30 03:12:42</t>
+          <t>2026-05-30 10:41:38</t>
         </is>
       </c>
     </row>
@@ -930,7 +930,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-05-30 03:12:42</t>
+          <t>2026-05-30 10:41:38</t>
         </is>
       </c>
     </row>
@@ -1024,7 +1024,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-05-30 03:12:42</t>
+          <t>2026-05-30 10:41:38</t>
         </is>
       </c>
     </row>
@@ -1118,7 +1118,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-05-30 03:12:42</t>
+          <t>2026-05-30 10:41:38</t>
         </is>
       </c>
     </row>
@@ -1212,7 +1212,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-05-30 03:12:42</t>
+          <t>2026-05-30 10:41:38</t>
         </is>
       </c>
     </row>
@@ -1306,7 +1306,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-05-30 03:12:42</t>
+          <t>2026-05-30 10:41:38</t>
         </is>
       </c>
     </row>
@@ -1400,7 +1400,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-05-30 03:12:42</t>
+          <t>2026-05-30 10:41:38</t>
         </is>
       </c>
     </row>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-05-30 03:12:42</t>
+          <t>2026-05-30 10:41:38</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-05-30 03:12:42</t>
+          <t>2026-05-30 10:41:38</t>
         </is>
       </c>
     </row>

--- a/data/exports/final_predictions/lotto_ensemble_predictions.xlsx
+++ b/data/exports/final_predictions/lotto_ensemble_predictions.xlsx
@@ -648,7 +648,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-05-30 10:41:38</t>
+          <t>2026-05-30 14:19:48</t>
         </is>
       </c>
     </row>
@@ -742,7 +742,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-05-30 10:41:38</t>
+          <t>2026-05-30 14:19:48</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-05-30 10:41:38</t>
+          <t>2026-05-30 14:19:48</t>
         </is>
       </c>
     </row>
@@ -930,7 +930,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-05-30 10:41:38</t>
+          <t>2026-05-30 14:19:48</t>
         </is>
       </c>
     </row>
@@ -1024,7 +1024,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-05-30 10:41:38</t>
+          <t>2026-05-30 14:19:48</t>
         </is>
       </c>
     </row>
@@ -1118,7 +1118,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-05-30 10:41:38</t>
+          <t>2026-05-30 14:19:48</t>
         </is>
       </c>
     </row>
@@ -1212,7 +1212,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-05-30 10:41:38</t>
+          <t>2026-05-30 14:19:48</t>
         </is>
       </c>
     </row>
@@ -1306,7 +1306,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-05-30 10:41:38</t>
+          <t>2026-05-30 14:19:48</t>
         </is>
       </c>
     </row>
@@ -1400,7 +1400,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-05-30 10:41:38</t>
+          <t>2026-05-30 14:19:48</t>
         </is>
       </c>
     </row>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-05-30 10:41:38</t>
+          <t>2026-05-30 14:19:48</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-05-30 10:41:38</t>
+          <t>2026-05-30 14:19:48</t>
         </is>
       </c>
     </row>

--- a/data/exports/final_predictions/lotto_ensemble_predictions.xlsx
+++ b/data/exports/final_predictions/lotto_ensemble_predictions.xlsx
@@ -597,22 +597,22 @@
         <v>49</v>
       </c>
       <c r="L2" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="M2" t="n">
         <v>56</v>
       </c>
       <c r="N2" t="n">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="O2" t="n">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="P2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R2" t="n">
         <v>55</v>
@@ -639,16 +639,16 @@
         <v>8</v>
       </c>
       <c r="Z2" t="n">
-        <v>73.84999999999999</v>
+        <v>73.86</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1|4|44|49|52|56|14</t>
+          <t>1|4|44|49|51|56|29</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-05-30 14:19:48</t>
+          <t>2026-05-31 11:23:01</t>
         </is>
       </c>
     </row>
@@ -679,28 +679,28 @@
         <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J3" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="K3" t="n">
         <v>32</v>
       </c>
       <c r="L3" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="M3" t="n">
         <v>49</v>
       </c>
       <c r="N3" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="O3" t="n">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="P3" t="n">
         <v>3</v>
@@ -709,7 +709,7 @@
         <v>3</v>
       </c>
       <c r="R3" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -733,16 +733,16 @@
         <v>5</v>
       </c>
       <c r="Z3" t="n">
-        <v>47.85</v>
+        <v>47.86</v>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>11|12|22|32|37|49|21</t>
+          <t>12|13|24|32|35|49|11</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-05-30 14:19:48</t>
+          <t>2026-05-31 11:23:01</t>
         </is>
       </c>
     </row>
@@ -773,28 +773,28 @@
         <v>2</v>
       </c>
       <c r="H4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I4" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J4" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="K4" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="L4" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="M4" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="N4" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="O4" t="n">
-        <v>163</v>
+        <v>153</v>
       </c>
       <c r="P4" t="n">
         <v>3</v>
@@ -827,16 +827,16 @@
         <v>5</v>
       </c>
       <c r="Z4" t="n">
-        <v>42.85</v>
+        <v>42.86</v>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>7|12|23|33|40|48|42</t>
+          <t>8|11|17|32|36|49|50</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-05-30 14:19:48</t>
+          <t>2026-05-31 11:23:01</t>
         </is>
       </c>
     </row>
@@ -870,25 +870,25 @@
         <v>8</v>
       </c>
       <c r="I5" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J5" t="n">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="K5" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="L5" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="M5" t="n">
         <v>47</v>
       </c>
       <c r="N5" t="n">
-        <v>16</v>
+        <v>41</v>
       </c>
       <c r="O5" t="n">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="P5" t="n">
         <v>3</v>
@@ -921,16 +921,16 @@
         <v>5</v>
       </c>
       <c r="Z5" t="n">
-        <v>40.35</v>
+        <v>40.36</v>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>8|13|18|32|39|47|16</t>
+          <t>8|12|29|33|40|47|41</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-05-30 14:19:48</t>
+          <t>2026-05-31 11:23:01</t>
         </is>
       </c>
     </row>
@@ -961,28 +961,28 @@
         <v>4</v>
       </c>
       <c r="H6" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="I6" t="n">
         <v>8</v>
       </c>
       <c r="J6" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="K6" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="L6" t="n">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="M6" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="N6" t="n">
-        <v>16</v>
+        <v>52</v>
       </c>
       <c r="O6" t="n">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="P6" t="n">
         <v>3</v>
@@ -991,7 +991,7 @@
         <v>3</v>
       </c>
       <c r="R6" t="n">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1015,16 +1015,16 @@
         <v>5</v>
       </c>
       <c r="Z6" t="n">
-        <v>38.85</v>
+        <v>38.86</v>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2|8|23|38|43|47|16</t>
+          <t>7|8|22|32|37|49|52</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-05-30 14:19:48</t>
+          <t>2026-05-31 11:23:01</t>
         </is>
       </c>
     </row>
@@ -1055,37 +1055,37 @@
         <v>5</v>
       </c>
       <c r="H7" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="I7" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J7" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="K7" t="n">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="L7" t="n">
+        <v>37</v>
+      </c>
+      <c r="M7" t="n">
+        <v>45</v>
+      </c>
+      <c r="N7" t="n">
+        <v>8</v>
+      </c>
+      <c r="O7" t="n">
+        <v>149</v>
+      </c>
+      <c r="P7" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>3</v>
+      </c>
+      <c r="R7" t="n">
         <v>44</v>
-      </c>
-      <c r="M7" t="n">
-        <v>47</v>
-      </c>
-      <c r="N7" t="n">
-        <v>27</v>
-      </c>
-      <c r="O7" t="n">
-        <v>169</v>
-      </c>
-      <c r="P7" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>3</v>
-      </c>
-      <c r="R7" t="n">
-        <v>40</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1109,16 +1109,16 @@
         <v>5</v>
       </c>
       <c r="Z7" t="n">
-        <v>37.85</v>
+        <v>37.86</v>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>7|11|20|40|44|47|27</t>
+          <t>1|12|22|32|37|45|8</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-05-30 14:19:48</t>
+          <t>2026-05-31 11:23:01</t>
         </is>
       </c>
     </row>
@@ -1149,28 +1149,28 @@
         <v>6</v>
       </c>
       <c r="H8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I8" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="J8" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="K8" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="L8" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="M8" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="N8" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="O8" t="n">
-        <v>153</v>
+        <v>161</v>
       </c>
       <c r="P8" t="n">
         <v>3</v>
@@ -1179,7 +1179,7 @@
         <v>3</v>
       </c>
       <c r="R8" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1203,16 +1203,16 @@
         <v>5</v>
       </c>
       <c r="Z8" t="n">
-        <v>37.13571428571429</v>
+        <v>37.14571428571428</v>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>1|12|15|36|40|49|9</t>
+          <t>2|8|23|38|43|47|16</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-05-30 14:19:48</t>
+          <t>2026-05-31 11:23:01</t>
         </is>
       </c>
     </row>
@@ -1243,13 +1243,13 @@
         <v>7</v>
       </c>
       <c r="H9" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="I9" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="J9" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K9" t="n">
         <v>32</v>
@@ -1258,13 +1258,13 @@
         <v>41</v>
       </c>
       <c r="M9" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="N9" t="n">
-        <v>43</v>
+        <v>2</v>
       </c>
       <c r="O9" t="n">
-        <v>159</v>
+        <v>175</v>
       </c>
       <c r="P9" t="n">
         <v>3</v>
@@ -1273,7 +1273,7 @@
         <v>3</v>
       </c>
       <c r="R9" t="n">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1297,16 +1297,16 @@
         <v>5</v>
       </c>
       <c r="Z9" t="n">
-        <v>36.6</v>
+        <v>36.61</v>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>5|8|27|32|41|46|43</t>
+          <t>12|13|28|32|41|49|2</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-05-30 14:19:48</t>
+          <t>2026-05-31 11:23:01</t>
         </is>
       </c>
     </row>
@@ -1337,28 +1337,28 @@
         <v>8</v>
       </c>
       <c r="H10" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I10" t="n">
         <v>11</v>
       </c>
       <c r="J10" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="K10" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="L10" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="M10" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="N10" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="O10" t="n">
-        <v>161</v>
+        <v>169</v>
       </c>
       <c r="P10" t="n">
         <v>3</v>
@@ -1367,7 +1367,7 @@
         <v>3</v>
       </c>
       <c r="R10" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1391,16 +1391,16 @@
         <v>5</v>
       </c>
       <c r="Z10" t="n">
-        <v>36.18333333333334</v>
+        <v>36.19333333333333</v>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>8|11|15|36|42|49|28</t>
+          <t>7|11|20|40|44|47|27</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-05-30 14:19:48</t>
+          <t>2026-05-31 11:23:01</t>
         </is>
       </c>
     </row>
@@ -1431,28 +1431,28 @@
         <v>9</v>
       </c>
       <c r="H11" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I11" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="J11" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="K11" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="L11" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="M11" t="n">
         <v>49</v>
       </c>
       <c r="N11" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="O11" t="n">
-        <v>167</v>
+        <v>159</v>
       </c>
       <c r="P11" t="n">
         <v>3</v>
@@ -1461,7 +1461,7 @@
         <v>3</v>
       </c>
       <c r="R11" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1485,16 +1485,16 @@
         <v>5</v>
       </c>
       <c r="Z11" t="n">
-        <v>35.85</v>
+        <v>35.86</v>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>8|15|27|32|36|49|12</t>
+          <t>6|12|26|31|35|49|25</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-05-30 14:19:48</t>
+          <t>2026-05-31 11:23:01</t>
         </is>
       </c>
     </row>
@@ -1525,37 +1525,37 @@
         <v>10</v>
       </c>
       <c r="H12" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I12" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="J12" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="K12" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="L12" t="n">
+        <v>36</v>
+      </c>
+      <c r="M12" t="n">
+        <v>46</v>
+      </c>
+      <c r="N12" t="n">
+        <v>53</v>
+      </c>
+      <c r="O12" t="n">
+        <v>143</v>
+      </c>
+      <c r="P12" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>3</v>
+      </c>
+      <c r="R12" t="n">
         <v>40</v>
-      </c>
-      <c r="M12" t="n">
-        <v>48</v>
-      </c>
-      <c r="N12" t="n">
-        <v>15</v>
-      </c>
-      <c r="O12" t="n">
-        <v>151</v>
-      </c>
-      <c r="P12" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>3</v>
-      </c>
-      <c r="R12" t="n">
-        <v>45</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1579,16 +1579,16 @@
         <v>5</v>
       </c>
       <c r="Z12" t="n">
-        <v>35.57727272727273</v>
+        <v>35.58727272727273</v>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>3|7|21|32|40|48|15</t>
+          <t>6|9|15|31|36|46|53</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-05-30 14:19:48</t>
+          <t>2026-05-31 11:23:01</t>
         </is>
       </c>
     </row>

--- a/data/exports/final_predictions/lotto_ensemble_predictions.xlsx
+++ b/data/exports/final_predictions/lotto_ensemble_predictions.xlsx
@@ -648,7 +648,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-05-31 11:23:01</t>
+          <t>2026-06-01 09:02:20</t>
         </is>
       </c>
     </row>
@@ -742,7 +742,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-05-31 11:23:01</t>
+          <t>2026-06-01 09:02:20</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-05-31 11:23:01</t>
+          <t>2026-06-01 09:02:20</t>
         </is>
       </c>
     </row>
@@ -930,7 +930,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-05-31 11:23:01</t>
+          <t>2026-06-01 09:02:20</t>
         </is>
       </c>
     </row>
@@ -1024,7 +1024,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-05-31 11:23:01</t>
+          <t>2026-06-01 09:02:20</t>
         </is>
       </c>
     </row>
@@ -1118,7 +1118,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-05-31 11:23:01</t>
+          <t>2026-06-01 09:02:20</t>
         </is>
       </c>
     </row>
@@ -1212,7 +1212,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-05-31 11:23:01</t>
+          <t>2026-06-01 09:02:20</t>
         </is>
       </c>
     </row>
@@ -1306,7 +1306,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-05-31 11:23:01</t>
+          <t>2026-06-01 09:02:20</t>
         </is>
       </c>
     </row>
@@ -1400,7 +1400,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-05-31 11:23:01</t>
+          <t>2026-06-01 09:02:20</t>
         </is>
       </c>
     </row>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-05-31 11:23:01</t>
+          <t>2026-06-01 09:02:20</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-05-31 11:23:01</t>
+          <t>2026-06-01 09:02:20</t>
         </is>
       </c>
     </row>

--- a/data/exports/final_predictions/lotto_ensemble_predictions.xlsx
+++ b/data/exports/final_predictions/lotto_ensemble_predictions.xlsx
@@ -648,7 +648,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-06-01 09:02:20</t>
+          <t>2026-06-01 20:59:44</t>
         </is>
       </c>
     </row>
@@ -742,7 +742,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-06-01 09:02:20</t>
+          <t>2026-06-01 20:59:44</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-06-01 09:02:20</t>
+          <t>2026-06-01 20:59:44</t>
         </is>
       </c>
     </row>
@@ -930,7 +930,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-06-01 09:02:20</t>
+          <t>2026-06-01 20:59:44</t>
         </is>
       </c>
     </row>
@@ -1024,7 +1024,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-06-01 09:02:20</t>
+          <t>2026-06-01 20:59:44</t>
         </is>
       </c>
     </row>
@@ -1118,7 +1118,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-06-01 09:02:20</t>
+          <t>2026-06-01 20:59:44</t>
         </is>
       </c>
     </row>
@@ -1212,7 +1212,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-06-01 09:02:20</t>
+          <t>2026-06-01 20:59:44</t>
         </is>
       </c>
     </row>
@@ -1306,7 +1306,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-06-01 09:02:20</t>
+          <t>2026-06-01 20:59:44</t>
         </is>
       </c>
     </row>
@@ -1400,7 +1400,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-06-01 09:02:20</t>
+          <t>2026-06-01 20:59:44</t>
         </is>
       </c>
     </row>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-06-01 09:02:20</t>
+          <t>2026-06-01 20:59:44</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-06-01 09:02:20</t>
+          <t>2026-06-01 20:59:44</t>
         </is>
       </c>
     </row>

--- a/data/exports/final_predictions/lotto_ensemble_predictions.xlsx
+++ b/data/exports/final_predictions/lotto_ensemble_predictions.xlsx
@@ -648,7 +648,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-06-01 20:59:44</t>
+          <t>2026-06-02 18:38:28</t>
         </is>
       </c>
     </row>
@@ -742,7 +742,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-06-01 20:59:44</t>
+          <t>2026-06-02 18:38:28</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-06-01 20:59:44</t>
+          <t>2026-06-02 18:38:28</t>
         </is>
       </c>
     </row>
@@ -930,7 +930,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-06-01 20:59:44</t>
+          <t>2026-06-02 18:38:28</t>
         </is>
       </c>
     </row>
@@ -1024,7 +1024,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-06-01 20:59:44</t>
+          <t>2026-06-02 18:38:28</t>
         </is>
       </c>
     </row>
@@ -1118,7 +1118,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-06-01 20:59:44</t>
+          <t>2026-06-02 18:38:28</t>
         </is>
       </c>
     </row>
@@ -1212,7 +1212,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-06-01 20:59:44</t>
+          <t>2026-06-02 18:38:28</t>
         </is>
       </c>
     </row>
@@ -1306,7 +1306,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-06-01 20:59:44</t>
+          <t>2026-06-02 18:38:28</t>
         </is>
       </c>
     </row>
@@ -1400,7 +1400,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-06-01 20:59:44</t>
+          <t>2026-06-02 18:38:28</t>
         </is>
       </c>
     </row>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-06-01 20:59:44</t>
+          <t>2026-06-02 18:38:28</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-06-01 20:59:44</t>
+          <t>2026-06-02 18:38:28</t>
         </is>
       </c>
     </row>

--- a/data/exports/final_predictions/lotto_ensemble_predictions.xlsx
+++ b/data/exports/final_predictions/lotto_ensemble_predictions.xlsx
@@ -648,7 +648,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-06-02 18:38:28</t>
+          <t>2026-06-03 19:09:42</t>
         </is>
       </c>
     </row>
@@ -742,7 +742,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-06-02 18:38:28</t>
+          <t>2026-06-03 19:09:42</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-06-02 18:38:28</t>
+          <t>2026-06-03 19:09:42</t>
         </is>
       </c>
     </row>
@@ -930,7 +930,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-06-02 18:38:28</t>
+          <t>2026-06-03 19:09:42</t>
         </is>
       </c>
     </row>
@@ -1024,7 +1024,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-06-02 18:38:28</t>
+          <t>2026-06-03 19:09:42</t>
         </is>
       </c>
     </row>
@@ -1118,7 +1118,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-06-02 18:38:28</t>
+          <t>2026-06-03 19:09:42</t>
         </is>
       </c>
     </row>
@@ -1212,7 +1212,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-06-02 18:38:28</t>
+          <t>2026-06-03 19:09:42</t>
         </is>
       </c>
     </row>
@@ -1306,7 +1306,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-06-02 18:38:28</t>
+          <t>2026-06-03 19:09:42</t>
         </is>
       </c>
     </row>
@@ -1400,7 +1400,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-06-02 18:38:28</t>
+          <t>2026-06-03 19:09:42</t>
         </is>
       </c>
     </row>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-06-02 18:38:28</t>
+          <t>2026-06-03 19:09:42</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-06-02 18:38:28</t>
+          <t>2026-06-03 19:09:42</t>
         </is>
       </c>
     </row>

--- a/data/exports/final_predictions/lotto_ensemble_predictions.xlsx
+++ b/data/exports/final_predictions/lotto_ensemble_predictions.xlsx
@@ -585,7 +585,7 @@
         <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I2" t="n">
         <v>4</v>
@@ -603,19 +603,19 @@
         <v>56</v>
       </c>
       <c r="N2" t="n">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="O2" t="n">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="P2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R2" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -639,16 +639,16 @@
         <v>8</v>
       </c>
       <c r="Z2" t="n">
-        <v>73.86</v>
+        <v>73.84</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1|4|44|49|51|56|29</t>
+          <t>2|4|44|49|51|56|47</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-06-03 19:09:42</t>
+          <t>2026-06-04 14:28:51</t>
         </is>
       </c>
     </row>
@@ -679,28 +679,28 @@
         <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="I3" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="J3" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="K3" t="n">
         <v>32</v>
       </c>
       <c r="L3" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="M3" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="N3" t="n">
-        <v>11</v>
+        <v>46</v>
       </c>
       <c r="O3" t="n">
-        <v>165</v>
+        <v>157</v>
       </c>
       <c r="P3" t="n">
         <v>3</v>
@@ -709,7 +709,7 @@
         <v>3</v>
       </c>
       <c r="R3" t="n">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -733,16 +733,16 @@
         <v>5</v>
       </c>
       <c r="Z3" t="n">
-        <v>47.86</v>
+        <v>47.84</v>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>12|13|24|32|35|49|11</t>
+          <t>1|11|27|32|38|48|46</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-06-03 19:09:42</t>
+          <t>2026-06-04 14:28:51</t>
         </is>
       </c>
     </row>
@@ -773,28 +773,28 @@
         <v>2</v>
       </c>
       <c r="H4" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="I4" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="J4" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="K4" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="L4" t="n">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="M4" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="N4" t="n">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="O4" t="n">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="P4" t="n">
         <v>3</v>
@@ -803,7 +803,7 @@
         <v>3</v>
       </c>
       <c r="R4" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -827,16 +827,16 @@
         <v>5</v>
       </c>
       <c r="Z4" t="n">
-        <v>42.86</v>
+        <v>42.84</v>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>8|11|17|32|36|49|50</t>
+          <t>3|9|23|30|44|48|37</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-06-03 19:09:42</t>
+          <t>2026-06-04 14:28:51</t>
         </is>
       </c>
     </row>
@@ -867,28 +867,28 @@
         <v>3</v>
       </c>
       <c r="H5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I5" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J5" t="n">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="K5" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="L5" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="M5" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="N5" t="n">
-        <v>41</v>
+        <v>11</v>
       </c>
       <c r="O5" t="n">
-        <v>169</v>
+        <v>157</v>
       </c>
       <c r="P5" t="n">
         <v>3</v>
@@ -897,7 +897,7 @@
         <v>3</v>
       </c>
       <c r="R5" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -921,16 +921,16 @@
         <v>5</v>
       </c>
       <c r="Z5" t="n">
-        <v>40.36</v>
+        <v>40.34</v>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>8|12|29|33|40|47|41</t>
+          <t>9|13|21|32|36|46|11</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-06-03 19:09:42</t>
+          <t>2026-06-04 14:28:51</t>
         </is>
       </c>
     </row>
@@ -961,28 +961,28 @@
         <v>4</v>
       </c>
       <c r="H6" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I6" t="n">
         <v>8</v>
       </c>
       <c r="J6" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="K6" t="n">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="L6" t="n">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="M6" t="n">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="N6" t="n">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="O6" t="n">
-        <v>155</v>
+        <v>169</v>
       </c>
       <c r="P6" t="n">
         <v>3</v>
@@ -991,7 +991,7 @@
         <v>3</v>
       </c>
       <c r="R6" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1015,16 +1015,16 @@
         <v>5</v>
       </c>
       <c r="Z6" t="n">
-        <v>38.86</v>
+        <v>38.84</v>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>7|8|22|32|37|49|52</t>
+          <t>5|8|24|43|44|45|38</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-06-03 19:09:42</t>
+          <t>2026-06-04 14:28:51</t>
         </is>
       </c>
     </row>
@@ -1055,28 +1055,28 @@
         <v>5</v>
       </c>
       <c r="H7" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="I7" t="n">
         <v>12</v>
       </c>
       <c r="J7" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="K7" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="L7" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="M7" t="n">
         <v>45</v>
       </c>
       <c r="N7" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="O7" t="n">
-        <v>149</v>
+        <v>157</v>
       </c>
       <c r="P7" t="n">
         <v>3</v>
@@ -1085,7 +1085,7 @@
         <v>3</v>
       </c>
       <c r="R7" t="n">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1109,16 +1109,16 @@
         <v>5</v>
       </c>
       <c r="Z7" t="n">
-        <v>37.86</v>
+        <v>37.84</v>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>1|12|22|32|37|45|8</t>
+          <t>8|12|15|38|39|45|18</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-06-03 19:09:42</t>
+          <t>2026-06-04 14:28:51</t>
         </is>
       </c>
     </row>
@@ -1149,37 +1149,37 @@
         <v>6</v>
       </c>
       <c r="H8" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="I8" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="J8" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="K8" t="n">
+        <v>37</v>
+      </c>
+      <c r="L8" t="n">
+        <v>42</v>
+      </c>
+      <c r="M8" t="n">
+        <v>49</v>
+      </c>
+      <c r="N8" t="n">
+        <v>43</v>
+      </c>
+      <c r="O8" t="n">
+        <v>173</v>
+      </c>
+      <c r="P8" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>3</v>
+      </c>
+      <c r="R8" t="n">
         <v>38</v>
-      </c>
-      <c r="L8" t="n">
-        <v>43</v>
-      </c>
-      <c r="M8" t="n">
-        <v>47</v>
-      </c>
-      <c r="N8" t="n">
-        <v>16</v>
-      </c>
-      <c r="O8" t="n">
-        <v>161</v>
-      </c>
-      <c r="P8" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>3</v>
-      </c>
-      <c r="R8" t="n">
-        <v>45</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1203,16 +1203,16 @@
         <v>5</v>
       </c>
       <c r="Z8" t="n">
-        <v>37.14571428571428</v>
+        <v>37.12571428571429</v>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2|8|23|38|43|47|16</t>
+          <t>11|12|22|37|42|49|43</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-06-03 19:09:42</t>
+          <t>2026-06-04 14:28:51</t>
         </is>
       </c>
     </row>
@@ -1243,16 +1243,16 @@
         <v>7</v>
       </c>
       <c r="H9" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="I9" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="J9" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="K9" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="L9" t="n">
         <v>41</v>
@@ -1261,10 +1261,10 @@
         <v>49</v>
       </c>
       <c r="N9" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="O9" t="n">
-        <v>175</v>
+        <v>159</v>
       </c>
       <c r="P9" t="n">
         <v>3</v>
@@ -1273,7 +1273,7 @@
         <v>3</v>
       </c>
       <c r="R9" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1297,16 +1297,16 @@
         <v>5</v>
       </c>
       <c r="Z9" t="n">
-        <v>36.61</v>
+        <v>36.59</v>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>12|13|28|32|41|49|2</t>
+          <t>8|9|16|36|41|49|20</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-06-03 19:09:42</t>
+          <t>2026-06-04 14:28:51</t>
         </is>
       </c>
     </row>
@@ -1337,28 +1337,28 @@
         <v>8</v>
       </c>
       <c r="H10" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I10" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J10" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="K10" t="n">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="L10" t="n">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="M10" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="N10" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="O10" t="n">
-        <v>169</v>
+        <v>159</v>
       </c>
       <c r="P10" t="n">
         <v>3</v>
@@ -1367,7 +1367,7 @@
         <v>3</v>
       </c>
       <c r="R10" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1391,16 +1391,16 @@
         <v>5</v>
       </c>
       <c r="Z10" t="n">
-        <v>36.19333333333333</v>
+        <v>36.17333333333333</v>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>7|11|20|40|44|47|27</t>
+          <t>6|12|26|31|35|49|25</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-06-03 19:09:42</t>
+          <t>2026-06-04 14:28:51</t>
         </is>
       </c>
     </row>
@@ -1434,25 +1434,25 @@
         <v>6</v>
       </c>
       <c r="I11" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J11" t="n">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="K11" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="L11" t="n">
         <v>35</v>
       </c>
       <c r="M11" t="n">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="N11" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="O11" t="n">
-        <v>159</v>
+        <v>147</v>
       </c>
       <c r="P11" t="n">
         <v>3</v>
@@ -1461,7 +1461,7 @@
         <v>3</v>
       </c>
       <c r="R11" t="n">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1485,16 +1485,16 @@
         <v>5</v>
       </c>
       <c r="Z11" t="n">
-        <v>35.86</v>
+        <v>35.84</v>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>6|12|26|31|35|49|25</t>
+          <t>6|13|15|32|35|46|17</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-06-03 19:09:42</t>
+          <t>2026-06-04 14:28:51</t>
         </is>
       </c>
     </row>
@@ -1525,16 +1525,16 @@
         <v>10</v>
       </c>
       <c r="H12" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="I12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J12" t="n">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="K12" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="L12" t="n">
         <v>36</v>
@@ -1543,10 +1543,10 @@
         <v>46</v>
       </c>
       <c r="N12" t="n">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="O12" t="n">
-        <v>143</v>
+        <v>165</v>
       </c>
       <c r="P12" t="n">
         <v>3</v>
@@ -1555,7 +1555,7 @@
         <v>3</v>
       </c>
       <c r="R12" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1579,16 +1579,16 @@
         <v>5</v>
       </c>
       <c r="Z12" t="n">
-        <v>35.58727272727273</v>
+        <v>35.56727272727272</v>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>6|9|15|31|36|46|53</t>
+          <t>9|10|29|35|36|46|43</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-06-03 19:09:42</t>
+          <t>2026-06-04 14:28:51</t>
         </is>
       </c>
     </row>

--- a/data/exports/final_predictions/lotto_ensemble_predictions.xlsx
+++ b/data/exports/final_predictions/lotto_ensemble_predictions.xlsx
@@ -585,7 +585,7 @@
         <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I2" t="n">
         <v>4</v>
@@ -597,13 +597,13 @@
         <v>49</v>
       </c>
       <c r="L2" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="M2" t="n">
         <v>56</v>
       </c>
       <c r="N2" t="n">
-        <v>47</v>
+        <v>14</v>
       </c>
       <c r="O2" t="n">
         <v>206</v>
@@ -615,7 +615,7 @@
         <v>4</v>
       </c>
       <c r="R2" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -639,16 +639,16 @@
         <v>8</v>
       </c>
       <c r="Z2" t="n">
-        <v>73.84</v>
+        <v>73.84999999999999</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2|4|44|49|51|56|47</t>
+          <t>1|4|44|49|52|56|14</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-06-04 14:28:51</t>
+          <t>2026-06-05 14:20:01</t>
         </is>
       </c>
     </row>
@@ -679,37 +679,37 @@
         <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="I3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J3" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="K3" t="n">
         <v>32</v>
       </c>
       <c r="L3" t="n">
+        <v>37</v>
+      </c>
+      <c r="M3" t="n">
+        <v>49</v>
+      </c>
+      <c r="N3" t="n">
+        <v>21</v>
+      </c>
+      <c r="O3" t="n">
+        <v>163</v>
+      </c>
+      <c r="P3" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>3</v>
+      </c>
+      <c r="R3" t="n">
         <v>38</v>
-      </c>
-      <c r="M3" t="n">
-        <v>48</v>
-      </c>
-      <c r="N3" t="n">
-        <v>46</v>
-      </c>
-      <c r="O3" t="n">
-        <v>157</v>
-      </c>
-      <c r="P3" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>3</v>
-      </c>
-      <c r="R3" t="n">
-        <v>47</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -733,16 +733,16 @@
         <v>5</v>
       </c>
       <c r="Z3" t="n">
-        <v>47.84</v>
+        <v>47.85</v>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>1|11|27|32|38|48|46</t>
+          <t>11|12|22|32|37|49|21</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-06-04 14:28:51</t>
+          <t>2026-06-05 14:20:01</t>
         </is>
       </c>
     </row>
@@ -773,28 +773,28 @@
         <v>2</v>
       </c>
       <c r="H4" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="I4" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="J4" t="n">
         <v>23</v>
       </c>
       <c r="K4" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="L4" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="M4" t="n">
         <v>48</v>
       </c>
       <c r="N4" t="n">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="O4" t="n">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="P4" t="n">
         <v>3</v>
@@ -803,7 +803,7 @@
         <v>3</v>
       </c>
       <c r="R4" t="n">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -827,16 +827,16 @@
         <v>5</v>
       </c>
       <c r="Z4" t="n">
-        <v>42.84</v>
+        <v>42.85</v>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>3|9|23|30|44|48|37</t>
+          <t>7|12|23|33|40|48|42</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-06-04 14:28:51</t>
+          <t>2026-06-05 14:20:01</t>
         </is>
       </c>
     </row>
@@ -867,25 +867,25 @@
         <v>3</v>
       </c>
       <c r="H5" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I5" t="n">
         <v>13</v>
       </c>
       <c r="J5" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="K5" t="n">
         <v>32</v>
       </c>
       <c r="L5" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="M5" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="N5" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="O5" t="n">
         <v>157</v>
@@ -897,7 +897,7 @@
         <v>3</v>
       </c>
       <c r="R5" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -921,16 +921,16 @@
         <v>5</v>
       </c>
       <c r="Z5" t="n">
-        <v>40.34</v>
+        <v>40.35</v>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>9|13|21|32|36|46|11</t>
+          <t>8|13|18|32|39|47|16</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-06-04 14:28:51</t>
+          <t>2026-06-05 14:20:01</t>
         </is>
       </c>
     </row>
@@ -961,37 +961,37 @@
         <v>4</v>
       </c>
       <c r="H6" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I6" t="n">
         <v>8</v>
       </c>
       <c r="J6" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="K6" t="n">
+        <v>38</v>
+      </c>
+      <c r="L6" t="n">
         <v>43</v>
       </c>
-      <c r="L6" t="n">
-        <v>44</v>
-      </c>
       <c r="M6" t="n">
+        <v>47</v>
+      </c>
+      <c r="N6" t="n">
+        <v>16</v>
+      </c>
+      <c r="O6" t="n">
+        <v>161</v>
+      </c>
+      <c r="P6" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>3</v>
+      </c>
+      <c r="R6" t="n">
         <v>45</v>
-      </c>
-      <c r="N6" t="n">
-        <v>38</v>
-      </c>
-      <c r="O6" t="n">
-        <v>169</v>
-      </c>
-      <c r="P6" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>3</v>
-      </c>
-      <c r="R6" t="n">
-        <v>40</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1015,16 +1015,16 @@
         <v>5</v>
       </c>
       <c r="Z6" t="n">
-        <v>38.84</v>
+        <v>38.85</v>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>5|8|24|43|44|45|38</t>
+          <t>2|8|23|38|43|47|16</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-06-04 14:28:51</t>
+          <t>2026-06-05 14:20:01</t>
         </is>
       </c>
     </row>
@@ -1055,28 +1055,28 @@
         <v>5</v>
       </c>
       <c r="H7" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I7" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J7" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="K7" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="L7" t="n">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="M7" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="N7" t="n">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="O7" t="n">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="P7" t="n">
         <v>3</v>
@@ -1085,7 +1085,7 @@
         <v>3</v>
       </c>
       <c r="R7" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1109,16 +1109,16 @@
         <v>5</v>
       </c>
       <c r="Z7" t="n">
-        <v>37.84</v>
+        <v>37.85</v>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>8|12|15|38|39|45|18</t>
+          <t>7|11|20|40|44|47|27</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-06-04 14:28:51</t>
+          <t>2026-06-05 14:20:01</t>
         </is>
       </c>
     </row>
@@ -1149,28 +1149,28 @@
         <v>6</v>
       </c>
       <c r="H8" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="I8" t="n">
         <v>12</v>
       </c>
       <c r="J8" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="K8" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="L8" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="M8" t="n">
         <v>49</v>
       </c>
       <c r="N8" t="n">
-        <v>43</v>
+        <v>9</v>
       </c>
       <c r="O8" t="n">
-        <v>173</v>
+        <v>153</v>
       </c>
       <c r="P8" t="n">
         <v>3</v>
@@ -1179,7 +1179,7 @@
         <v>3</v>
       </c>
       <c r="R8" t="n">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1203,16 +1203,16 @@
         <v>5</v>
       </c>
       <c r="Z8" t="n">
-        <v>37.12571428571429</v>
+        <v>37.13571428571429</v>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>11|12|22|37|42|49|43</t>
+          <t>1|12|15|36|40|49|9</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-06-04 14:28:51</t>
+          <t>2026-06-05 14:20:01</t>
         </is>
       </c>
     </row>
@@ -1243,25 +1243,25 @@
         <v>7</v>
       </c>
       <c r="H9" t="n">
+        <v>5</v>
+      </c>
+      <c r="I9" t="n">
         <v>8</v>
       </c>
-      <c r="I9" t="n">
-        <v>9</v>
-      </c>
       <c r="J9" t="n">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="K9" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="L9" t="n">
         <v>41</v>
       </c>
       <c r="M9" t="n">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="N9" t="n">
-        <v>20</v>
+        <v>43</v>
       </c>
       <c r="O9" t="n">
         <v>159</v>
@@ -1297,16 +1297,16 @@
         <v>5</v>
       </c>
       <c r="Z9" t="n">
-        <v>36.59</v>
+        <v>36.6</v>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>8|9|16|36|41|49|20</t>
+          <t>5|8|27|32|41|46|43</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-06-04 14:28:51</t>
+          <t>2026-06-05 14:20:01</t>
         </is>
       </c>
     </row>
@@ -1337,28 +1337,28 @@
         <v>8</v>
       </c>
       <c r="H10" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I10" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J10" t="n">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="K10" t="n">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="L10" t="n">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="M10" t="n">
         <v>49</v>
       </c>
       <c r="N10" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="O10" t="n">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="P10" t="n">
         <v>3</v>
@@ -1367,7 +1367,7 @@
         <v>3</v>
       </c>
       <c r="R10" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1391,16 +1391,16 @@
         <v>5</v>
       </c>
       <c r="Z10" t="n">
-        <v>36.17333333333333</v>
+        <v>36.18333333333334</v>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>6|12|26|31|35|49|25</t>
+          <t>8|11|15|36|42|49|28</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-06-04 14:28:51</t>
+          <t>2026-06-05 14:20:01</t>
         </is>
       </c>
     </row>
@@ -1431,28 +1431,28 @@
         <v>9</v>
       </c>
       <c r="H11" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I11" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="J11" t="n">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="K11" t="n">
         <v>32</v>
       </c>
       <c r="L11" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="M11" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="N11" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="O11" t="n">
-        <v>147</v>
+        <v>167</v>
       </c>
       <c r="P11" t="n">
         <v>3</v>
@@ -1461,7 +1461,7 @@
         <v>3</v>
       </c>
       <c r="R11" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1485,16 +1485,16 @@
         <v>5</v>
       </c>
       <c r="Z11" t="n">
-        <v>35.84</v>
+        <v>35.85</v>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>6|13|15|32|35|46|17</t>
+          <t>8|15|27|32|36|49|12</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-06-04 14:28:51</t>
+          <t>2026-06-05 14:20:01</t>
         </is>
       </c>
     </row>
@@ -1525,28 +1525,28 @@
         <v>10</v>
       </c>
       <c r="H12" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="I12" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="J12" t="n">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="K12" t="n">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="L12" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="M12" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="N12" t="n">
-        <v>43</v>
+        <v>15</v>
       </c>
       <c r="O12" t="n">
-        <v>165</v>
+        <v>151</v>
       </c>
       <c r="P12" t="n">
         <v>3</v>
@@ -1555,7 +1555,7 @@
         <v>3</v>
       </c>
       <c r="R12" t="n">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1579,16 +1579,16 @@
         <v>5</v>
       </c>
       <c r="Z12" t="n">
-        <v>35.56727272727272</v>
+        <v>35.57727272727273</v>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>9|10|29|35|36|46|43</t>
+          <t>3|7|21|32|40|48|15</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-06-04 14:28:51</t>
+          <t>2026-06-05 14:20:01</t>
         </is>
       </c>
     </row>

--- a/data/exports/final_predictions/lotto_ensemble_predictions.xlsx
+++ b/data/exports/final_predictions/lotto_ensemble_predictions.xlsx
@@ -585,7 +585,7 @@
         <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I2" t="n">
         <v>4</v>
@@ -597,13 +597,13 @@
         <v>49</v>
       </c>
       <c r="L2" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="M2" t="n">
         <v>56</v>
       </c>
       <c r="N2" t="n">
-        <v>14</v>
+        <v>47</v>
       </c>
       <c r="O2" t="n">
         <v>206</v>
@@ -615,7 +615,7 @@
         <v>4</v>
       </c>
       <c r="R2" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -639,16 +639,16 @@
         <v>8</v>
       </c>
       <c r="Z2" t="n">
-        <v>73.84999999999999</v>
+        <v>73.84</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1|4|44|49|52|56|14</t>
+          <t>2|4|44|49|51|56|47</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-06-05 14:20:01</t>
+          <t>2026-06-06 11:13:24</t>
         </is>
       </c>
     </row>
@@ -679,28 +679,28 @@
         <v>1</v>
       </c>
       <c r="H3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I3" t="n">
         <v>11</v>
       </c>
-      <c r="I3" t="n">
-        <v>12</v>
-      </c>
       <c r="J3" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="K3" t="n">
         <v>32</v>
       </c>
       <c r="L3" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M3" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="N3" t="n">
-        <v>21</v>
+        <v>46</v>
       </c>
       <c r="O3" t="n">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="P3" t="n">
         <v>3</v>
@@ -709,7 +709,7 @@
         <v>3</v>
       </c>
       <c r="R3" t="n">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -733,16 +733,16 @@
         <v>5</v>
       </c>
       <c r="Z3" t="n">
-        <v>47.85</v>
+        <v>47.84</v>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>11|12|22|32|37|49|21</t>
+          <t>1|11|27|32|38|48|46</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-06-05 14:20:01</t>
+          <t>2026-06-06 11:13:24</t>
         </is>
       </c>
     </row>
@@ -773,28 +773,28 @@
         <v>2</v>
       </c>
       <c r="H4" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="I4" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="J4" t="n">
         <v>23</v>
       </c>
       <c r="K4" t="n">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="L4" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="M4" t="n">
         <v>48</v>
       </c>
       <c r="N4" t="n">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="O4" t="n">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="P4" t="n">
         <v>3</v>
@@ -803,7 +803,7 @@
         <v>3</v>
       </c>
       <c r="R4" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -827,16 +827,16 @@
         <v>5</v>
       </c>
       <c r="Z4" t="n">
-        <v>42.85</v>
+        <v>42.84</v>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>7|12|23|33|40|48|42</t>
+          <t>3|9|23|30|44|48|37</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-06-05 14:20:01</t>
+          <t>2026-06-06 11:13:24</t>
         </is>
       </c>
     </row>
@@ -867,25 +867,25 @@
         <v>3</v>
       </c>
       <c r="H5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I5" t="n">
         <v>13</v>
       </c>
       <c r="J5" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="K5" t="n">
         <v>32</v>
       </c>
       <c r="L5" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="M5" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="N5" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="O5" t="n">
         <v>157</v>
@@ -897,7 +897,7 @@
         <v>3</v>
       </c>
       <c r="R5" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -921,16 +921,16 @@
         <v>5</v>
       </c>
       <c r="Z5" t="n">
-        <v>40.35</v>
+        <v>40.34</v>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>8|13|18|32|39|47|16</t>
+          <t>9|13|21|32|36|46|11</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-06-05 14:20:01</t>
+          <t>2026-06-06 11:13:24</t>
         </is>
       </c>
     </row>
@@ -961,28 +961,28 @@
         <v>4</v>
       </c>
       <c r="H6" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I6" t="n">
         <v>8</v>
       </c>
       <c r="J6" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K6" t="n">
+        <v>43</v>
+      </c>
+      <c r="L6" t="n">
+        <v>44</v>
+      </c>
+      <c r="M6" t="n">
+        <v>45</v>
+      </c>
+      <c r="N6" t="n">
         <v>38</v>
       </c>
-      <c r="L6" t="n">
-        <v>43</v>
-      </c>
-      <c r="M6" t="n">
-        <v>47</v>
-      </c>
-      <c r="N6" t="n">
-        <v>16</v>
-      </c>
       <c r="O6" t="n">
-        <v>161</v>
+        <v>169</v>
       </c>
       <c r="P6" t="n">
         <v>3</v>
@@ -991,7 +991,7 @@
         <v>3</v>
       </c>
       <c r="R6" t="n">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1015,16 +1015,16 @@
         <v>5</v>
       </c>
       <c r="Z6" t="n">
-        <v>38.85</v>
+        <v>38.84</v>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2|8|23|38|43|47|16</t>
+          <t>5|8|24|43|44|45|38</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-06-05 14:20:01</t>
+          <t>2026-06-06 11:13:24</t>
         </is>
       </c>
     </row>
@@ -1055,28 +1055,28 @@
         <v>5</v>
       </c>
       <c r="H7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I7" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J7" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="K7" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="L7" t="n">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="M7" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="N7" t="n">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="O7" t="n">
-        <v>169</v>
+        <v>157</v>
       </c>
       <c r="P7" t="n">
         <v>3</v>
@@ -1085,7 +1085,7 @@
         <v>3</v>
       </c>
       <c r="R7" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1109,16 +1109,16 @@
         <v>5</v>
       </c>
       <c r="Z7" t="n">
-        <v>37.85</v>
+        <v>37.84</v>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>7|11|20|40|44|47|27</t>
+          <t>8|12|15|38|39|45|18</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-06-05 14:20:01</t>
+          <t>2026-06-06 11:13:24</t>
         </is>
       </c>
     </row>
@@ -1149,28 +1149,28 @@
         <v>6</v>
       </c>
       <c r="H8" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="I8" t="n">
         <v>12</v>
       </c>
       <c r="J8" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="K8" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="L8" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="M8" t="n">
         <v>49</v>
       </c>
       <c r="N8" t="n">
-        <v>9</v>
+        <v>43</v>
       </c>
       <c r="O8" t="n">
-        <v>153</v>
+        <v>173</v>
       </c>
       <c r="P8" t="n">
         <v>3</v>
@@ -1179,7 +1179,7 @@
         <v>3</v>
       </c>
       <c r="R8" t="n">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1203,16 +1203,16 @@
         <v>5</v>
       </c>
       <c r="Z8" t="n">
-        <v>37.13571428571429</v>
+        <v>37.12571428571429</v>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>1|12|15|36|40|49|9</t>
+          <t>11|12|22|37|42|49|43</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-06-05 14:20:01</t>
+          <t>2026-06-06 11:13:24</t>
         </is>
       </c>
     </row>
@@ -1243,25 +1243,25 @@
         <v>7</v>
       </c>
       <c r="H9" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="I9" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J9" t="n">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="K9" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="L9" t="n">
         <v>41</v>
       </c>
       <c r="M9" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="N9" t="n">
-        <v>43</v>
+        <v>20</v>
       </c>
       <c r="O9" t="n">
         <v>159</v>
@@ -1297,16 +1297,16 @@
         <v>5</v>
       </c>
       <c r="Z9" t="n">
-        <v>36.6</v>
+        <v>36.59</v>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>5|8|27|32|41|46|43</t>
+          <t>8|9|16|36|41|49|20</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-06-05 14:20:01</t>
+          <t>2026-06-06 11:13:24</t>
         </is>
       </c>
     </row>
@@ -1337,28 +1337,28 @@
         <v>8</v>
       </c>
       <c r="H10" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I10" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J10" t="n">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="K10" t="n">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="L10" t="n">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="M10" t="n">
         <v>49</v>
       </c>
       <c r="N10" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="O10" t="n">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="P10" t="n">
         <v>3</v>
@@ -1367,7 +1367,7 @@
         <v>3</v>
       </c>
       <c r="R10" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1391,16 +1391,16 @@
         <v>5</v>
       </c>
       <c r="Z10" t="n">
-        <v>36.18333333333334</v>
+        <v>36.17333333333333</v>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>8|11|15|36|42|49|28</t>
+          <t>6|12|26|31|35|49|25</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-06-05 14:20:01</t>
+          <t>2026-06-06 11:13:24</t>
         </is>
       </c>
     </row>
@@ -1431,28 +1431,28 @@
         <v>9</v>
       </c>
       <c r="H11" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I11" t="n">
+        <v>13</v>
+      </c>
+      <c r="J11" t="n">
         <v>15</v>
-      </c>
-      <c r="J11" t="n">
-        <v>27</v>
       </c>
       <c r="K11" t="n">
         <v>32</v>
       </c>
       <c r="L11" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="M11" t="n">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="N11" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="O11" t="n">
-        <v>167</v>
+        <v>147</v>
       </c>
       <c r="P11" t="n">
         <v>3</v>
@@ -1461,7 +1461,7 @@
         <v>3</v>
       </c>
       <c r="R11" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1485,16 +1485,16 @@
         <v>5</v>
       </c>
       <c r="Z11" t="n">
-        <v>35.85</v>
+        <v>35.84</v>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>8|15|27|32|36|49|12</t>
+          <t>6|13|15|32|35|46|17</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-06-05 14:20:01</t>
+          <t>2026-06-06 11:13:24</t>
         </is>
       </c>
     </row>
@@ -1525,28 +1525,28 @@
         <v>10</v>
       </c>
       <c r="H12" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="I12" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J12" t="n">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="K12" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="L12" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="M12" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="N12" t="n">
-        <v>15</v>
+        <v>43</v>
       </c>
       <c r="O12" t="n">
-        <v>151</v>
+        <v>165</v>
       </c>
       <c r="P12" t="n">
         <v>3</v>
@@ -1555,7 +1555,7 @@
         <v>3</v>
       </c>
       <c r="R12" t="n">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1579,16 +1579,16 @@
         <v>5</v>
       </c>
       <c r="Z12" t="n">
-        <v>35.57727272727273</v>
+        <v>35.56727272727272</v>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>3|7|21|32|40|48|15</t>
+          <t>9|10|29|35|36|46|43</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-06-05 14:20:01</t>
+          <t>2026-06-06 11:13:24</t>
         </is>
       </c>
     </row>

--- a/data/exports/final_predictions/lotto_ensemble_predictions.xlsx
+++ b/data/exports/final_predictions/lotto_ensemble_predictions.xlsx
@@ -603,7 +603,7 @@
         <v>56</v>
       </c>
       <c r="N2" t="n">
-        <v>47</v>
+        <v>22</v>
       </c>
       <c r="O2" t="n">
         <v>206</v>
@@ -639,16 +639,16 @@
         <v>8</v>
       </c>
       <c r="Z2" t="n">
-        <v>73.84</v>
+        <v>73.75</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2|4|44|49|51|56|47</t>
+          <t>2|4|44|49|51|56|22</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-06-06 11:13:24</t>
+          <t>2026-06-07 11:31:48</t>
         </is>
       </c>
     </row>
@@ -679,28 +679,28 @@
         <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="I3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J3" t="n">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="K3" t="n">
         <v>32</v>
       </c>
       <c r="L3" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="M3" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="N3" t="n">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="O3" t="n">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="P3" t="n">
         <v>3</v>
@@ -709,7 +709,7 @@
         <v>3</v>
       </c>
       <c r="R3" t="n">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -733,16 +733,16 @@
         <v>5</v>
       </c>
       <c r="Z3" t="n">
-        <v>47.84</v>
+        <v>47.75</v>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>1|11|27|32|38|48|46</t>
+          <t>9|12|15|32|41|46|23</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-06-06 11:13:24</t>
+          <t>2026-06-07 11:31:48</t>
         </is>
       </c>
     </row>
@@ -773,28 +773,28 @@
         <v>2</v>
       </c>
       <c r="H4" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="I4" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="J4" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="K4" t="n">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="L4" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="M4" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="N4" t="n">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="O4" t="n">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="P4" t="n">
         <v>3</v>
@@ -803,7 +803,7 @@
         <v>3</v>
       </c>
       <c r="R4" t="n">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -827,16 +827,16 @@
         <v>5</v>
       </c>
       <c r="Z4" t="n">
-        <v>42.84</v>
+        <v>42.75</v>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>3|9|23|30|44|48|37</t>
+          <t>11|12|20|39|40|45|28</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-06-06 11:13:24</t>
+          <t>2026-06-07 11:31:48</t>
         </is>
       </c>
     </row>
@@ -867,28 +867,28 @@
         <v>3</v>
       </c>
       <c r="H5" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="I5" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="J5" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="K5" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="L5" t="n">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="M5" t="n">
         <v>46</v>
       </c>
       <c r="N5" t="n">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="O5" t="n">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="P5" t="n">
         <v>3</v>
@@ -897,7 +897,7 @@
         <v>3</v>
       </c>
       <c r="R5" t="n">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -921,16 +921,16 @@
         <v>5</v>
       </c>
       <c r="Z5" t="n">
-        <v>40.34</v>
+        <v>40.25</v>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>9|13|21|32|36|46|11</t>
+          <t>4|8|17|35|43|46|24</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-06-06 11:13:24</t>
+          <t>2026-06-07 11:31:48</t>
         </is>
       </c>
     </row>
@@ -961,28 +961,28 @@
         <v>4</v>
       </c>
       <c r="H6" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="I6" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="J6" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="K6" t="n">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="L6" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="M6" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="N6" t="n">
-        <v>38</v>
+        <v>10</v>
       </c>
       <c r="O6" t="n">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="P6" t="n">
         <v>3</v>
@@ -991,7 +991,7 @@
         <v>3</v>
       </c>
       <c r="R6" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1015,16 +1015,16 @@
         <v>5</v>
       </c>
       <c r="Z6" t="n">
-        <v>38.84</v>
+        <v>38.75</v>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>5|8|24|43|44|45|38</t>
+          <t>8|11|22|33|42|49|10</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-06-06 11:13:24</t>
+          <t>2026-06-07 11:31:48</t>
         </is>
       </c>
     </row>
@@ -1058,16 +1058,16 @@
         <v>8</v>
       </c>
       <c r="I7" t="n">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="J7" t="n">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="K7" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="L7" t="n">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="M7" t="n">
         <v>45</v>
@@ -1076,7 +1076,7 @@
         <v>18</v>
       </c>
       <c r="O7" t="n">
-        <v>157</v>
+        <v>173</v>
       </c>
       <c r="P7" t="n">
         <v>3</v>
@@ -1109,16 +1109,16 @@
         <v>5</v>
       </c>
       <c r="Z7" t="n">
-        <v>37.84</v>
+        <v>37.75</v>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>8|12|15|38|39|45|18</t>
+          <t>8|27|28|32|33|45|18</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-06-06 11:13:24</t>
+          <t>2026-06-07 11:31:48</t>
         </is>
       </c>
     </row>
@@ -1149,25 +1149,25 @@
         <v>6</v>
       </c>
       <c r="H8" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="I8" t="n">
         <v>12</v>
       </c>
       <c r="J8" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="K8" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="L8" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="M8" t="n">
         <v>49</v>
       </c>
       <c r="N8" t="n">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="O8" t="n">
         <v>173</v>
@@ -1179,7 +1179,7 @@
         <v>3</v>
       </c>
       <c r="R8" t="n">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1203,16 +1203,16 @@
         <v>5</v>
       </c>
       <c r="Z8" t="n">
-        <v>37.12571428571429</v>
+        <v>37.03571428571428</v>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>11|12|22|37|42|49|43</t>
+          <t>1|12|28|40|43|49|51</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-06-06 11:13:24</t>
+          <t>2026-06-07 11:31:48</t>
         </is>
       </c>
     </row>
@@ -1243,28 +1243,28 @@
         <v>7</v>
       </c>
       <c r="H9" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I9" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J9" t="n">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="K9" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="L9" t="n">
         <v>41</v>
       </c>
       <c r="M9" t="n">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="N9" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="O9" t="n">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="P9" t="n">
         <v>3</v>
@@ -1273,7 +1273,7 @@
         <v>3</v>
       </c>
       <c r="R9" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1297,16 +1297,16 @@
         <v>5</v>
       </c>
       <c r="Z9" t="n">
-        <v>36.59</v>
+        <v>36.5</v>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>8|9|16|36|41|49|20</t>
+          <t>7|10|29|32|41|46|16</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-06-06 11:13:24</t>
+          <t>2026-06-07 11:31:48</t>
         </is>
       </c>
     </row>
@@ -1337,28 +1337,28 @@
         <v>8</v>
       </c>
       <c r="H10" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I10" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="J10" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="K10" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="L10" t="n">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="M10" t="n">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="N10" t="n">
         <v>25</v>
       </c>
       <c r="O10" t="n">
-        <v>159</v>
+        <v>171</v>
       </c>
       <c r="P10" t="n">
         <v>3</v>
@@ -1367,7 +1367,7 @@
         <v>3</v>
       </c>
       <c r="R10" t="n">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1391,16 +1391,16 @@
         <v>5</v>
       </c>
       <c r="Z10" t="n">
-        <v>36.17333333333333</v>
+        <v>36.08333333333333</v>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>6|12|26|31|35|49|25</t>
+          <t>8|18|24|33|43|45|25</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-06-06 11:13:24</t>
+          <t>2026-06-07 11:31:48</t>
         </is>
       </c>
     </row>
@@ -1431,25 +1431,25 @@
         <v>9</v>
       </c>
       <c r="H11" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I11" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="J11" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="K11" t="n">
         <v>32</v>
       </c>
       <c r="L11" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="M11" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="N11" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="O11" t="n">
         <v>147</v>
@@ -1485,16 +1485,16 @@
         <v>5</v>
       </c>
       <c r="Z11" t="n">
-        <v>35.84</v>
+        <v>35.75</v>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>6|13|15|32|35|46|17</t>
+          <t>7|8|17|32|36|47|1</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-06-06 11:13:24</t>
+          <t>2026-06-07 11:31:48</t>
         </is>
       </c>
     </row>
@@ -1525,28 +1525,28 @@
         <v>10</v>
       </c>
       <c r="H12" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="I12" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="J12" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="K12" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="L12" t="n">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="M12" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="N12" t="n">
-        <v>43</v>
+        <v>20</v>
       </c>
       <c r="O12" t="n">
-        <v>165</v>
+        <v>151</v>
       </c>
       <c r="P12" t="n">
         <v>3</v>
@@ -1555,7 +1555,7 @@
         <v>3</v>
       </c>
       <c r="R12" t="n">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1579,16 +1579,16 @@
         <v>5</v>
       </c>
       <c r="Z12" t="n">
-        <v>35.56727272727272</v>
+        <v>35.47727272727273</v>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>9|10|29|35|36|46|43</t>
+          <t>2|6|23|30|41|49|20</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-06-06 11:13:24</t>
+          <t>2026-06-07 11:31:48</t>
         </is>
       </c>
     </row>

--- a/data/exports/final_predictions/lotto_ensemble_predictions.xlsx
+++ b/data/exports/final_predictions/lotto_ensemble_predictions.xlsx
@@ -648,7 +648,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-06-07 11:31:48</t>
+          <t>2026-06-08 17:07:05</t>
         </is>
       </c>
     </row>
@@ -742,7 +742,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-06-07 11:31:48</t>
+          <t>2026-06-08 17:07:05</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-06-07 11:31:48</t>
+          <t>2026-06-08 17:07:05</t>
         </is>
       </c>
     </row>
@@ -930,7 +930,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-06-07 11:31:48</t>
+          <t>2026-06-08 17:07:05</t>
         </is>
       </c>
     </row>
@@ -1024,7 +1024,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-06-07 11:31:48</t>
+          <t>2026-06-08 17:07:05</t>
         </is>
       </c>
     </row>
@@ -1118,7 +1118,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-06-07 11:31:48</t>
+          <t>2026-06-08 17:07:05</t>
         </is>
       </c>
     </row>
@@ -1212,7 +1212,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-06-07 11:31:48</t>
+          <t>2026-06-08 17:07:05</t>
         </is>
       </c>
     </row>
@@ -1306,7 +1306,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-06-07 11:31:48</t>
+          <t>2026-06-08 17:07:05</t>
         </is>
       </c>
     </row>
@@ -1400,7 +1400,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-06-07 11:31:48</t>
+          <t>2026-06-08 17:07:05</t>
         </is>
       </c>
     </row>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-06-07 11:31:48</t>
+          <t>2026-06-08 17:07:05</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-06-07 11:31:48</t>
+          <t>2026-06-08 17:07:05</t>
         </is>
       </c>
     </row>

--- a/data/exports/final_predictions/lotto_ensemble_predictions.xlsx
+++ b/data/exports/final_predictions/lotto_ensemble_predictions.xlsx
@@ -648,7 +648,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-06-08 17:07:05</t>
+          <t>2026-06-09 14:12:28</t>
         </is>
       </c>
     </row>
@@ -742,7 +742,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-06-08 17:07:05</t>
+          <t>2026-06-09 14:12:28</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-06-08 17:07:05</t>
+          <t>2026-06-09 14:12:28</t>
         </is>
       </c>
     </row>
@@ -930,7 +930,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-06-08 17:07:05</t>
+          <t>2026-06-09 14:12:28</t>
         </is>
       </c>
     </row>
@@ -1024,7 +1024,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-06-08 17:07:05</t>
+          <t>2026-06-09 14:12:28</t>
         </is>
       </c>
     </row>
@@ -1118,7 +1118,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-06-08 17:07:05</t>
+          <t>2026-06-09 14:12:28</t>
         </is>
       </c>
     </row>
@@ -1212,7 +1212,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-06-08 17:07:05</t>
+          <t>2026-06-09 14:12:28</t>
         </is>
       </c>
     </row>
@@ -1306,7 +1306,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-06-08 17:07:05</t>
+          <t>2026-06-09 14:12:28</t>
         </is>
       </c>
     </row>
@@ -1400,7 +1400,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-06-08 17:07:05</t>
+          <t>2026-06-09 14:12:28</t>
         </is>
       </c>
     </row>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-06-08 17:07:05</t>
+          <t>2026-06-09 14:12:28</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-06-08 17:07:05</t>
+          <t>2026-06-09 14:12:28</t>
         </is>
       </c>
     </row>

--- a/data/exports/final_predictions/lotto_ensemble_predictions.xlsx
+++ b/data/exports/final_predictions/lotto_ensemble_predictions.xlsx
@@ -648,7 +648,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-06-09 14:12:28</t>
+          <t>2026-06-10 16:59:53</t>
         </is>
       </c>
     </row>
@@ -742,7 +742,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-06-09 14:12:28</t>
+          <t>2026-06-10 16:59:53</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-06-09 14:12:28</t>
+          <t>2026-06-10 16:59:53</t>
         </is>
       </c>
     </row>
@@ -930,7 +930,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-06-09 14:12:28</t>
+          <t>2026-06-10 16:59:53</t>
         </is>
       </c>
     </row>
@@ -1024,7 +1024,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-06-09 14:12:28</t>
+          <t>2026-06-10 16:59:53</t>
         </is>
       </c>
     </row>
@@ -1118,7 +1118,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-06-09 14:12:28</t>
+          <t>2026-06-10 16:59:53</t>
         </is>
       </c>
     </row>
@@ -1212,7 +1212,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-06-09 14:12:28</t>
+          <t>2026-06-10 16:59:53</t>
         </is>
       </c>
     </row>
@@ -1306,7 +1306,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-06-09 14:12:28</t>
+          <t>2026-06-10 16:59:53</t>
         </is>
       </c>
     </row>
@@ -1400,7 +1400,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-06-09 14:12:28</t>
+          <t>2026-06-10 16:59:53</t>
         </is>
       </c>
     </row>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-06-09 14:12:28</t>
+          <t>2026-06-10 16:59:53</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-06-09 14:12:28</t>
+          <t>2026-06-10 16:59:53</t>
         </is>
       </c>
     </row>

--- a/data/exports/final_predictions/lotto_ensemble_predictions.xlsx
+++ b/data/exports/final_predictions/lotto_ensemble_predictions.xlsx
@@ -585,7 +585,7 @@
         <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I2" t="n">
         <v>4</v>
@@ -597,13 +597,13 @@
         <v>49</v>
       </c>
       <c r="L2" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="M2" t="n">
         <v>56</v>
       </c>
       <c r="N2" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="O2" t="n">
         <v>206</v>
@@ -615,7 +615,7 @@
         <v>4</v>
       </c>
       <c r="R2" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -639,16 +639,16 @@
         <v>8</v>
       </c>
       <c r="Z2" t="n">
-        <v>73.75</v>
+        <v>73.84999999999999</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2|4|44|49|51|56|22</t>
+          <t>1|4|44|49|52|56|14</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-06-10 16:59:53</t>
+          <t>2026-06-11 17:59:21</t>
         </is>
       </c>
     </row>
@@ -679,28 +679,28 @@
         <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="I3" t="n">
         <v>12</v>
       </c>
       <c r="J3" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="K3" t="n">
         <v>32</v>
       </c>
       <c r="L3" t="n">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="M3" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="N3" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="O3" t="n">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="P3" t="n">
         <v>3</v>
@@ -709,7 +709,7 @@
         <v>3</v>
       </c>
       <c r="R3" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -733,16 +733,16 @@
         <v>5</v>
       </c>
       <c r="Z3" t="n">
-        <v>47.75</v>
+        <v>47.85</v>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>9|12|15|32|41|46|23</t>
+          <t>11|12|22|32|37|49|21</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-06-10 16:59:53</t>
+          <t>2026-06-11 17:59:21</t>
         </is>
       </c>
     </row>
@@ -773,28 +773,28 @@
         <v>2</v>
       </c>
       <c r="H4" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="I4" t="n">
         <v>12</v>
       </c>
       <c r="J4" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="K4" t="n">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="L4" t="n">
         <v>40</v>
       </c>
       <c r="M4" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="N4" t="n">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="O4" t="n">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="P4" t="n">
         <v>3</v>
@@ -803,7 +803,7 @@
         <v>3</v>
       </c>
       <c r="R4" t="n">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -827,16 +827,16 @@
         <v>5</v>
       </c>
       <c r="Z4" t="n">
-        <v>42.75</v>
+        <v>42.85</v>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>11|12|20|39|40|45|28</t>
+          <t>7|12|23|33|40|48|42</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-06-10 16:59:53</t>
+          <t>2026-06-11 17:59:21</t>
         </is>
       </c>
     </row>
@@ -867,28 +867,28 @@
         <v>3</v>
       </c>
       <c r="H5" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="I5" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="J5" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K5" t="n">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="L5" t="n">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="M5" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="N5" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="O5" t="n">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="P5" t="n">
         <v>3</v>
@@ -897,7 +897,7 @@
         <v>3</v>
       </c>
       <c r="R5" t="n">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -921,16 +921,16 @@
         <v>5</v>
       </c>
       <c r="Z5" t="n">
-        <v>40.25</v>
+        <v>40.35</v>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>4|8|17|35|43|46|24</t>
+          <t>8|13|18|32|39|47|16</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-06-10 16:59:53</t>
+          <t>2026-06-11 17:59:21</t>
         </is>
       </c>
     </row>
@@ -961,28 +961,28 @@
         <v>4</v>
       </c>
       <c r="H6" t="n">
+        <v>2</v>
+      </c>
+      <c r="I6" t="n">
         <v>8</v>
       </c>
-      <c r="I6" t="n">
-        <v>11</v>
-      </c>
       <c r="J6" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K6" t="n">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="L6" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="M6" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="N6" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="O6" t="n">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="P6" t="n">
         <v>3</v>
@@ -991,7 +991,7 @@
         <v>3</v>
       </c>
       <c r="R6" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1015,16 +1015,16 @@
         <v>5</v>
       </c>
       <c r="Z6" t="n">
-        <v>38.75</v>
+        <v>38.85</v>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>8|11|22|33|42|49|10</t>
+          <t>2|8|23|38|43|47|16</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-06-10 16:59:53</t>
+          <t>2026-06-11 17:59:21</t>
         </is>
       </c>
     </row>
@@ -1055,28 +1055,28 @@
         <v>5</v>
       </c>
       <c r="H7" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I7" t="n">
+        <v>11</v>
+      </c>
+      <c r="J7" t="n">
+        <v>20</v>
+      </c>
+      <c r="K7" t="n">
+        <v>40</v>
+      </c>
+      <c r="L7" t="n">
+        <v>44</v>
+      </c>
+      <c r="M7" t="n">
+        <v>47</v>
+      </c>
+      <c r="N7" t="n">
         <v>27</v>
       </c>
-      <c r="J7" t="n">
-        <v>28</v>
-      </c>
-      <c r="K7" t="n">
-        <v>32</v>
-      </c>
-      <c r="L7" t="n">
-        <v>33</v>
-      </c>
-      <c r="M7" t="n">
-        <v>45</v>
-      </c>
-      <c r="N7" t="n">
-        <v>18</v>
-      </c>
       <c r="O7" t="n">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="P7" t="n">
         <v>3</v>
@@ -1085,7 +1085,7 @@
         <v>3</v>
       </c>
       <c r="R7" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1109,16 +1109,16 @@
         <v>5</v>
       </c>
       <c r="Z7" t="n">
-        <v>37.75</v>
+        <v>37.85</v>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>8|27|28|32|33|45|18</t>
+          <t>7|11|20|40|44|47|27</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-06-10 16:59:53</t>
+          <t>2026-06-11 17:59:21</t>
         </is>
       </c>
     </row>
@@ -1155,22 +1155,22 @@
         <v>12</v>
       </c>
       <c r="J8" t="n">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="K8" t="n">
+        <v>36</v>
+      </c>
+      <c r="L8" t="n">
         <v>40</v>
-      </c>
-      <c r="L8" t="n">
-        <v>43</v>
       </c>
       <c r="M8" t="n">
         <v>49</v>
       </c>
       <c r="N8" t="n">
-        <v>51</v>
+        <v>9</v>
       </c>
       <c r="O8" t="n">
-        <v>173</v>
+        <v>153</v>
       </c>
       <c r="P8" t="n">
         <v>3</v>
@@ -1203,16 +1203,16 @@
         <v>5</v>
       </c>
       <c r="Z8" t="n">
-        <v>37.03571428571428</v>
+        <v>37.13571428571429</v>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>1|12|28|40|43|49|51</t>
+          <t>1|12|15|36|40|49|9</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-06-10 16:59:53</t>
+          <t>2026-06-11 17:59:21</t>
         </is>
       </c>
     </row>
@@ -1243,13 +1243,13 @@
         <v>7</v>
       </c>
       <c r="H9" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I9" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J9" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="K9" t="n">
         <v>32</v>
@@ -1261,10 +1261,10 @@
         <v>46</v>
       </c>
       <c r="N9" t="n">
-        <v>16</v>
+        <v>43</v>
       </c>
       <c r="O9" t="n">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="P9" t="n">
         <v>3</v>
@@ -1273,7 +1273,7 @@
         <v>3</v>
       </c>
       <c r="R9" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1297,16 +1297,16 @@
         <v>5</v>
       </c>
       <c r="Z9" t="n">
-        <v>36.5</v>
+        <v>36.6</v>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>7|10|29|32|41|46|16</t>
+          <t>5|8|27|32|41|46|43</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-06-10 16:59:53</t>
+          <t>2026-06-11 17:59:21</t>
         </is>
       </c>
     </row>
@@ -1340,25 +1340,25 @@
         <v>8</v>
       </c>
       <c r="I10" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="J10" t="n">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="K10" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="L10" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="M10" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="N10" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="O10" t="n">
-        <v>171</v>
+        <v>161</v>
       </c>
       <c r="P10" t="n">
         <v>3</v>
@@ -1367,7 +1367,7 @@
         <v>3</v>
       </c>
       <c r="R10" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1391,16 +1391,16 @@
         <v>5</v>
       </c>
       <c r="Z10" t="n">
-        <v>36.08333333333333</v>
+        <v>36.18333333333334</v>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>8|18|24|33|43|45|25</t>
+          <t>8|11|15|36|42|49|28</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-06-10 16:59:53</t>
+          <t>2026-06-11 17:59:21</t>
         </is>
       </c>
     </row>
@@ -1431,13 +1431,13 @@
         <v>9</v>
       </c>
       <c r="H11" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I11" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="J11" t="n">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="K11" t="n">
         <v>32</v>
@@ -1446,13 +1446,13 @@
         <v>36</v>
       </c>
       <c r="M11" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="N11" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="O11" t="n">
-        <v>147</v>
+        <v>167</v>
       </c>
       <c r="P11" t="n">
         <v>3</v>
@@ -1461,7 +1461,7 @@
         <v>3</v>
       </c>
       <c r="R11" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1485,16 +1485,16 @@
         <v>5</v>
       </c>
       <c r="Z11" t="n">
-        <v>35.75</v>
+        <v>35.85</v>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>7|8|17|32|36|47|1</t>
+          <t>8|15|27|32|36|49|12</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-06-10 16:59:53</t>
+          <t>2026-06-11 17:59:21</t>
         </is>
       </c>
     </row>
@@ -1525,25 +1525,25 @@
         <v>10</v>
       </c>
       <c r="H12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J12" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="K12" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="L12" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="M12" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="N12" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="O12" t="n">
         <v>151</v>
@@ -1555,7 +1555,7 @@
         <v>3</v>
       </c>
       <c r="R12" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1579,16 +1579,16 @@
         <v>5</v>
       </c>
       <c r="Z12" t="n">
-        <v>35.47727272727273</v>
+        <v>35.57727272727273</v>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2|6|23|30|41|49|20</t>
+          <t>3|7|21|32|40|48|15</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-06-10 16:59:53</t>
+          <t>2026-06-11 17:59:21</t>
         </is>
       </c>
     </row>

--- a/data/exports/final_predictions/lotto_ensemble_predictions.xlsx
+++ b/data/exports/final_predictions/lotto_ensemble_predictions.xlsx
@@ -585,7 +585,7 @@
         <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I2" t="n">
         <v>4</v>
@@ -597,13 +597,13 @@
         <v>49</v>
       </c>
       <c r="L2" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="M2" t="n">
         <v>56</v>
       </c>
       <c r="N2" t="n">
-        <v>14</v>
+        <v>47</v>
       </c>
       <c r="O2" t="n">
         <v>206</v>
@@ -615,7 +615,7 @@
         <v>4</v>
       </c>
       <c r="R2" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -639,16 +639,16 @@
         <v>8</v>
       </c>
       <c r="Z2" t="n">
-        <v>73.84999999999999</v>
+        <v>73.79000000000001</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1|4|44|49|52|56|14</t>
+          <t>2|4|44|49|51|56|47</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-06-11 17:59:21</t>
+          <t>2026-06-12 14:35:03</t>
         </is>
       </c>
     </row>
@@ -679,7 +679,7 @@
         <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="I3" t="n">
         <v>12</v>
@@ -688,19 +688,19 @@
         <v>22</v>
       </c>
       <c r="K3" t="n">
+        <v>31</v>
+      </c>
+      <c r="L3" t="n">
         <v>32</v>
-      </c>
-      <c r="L3" t="n">
-        <v>37</v>
       </c>
       <c r="M3" t="n">
         <v>49</v>
       </c>
       <c r="N3" t="n">
-        <v>21</v>
+        <v>38</v>
       </c>
       <c r="O3" t="n">
-        <v>163</v>
+        <v>155</v>
       </c>
       <c r="P3" t="n">
         <v>3</v>
@@ -709,7 +709,7 @@
         <v>3</v>
       </c>
       <c r="R3" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -733,16 +733,16 @@
         <v>5</v>
       </c>
       <c r="Z3" t="n">
-        <v>47.85</v>
+        <v>47.79</v>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>11|12|22|32|37|49|21</t>
+          <t>9|12|22|31|32|49|38</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-06-11 17:59:21</t>
+          <t>2026-06-12 14:35:03</t>
         </is>
       </c>
     </row>
@@ -773,25 +773,25 @@
         <v>2</v>
       </c>
       <c r="H4" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="I4" t="n">
         <v>12</v>
       </c>
       <c r="J4" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="K4" t="n">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="L4" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="M4" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="N4" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="O4" t="n">
         <v>163</v>
@@ -803,7 +803,7 @@
         <v>3</v>
       </c>
       <c r="R4" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -827,16 +827,16 @@
         <v>5</v>
       </c>
       <c r="Z4" t="n">
-        <v>42.85</v>
+        <v>42.79</v>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>7|12|23|33|40|48|42</t>
+          <t>4|12|17|40|41|49|43</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-06-11 17:59:21</t>
+          <t>2026-06-12 14:35:03</t>
         </is>
       </c>
     </row>
@@ -867,28 +867,28 @@
         <v>3</v>
       </c>
       <c r="H5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I5" t="n">
         <v>13</v>
       </c>
       <c r="J5" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="K5" t="n">
         <v>32</v>
       </c>
       <c r="L5" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="M5" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="N5" t="n">
-        <v>16</v>
+        <v>54</v>
       </c>
       <c r="O5" t="n">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="P5" t="n">
         <v>3</v>
@@ -897,7 +897,7 @@
         <v>3</v>
       </c>
       <c r="R5" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -921,16 +921,16 @@
         <v>5</v>
       </c>
       <c r="Z5" t="n">
-        <v>40.35</v>
+        <v>40.29</v>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>8|13|18|32|39|47|16</t>
+          <t>9|13|22|32|37|46|54</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-06-11 17:59:21</t>
+          <t>2026-06-12 14:35:03</t>
         </is>
       </c>
     </row>
@@ -961,28 +961,28 @@
         <v>4</v>
       </c>
       <c r="H6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I6" t="n">
         <v>8</v>
       </c>
       <c r="J6" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="K6" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L6" t="n">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="M6" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="N6" t="n">
-        <v>16</v>
+        <v>42</v>
       </c>
       <c r="O6" t="n">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="P6" t="n">
         <v>3</v>
@@ -991,7 +991,7 @@
         <v>3</v>
       </c>
       <c r="R6" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1015,16 +1015,16 @@
         <v>5</v>
       </c>
       <c r="Z6" t="n">
-        <v>38.85</v>
+        <v>38.79</v>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2|8|23|38|43|47|16</t>
+          <t>1|8|26|39|40|45|42</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-06-11 17:59:21</t>
+          <t>2026-06-12 14:35:03</t>
         </is>
       </c>
     </row>
@@ -1055,28 +1055,28 @@
         <v>5</v>
       </c>
       <c r="H7" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="I7" t="n">
+        <v>12</v>
+      </c>
+      <c r="J7" t="n">
+        <v>16</v>
+      </c>
+      <c r="K7" t="n">
+        <v>41</v>
+      </c>
+      <c r="L7" t="n">
+        <v>43</v>
+      </c>
+      <c r="M7" t="n">
+        <v>49</v>
+      </c>
+      <c r="N7" t="n">
         <v>11</v>
       </c>
-      <c r="J7" t="n">
-        <v>20</v>
-      </c>
-      <c r="K7" t="n">
-        <v>40</v>
-      </c>
-      <c r="L7" t="n">
-        <v>44</v>
-      </c>
-      <c r="M7" t="n">
-        <v>47</v>
-      </c>
-      <c r="N7" t="n">
-        <v>27</v>
-      </c>
       <c r="O7" t="n">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="P7" t="n">
         <v>3</v>
@@ -1085,7 +1085,7 @@
         <v>3</v>
       </c>
       <c r="R7" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1109,16 +1109,16 @@
         <v>5</v>
       </c>
       <c r="Z7" t="n">
-        <v>37.85</v>
+        <v>37.79</v>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>7|11|20|40|44|47|27</t>
+          <t>4|12|16|41|43|49|11</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-06-11 17:59:21</t>
+          <t>2026-06-12 14:35:03</t>
         </is>
       </c>
     </row>
@@ -1149,28 +1149,28 @@
         <v>6</v>
       </c>
       <c r="H8" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="I8" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J8" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="K8" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="L8" t="n">
         <v>40</v>
       </c>
       <c r="M8" t="n">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="N8" t="n">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="O8" t="n">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="P8" t="n">
         <v>3</v>
@@ -1179,7 +1179,7 @@
         <v>3</v>
       </c>
       <c r="R8" t="n">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1203,16 +1203,16 @@
         <v>5</v>
       </c>
       <c r="Z8" t="n">
-        <v>37.13571428571429</v>
+        <v>37.07571428571428</v>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>1|12|15|36|40|49|9</t>
+          <t>8|11|23|30|40|45|33</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-06-11 17:59:21</t>
+          <t>2026-06-12 14:35:03</t>
         </is>
       </c>
     </row>
@@ -1243,28 +1243,28 @@
         <v>7</v>
       </c>
       <c r="H9" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I9" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="J9" t="n">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="K9" t="n">
         <v>32</v>
       </c>
       <c r="L9" t="n">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="M9" t="n">
         <v>46</v>
       </c>
       <c r="N9" t="n">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="O9" t="n">
-        <v>159</v>
+        <v>143</v>
       </c>
       <c r="P9" t="n">
         <v>3</v>
@@ -1273,7 +1273,7 @@
         <v>3</v>
       </c>
       <c r="R9" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1297,16 +1297,16 @@
         <v>5</v>
       </c>
       <c r="Z9" t="n">
-        <v>36.6</v>
+        <v>36.54</v>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>5|8|27|32|41|46|43</t>
+          <t>1|13|15|32|36|46|52</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-06-11 17:59:21</t>
+          <t>2026-06-12 14:35:03</t>
         </is>
       </c>
     </row>
@@ -1340,25 +1340,25 @@
         <v>8</v>
       </c>
       <c r="I10" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J10" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="K10" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="L10" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="M10" t="n">
         <v>49</v>
       </c>
       <c r="N10" t="n">
-        <v>28</v>
+        <v>5</v>
       </c>
       <c r="O10" t="n">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="P10" t="n">
         <v>3</v>
@@ -1391,16 +1391,16 @@
         <v>5</v>
       </c>
       <c r="Z10" t="n">
-        <v>36.18333333333334</v>
+        <v>36.12333333333333</v>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>8|11|15|36|42|49|28</t>
+          <t>8|12|17|38|43|49|5</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-06-11 17:59:21</t>
+          <t>2026-06-12 14:35:03</t>
         </is>
       </c>
     </row>
@@ -1431,28 +1431,28 @@
         <v>9</v>
       </c>
       <c r="H11" t="n">
+        <v>4</v>
+      </c>
+      <c r="I11" t="n">
         <v>8</v>
       </c>
-      <c r="I11" t="n">
-        <v>15</v>
-      </c>
       <c r="J11" t="n">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="K11" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="L11" t="n">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="M11" t="n">
         <v>49</v>
       </c>
       <c r="N11" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="O11" t="n">
-        <v>167</v>
+        <v>155</v>
       </c>
       <c r="P11" t="n">
         <v>3</v>
@@ -1461,7 +1461,7 @@
         <v>3</v>
       </c>
       <c r="R11" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1485,16 +1485,16 @@
         <v>5</v>
       </c>
       <c r="Z11" t="n">
-        <v>35.85</v>
+        <v>35.79</v>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>8|15|27|32|36|49|12</t>
+          <t>4|8|17|36|41|49|3</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-06-11 17:59:21</t>
+          <t>2026-06-12 14:35:03</t>
         </is>
       </c>
     </row>
@@ -1525,28 +1525,28 @@
         <v>10</v>
       </c>
       <c r="H12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J12" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="K12" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="L12" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="M12" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="N12" t="n">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="O12" t="n">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="P12" t="n">
         <v>3</v>
@@ -1555,7 +1555,7 @@
         <v>3</v>
       </c>
       <c r="R12" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1579,16 +1579,16 @@
         <v>5</v>
       </c>
       <c r="Z12" t="n">
-        <v>35.57727272727273</v>
+        <v>35.51727272727273</v>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>3|7|21|32|40|48|15</t>
+          <t>2|8|27|31|38|49|26</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-06-11 17:59:21</t>
+          <t>2026-06-12 14:35:03</t>
         </is>
       </c>
     </row>

--- a/data/exports/final_predictions/lotto_ensemble_predictions.xlsx
+++ b/data/exports/final_predictions/lotto_ensemble_predictions.xlsx
@@ -648,7 +648,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-06-12 14:35:03</t>
+          <t>2026-06-13 11:44:13</t>
         </is>
       </c>
     </row>
@@ -742,7 +742,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-06-12 14:35:03</t>
+          <t>2026-06-13 11:44:13</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-06-12 14:35:03</t>
+          <t>2026-06-13 11:44:13</t>
         </is>
       </c>
     </row>
@@ -930,7 +930,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-06-12 14:35:03</t>
+          <t>2026-06-13 11:44:13</t>
         </is>
       </c>
     </row>
@@ -1024,7 +1024,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-06-12 14:35:03</t>
+          <t>2026-06-13 11:44:13</t>
         </is>
       </c>
     </row>
@@ -1118,7 +1118,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-06-12 14:35:03</t>
+          <t>2026-06-13 11:44:13</t>
         </is>
       </c>
     </row>
@@ -1212,7 +1212,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-06-12 14:35:03</t>
+          <t>2026-06-13 11:44:13</t>
         </is>
       </c>
     </row>
@@ -1306,7 +1306,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-06-12 14:35:03</t>
+          <t>2026-06-13 11:44:13</t>
         </is>
       </c>
     </row>
@@ -1400,7 +1400,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-06-12 14:35:03</t>
+          <t>2026-06-13 11:44:13</t>
         </is>
       </c>
     </row>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-06-12 14:35:03</t>
+          <t>2026-06-13 11:44:13</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-06-12 14:35:03</t>
+          <t>2026-06-13 11:44:13</t>
         </is>
       </c>
     </row>

--- a/data/exports/final_predictions/lotto_ensemble_predictions.xlsx
+++ b/data/exports/final_predictions/lotto_ensemble_predictions.xlsx
@@ -639,7 +639,7 @@
         <v>8</v>
       </c>
       <c r="Z2" t="n">
-        <v>73.79000000000001</v>
+        <v>73.81999999999999</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
@@ -648,7 +648,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-06-13 11:44:13</t>
+          <t>2026-06-14 11:58:04</t>
         </is>
       </c>
     </row>
@@ -679,28 +679,28 @@
         <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="I3" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="J3" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="K3" t="n">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="L3" t="n">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="M3" t="n">
         <v>49</v>
       </c>
       <c r="N3" t="n">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="O3" t="n">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="P3" t="n">
         <v>3</v>
@@ -709,7 +709,7 @@
         <v>3</v>
       </c>
       <c r="R3" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -733,16 +733,16 @@
         <v>5</v>
       </c>
       <c r="Z3" t="n">
-        <v>47.79</v>
+        <v>47.82</v>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>9|12|22|31|32|49|38</t>
+          <t>4|8|15|40|43|49|27</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-06-13 11:44:13</t>
+          <t>2026-06-14 11:58:04</t>
         </is>
       </c>
     </row>
@@ -773,37 +773,37 @@
         <v>2</v>
       </c>
       <c r="H4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J4" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="K4" t="n">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="L4" t="n">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="M4" t="n">
         <v>49</v>
       </c>
       <c r="N4" t="n">
+        <v>58</v>
+      </c>
+      <c r="O4" t="n">
+        <v>151</v>
+      </c>
+      <c r="P4" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>3</v>
+      </c>
+      <c r="R4" t="n">
         <v>43</v>
-      </c>
-      <c r="O4" t="n">
-        <v>163</v>
-      </c>
-      <c r="P4" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>3</v>
-      </c>
-      <c r="R4" t="n">
-        <v>45</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -827,16 +827,16 @@
         <v>5</v>
       </c>
       <c r="Z4" t="n">
-        <v>42.79</v>
+        <v>42.82</v>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>4|12|17|40|41|49|43</t>
+          <t>6|13|15|32|36|49|58</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-06-13 11:44:13</t>
+          <t>2026-06-14 11:58:04</t>
         </is>
       </c>
     </row>
@@ -867,10 +867,10 @@
         <v>3</v>
       </c>
       <c r="H5" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="I5" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="J5" t="n">
         <v>22</v>
@@ -879,16 +879,16 @@
         <v>32</v>
       </c>
       <c r="L5" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="M5" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="N5" t="n">
-        <v>54</v>
+        <v>34</v>
       </c>
       <c r="O5" t="n">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="P5" t="n">
         <v>3</v>
@@ -897,7 +897,7 @@
         <v>3</v>
       </c>
       <c r="R5" t="n">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -921,16 +921,16 @@
         <v>5</v>
       </c>
       <c r="Z5" t="n">
-        <v>40.29</v>
+        <v>40.32</v>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>9|13|22|32|37|46|54</t>
+          <t>1|8|22|32|41|49|34</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-06-13 11:44:13</t>
+          <t>2026-06-14 11:58:04</t>
         </is>
       </c>
     </row>
@@ -961,28 +961,28 @@
         <v>4</v>
       </c>
       <c r="H6" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="I6" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="J6" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K6" t="n">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="L6" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="M6" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="N6" t="n">
-        <v>42</v>
+        <v>9</v>
       </c>
       <c r="O6" t="n">
-        <v>159</v>
+        <v>175</v>
       </c>
       <c r="P6" t="n">
         <v>3</v>
@@ -991,7 +991,7 @@
         <v>3</v>
       </c>
       <c r="R6" t="n">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1015,16 +1015,16 @@
         <v>5</v>
       </c>
       <c r="Z6" t="n">
-        <v>38.79</v>
+        <v>38.82</v>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>1|8|26|39|40|45|42</t>
+          <t>11|12|27|34|44|47|9</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-06-13 11:44:13</t>
+          <t>2026-06-14 11:58:04</t>
         </is>
       </c>
     </row>
@@ -1055,25 +1055,25 @@
         <v>5</v>
       </c>
       <c r="H7" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I7" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J7" t="n">
         <v>16</v>
       </c>
       <c r="K7" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="L7" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="M7" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="N7" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="O7" t="n">
         <v>165</v>
@@ -1085,7 +1085,7 @@
         <v>3</v>
       </c>
       <c r="R7" t="n">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1109,16 +1109,16 @@
         <v>5</v>
       </c>
       <c r="Z7" t="n">
-        <v>37.79</v>
+        <v>37.82</v>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>4|12|16|41|43|49|11</t>
+          <t>7|11|16|39|44|48|17</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-06-13 11:44:13</t>
+          <t>2026-06-14 11:58:04</t>
         </is>
       </c>
     </row>
@@ -1149,28 +1149,28 @@
         <v>6</v>
       </c>
       <c r="H8" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I8" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="J8" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="K8" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="L8" t="n">
         <v>40</v>
       </c>
       <c r="M8" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="N8" t="n">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="O8" t="n">
-        <v>157</v>
+        <v>175</v>
       </c>
       <c r="P8" t="n">
         <v>3</v>
@@ -1179,7 +1179,7 @@
         <v>3</v>
       </c>
       <c r="R8" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1203,16 +1203,16 @@
         <v>5</v>
       </c>
       <c r="Z8" t="n">
-        <v>37.07571428571428</v>
+        <v>37.10571428571428</v>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>8|11|23|30|40|45|33</t>
+          <t>10|17|27|33|40|48|8</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-06-13 11:44:13</t>
+          <t>2026-06-14 11:58:04</t>
         </is>
       </c>
     </row>
@@ -1246,25 +1246,25 @@
         <v>1</v>
       </c>
       <c r="I9" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="J9" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="K9" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="L9" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="M9" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="N9" t="n">
-        <v>52</v>
+        <v>34</v>
       </c>
       <c r="O9" t="n">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="P9" t="n">
         <v>3</v>
@@ -1273,7 +1273,7 @@
         <v>3</v>
       </c>
       <c r="R9" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1297,16 +1297,16 @@
         <v>5</v>
       </c>
       <c r="Z9" t="n">
-        <v>36.54</v>
+        <v>36.57</v>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>1|13|15|32|36|46|52</t>
+          <t>1|11|21|30|40|48|34</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-06-13 11:44:13</t>
+          <t>2026-06-14 11:58:04</t>
         </is>
       </c>
     </row>
@@ -1337,28 +1337,28 @@
         <v>8</v>
       </c>
       <c r="H10" t="n">
+        <v>9</v>
+      </c>
+      <c r="I10" t="n">
+        <v>11</v>
+      </c>
+      <c r="J10" t="n">
+        <v>26</v>
+      </c>
+      <c r="K10" t="n">
+        <v>30</v>
+      </c>
+      <c r="L10" t="n">
+        <v>33</v>
+      </c>
+      <c r="M10" t="n">
+        <v>46</v>
+      </c>
+      <c r="N10" t="n">
         <v>8</v>
       </c>
-      <c r="I10" t="n">
-        <v>12</v>
-      </c>
-      <c r="J10" t="n">
-        <v>17</v>
-      </c>
-      <c r="K10" t="n">
-        <v>38</v>
-      </c>
-      <c r="L10" t="n">
-        <v>43</v>
-      </c>
-      <c r="M10" t="n">
-        <v>49</v>
-      </c>
-      <c r="N10" t="n">
-        <v>5</v>
-      </c>
       <c r="O10" t="n">
-        <v>167</v>
+        <v>155</v>
       </c>
       <c r="P10" t="n">
         <v>3</v>
@@ -1367,7 +1367,7 @@
         <v>3</v>
       </c>
       <c r="R10" t="n">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1391,16 +1391,16 @@
         <v>5</v>
       </c>
       <c r="Z10" t="n">
-        <v>36.12333333333333</v>
+        <v>36.15333333333334</v>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>8|12|17|38|43|49|5</t>
+          <t>9|11|26|30|33|46|8</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-06-13 11:44:13</t>
+          <t>2026-06-14 11:58:04</t>
         </is>
       </c>
     </row>
@@ -1431,28 +1431,28 @@
         <v>9</v>
       </c>
       <c r="H11" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="I11" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="J11" t="n">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="K11" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="L11" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="M11" t="n">
         <v>49</v>
       </c>
       <c r="N11" t="n">
-        <v>3</v>
+        <v>31</v>
       </c>
       <c r="O11" t="n">
-        <v>155</v>
+        <v>171</v>
       </c>
       <c r="P11" t="n">
         <v>3</v>
@@ -1461,7 +1461,7 @@
         <v>3</v>
       </c>
       <c r="R11" t="n">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1485,16 +1485,16 @@
         <v>5</v>
       </c>
       <c r="Z11" t="n">
-        <v>35.79</v>
+        <v>35.82</v>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>4|8|17|36|41|49|3</t>
+          <t>8|16|27|32|39|49|31</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-06-13 11:44:13</t>
+          <t>2026-06-14 11:58:04</t>
         </is>
       </c>
     </row>
@@ -1525,37 +1525,37 @@
         <v>10</v>
       </c>
       <c r="H12" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="I12" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="J12" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="K12" t="n">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="L12" t="n">
+        <v>43</v>
+      </c>
+      <c r="M12" t="n">
+        <v>46</v>
+      </c>
+      <c r="N12" t="n">
+        <v>28</v>
+      </c>
+      <c r="O12" t="n">
+        <v>171</v>
+      </c>
+      <c r="P12" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>3</v>
+      </c>
+      <c r="R12" t="n">
         <v>38</v>
-      </c>
-      <c r="M12" t="n">
-        <v>49</v>
-      </c>
-      <c r="N12" t="n">
-        <v>26</v>
-      </c>
-      <c r="O12" t="n">
-        <v>155</v>
-      </c>
-      <c r="P12" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>3</v>
-      </c>
-      <c r="R12" t="n">
-        <v>47</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1579,16 +1579,16 @@
         <v>5</v>
       </c>
       <c r="Z12" t="n">
-        <v>35.51727272727273</v>
+        <v>35.54727272727273</v>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2|8|27|31|38|49|26</t>
+          <t>8|13|22|39|43|46|28</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-06-13 11:44:13</t>
+          <t>2026-06-14 11:58:04</t>
         </is>
       </c>
     </row>

--- a/data/exports/final_predictions/lotto_ensemble_predictions.xlsx
+++ b/data/exports/final_predictions/lotto_ensemble_predictions.xlsx
@@ -648,7 +648,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-06-14 11:58:04</t>
+          <t>2026-06-15 19:21:13</t>
         </is>
       </c>
     </row>
@@ -742,7 +742,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-06-14 11:58:04</t>
+          <t>2026-06-15 19:21:13</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-06-14 11:58:04</t>
+          <t>2026-06-15 19:21:13</t>
         </is>
       </c>
     </row>
@@ -930,7 +930,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-06-14 11:58:04</t>
+          <t>2026-06-15 19:21:13</t>
         </is>
       </c>
     </row>
@@ -1024,7 +1024,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-06-14 11:58:04</t>
+          <t>2026-06-15 19:21:13</t>
         </is>
       </c>
     </row>
@@ -1118,7 +1118,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-06-14 11:58:04</t>
+          <t>2026-06-15 19:21:13</t>
         </is>
       </c>
     </row>
@@ -1212,7 +1212,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-06-14 11:58:04</t>
+          <t>2026-06-15 19:21:13</t>
         </is>
       </c>
     </row>
@@ -1306,7 +1306,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-06-14 11:58:04</t>
+          <t>2026-06-15 19:21:13</t>
         </is>
       </c>
     </row>
@@ -1400,7 +1400,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-06-14 11:58:04</t>
+          <t>2026-06-15 19:21:13</t>
         </is>
       </c>
     </row>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-06-14 11:58:04</t>
+          <t>2026-06-15 19:21:13</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-06-14 11:58:04</t>
+          <t>2026-06-15 19:21:13</t>
         </is>
       </c>
     </row>

--- a/data/exports/final_predictions/lotto_ensemble_predictions.xlsx
+++ b/data/exports/final_predictions/lotto_ensemble_predictions.xlsx
@@ -648,7 +648,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-06-15 19:21:13</t>
+          <t>2026-06-16 19:09:06</t>
         </is>
       </c>
     </row>
@@ -742,7 +742,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-06-15 19:21:13</t>
+          <t>2026-06-16 19:09:06</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-06-15 19:21:13</t>
+          <t>2026-06-16 19:09:06</t>
         </is>
       </c>
     </row>
@@ -930,7 +930,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-06-15 19:21:13</t>
+          <t>2026-06-16 19:09:06</t>
         </is>
       </c>
     </row>
@@ -1024,7 +1024,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-06-15 19:21:13</t>
+          <t>2026-06-16 19:09:06</t>
         </is>
       </c>
     </row>
@@ -1118,7 +1118,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-06-15 19:21:13</t>
+          <t>2026-06-16 19:09:06</t>
         </is>
       </c>
     </row>
@@ -1212,7 +1212,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-06-15 19:21:13</t>
+          <t>2026-06-16 19:09:06</t>
         </is>
       </c>
     </row>
@@ -1306,7 +1306,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-06-15 19:21:13</t>
+          <t>2026-06-16 19:09:06</t>
         </is>
       </c>
     </row>
@@ -1400,7 +1400,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-06-15 19:21:13</t>
+          <t>2026-06-16 19:09:06</t>
         </is>
       </c>
     </row>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-06-15 19:21:13</t>
+          <t>2026-06-16 19:09:06</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-06-15 19:21:13</t>
+          <t>2026-06-16 19:09:06</t>
         </is>
       </c>
     </row>

--- a/data/exports/final_predictions/lotto_ensemble_predictions.xlsx
+++ b/data/exports/final_predictions/lotto_ensemble_predictions.xlsx
@@ -648,7 +648,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-06-16 19:09:06</t>
+          <t>2026-06-17 16:58:04</t>
         </is>
       </c>
     </row>
@@ -742,7 +742,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-06-16 19:09:06</t>
+          <t>2026-06-17 16:58:04</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-06-16 19:09:06</t>
+          <t>2026-06-17 16:58:04</t>
         </is>
       </c>
     </row>
@@ -930,7 +930,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-06-16 19:09:06</t>
+          <t>2026-06-17 16:58:04</t>
         </is>
       </c>
     </row>
@@ -1024,7 +1024,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-06-16 19:09:06</t>
+          <t>2026-06-17 16:58:04</t>
         </is>
       </c>
     </row>
@@ -1118,7 +1118,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-06-16 19:09:06</t>
+          <t>2026-06-17 16:58:04</t>
         </is>
       </c>
     </row>
@@ -1212,7 +1212,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-06-16 19:09:06</t>
+          <t>2026-06-17 16:58:04</t>
         </is>
       </c>
     </row>
@@ -1306,7 +1306,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-06-16 19:09:06</t>
+          <t>2026-06-17 16:58:04</t>
         </is>
       </c>
     </row>
@@ -1400,7 +1400,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-06-16 19:09:06</t>
+          <t>2026-06-17 16:58:04</t>
         </is>
       </c>
     </row>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-06-16 19:09:06</t>
+          <t>2026-06-17 16:58:04</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-06-16 19:09:06</t>
+          <t>2026-06-17 16:58:04</t>
         </is>
       </c>
     </row>

--- a/data/exports/final_predictions/lotto_ensemble_predictions.xlsx
+++ b/data/exports/final_predictions/lotto_ensemble_predictions.xlsx
@@ -585,10 +585,10 @@
         <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I2" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="J2" t="n">
         <v>44</v>
@@ -603,10 +603,10 @@
         <v>56</v>
       </c>
       <c r="N2" t="n">
-        <v>47</v>
+        <v>20</v>
       </c>
       <c r="O2" t="n">
-        <v>206</v>
+        <v>214</v>
       </c>
       <c r="P2" t="n">
         <v>2</v>
@@ -615,7 +615,7 @@
         <v>4</v>
       </c>
       <c r="R2" t="n">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -639,16 +639,16 @@
         <v>8</v>
       </c>
       <c r="Z2" t="n">
-        <v>73.81999999999999</v>
+        <v>73.84999999999999</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2|4|44|49|51|56|47</t>
+          <t>6|8|44|49|51|56|20</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-06-17 16:58:04</t>
+          <t>2026-06-18 16:59:40</t>
         </is>
       </c>
     </row>
@@ -679,28 +679,28 @@
         <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I3" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="J3" t="n">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="K3" t="n">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="L3" t="n">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="M3" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="N3" t="n">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="O3" t="n">
-        <v>159</v>
+        <v>169</v>
       </c>
       <c r="P3" t="n">
         <v>3</v>
@@ -709,7 +709,7 @@
         <v>3</v>
       </c>
       <c r="R3" t="n">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -733,16 +733,16 @@
         <v>5</v>
       </c>
       <c r="Z3" t="n">
-        <v>47.82</v>
+        <v>47.85</v>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>4|8|15|40|43|49|27</t>
+          <t>6|12|29|35|39|48|11</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-06-17 16:58:04</t>
+          <t>2026-06-18 16:59:40</t>
         </is>
       </c>
     </row>
@@ -773,28 +773,28 @@
         <v>2</v>
       </c>
       <c r="H4" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I4" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="J4" t="n">
         <v>15</v>
       </c>
       <c r="K4" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="L4" t="n">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="M4" t="n">
         <v>49</v>
       </c>
       <c r="N4" t="n">
-        <v>58</v>
+        <v>26</v>
       </c>
       <c r="O4" t="n">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="P4" t="n">
         <v>3</v>
@@ -803,7 +803,7 @@
         <v>3</v>
       </c>
       <c r="R4" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -827,16 +827,16 @@
         <v>5</v>
       </c>
       <c r="Z4" t="n">
-        <v>42.82</v>
+        <v>42.85</v>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>6|13|15|32|36|49|58</t>
+          <t>4|8|15|40|43|49|26</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-06-17 16:58:04</t>
+          <t>2026-06-18 16:59:40</t>
         </is>
       </c>
     </row>
@@ -867,28 +867,28 @@
         <v>3</v>
       </c>
       <c r="H5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I5" t="n">
         <v>8</v>
       </c>
       <c r="J5" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="K5" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="L5" t="n">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="M5" t="n">
         <v>49</v>
       </c>
       <c r="N5" t="n">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="O5" t="n">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="P5" t="n">
         <v>3</v>
@@ -897,7 +897,7 @@
         <v>3</v>
       </c>
       <c r="R5" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -921,16 +921,16 @@
         <v>5</v>
       </c>
       <c r="Z5" t="n">
-        <v>40.32</v>
+        <v>40.35</v>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>1|8|22|32|41|49|34</t>
+          <t>4|8|16|33|37|49|10</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-06-17 16:58:04</t>
+          <t>2026-06-18 16:59:40</t>
         </is>
       </c>
     </row>
@@ -961,28 +961,28 @@
         <v>4</v>
       </c>
       <c r="H6" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="I6" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J6" t="n">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="K6" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="L6" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="M6" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="N6" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="O6" t="n">
-        <v>175</v>
+        <v>157</v>
       </c>
       <c r="P6" t="n">
         <v>3</v>
@@ -991,7 +991,7 @@
         <v>3</v>
       </c>
       <c r="R6" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1015,16 +1015,16 @@
         <v>5</v>
       </c>
       <c r="Z6" t="n">
-        <v>38.82</v>
+        <v>38.85</v>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>11|12|27|34|44|47|9</t>
+          <t>9|13|15|32|40|48|8</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-06-17 16:58:04</t>
+          <t>2026-06-18 16:59:40</t>
         </is>
       </c>
     </row>
@@ -1055,28 +1055,28 @@
         <v>5</v>
       </c>
       <c r="H7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I7" t="n">
         <v>11</v>
       </c>
       <c r="J7" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="K7" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="L7" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="M7" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="N7" t="n">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="O7" t="n">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="P7" t="n">
         <v>3</v>
@@ -1109,16 +1109,16 @@
         <v>5</v>
       </c>
       <c r="Z7" t="n">
-        <v>37.82</v>
+        <v>37.85</v>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>7|11|16|39|44|48|17</t>
+          <t>8|11|24|36|43|49|34</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-06-17 16:58:04</t>
+          <t>2026-06-18 16:59:40</t>
         </is>
       </c>
     </row>
@@ -1149,28 +1149,28 @@
         <v>6</v>
       </c>
       <c r="H8" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I8" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="J8" t="n">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="K8" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="L8" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="M8" t="n">
         <v>48</v>
       </c>
       <c r="N8" t="n">
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="O8" t="n">
-        <v>175</v>
+        <v>163</v>
       </c>
       <c r="P8" t="n">
         <v>3</v>
@@ -1179,7 +1179,7 @@
         <v>3</v>
       </c>
       <c r="R8" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1203,16 +1203,16 @@
         <v>5</v>
       </c>
       <c r="Z8" t="n">
-        <v>37.10571428571428</v>
+        <v>37.13571428571429</v>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>10|17|27|33|40|48|8</t>
+          <t>12|13|19|32|39|48|31</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-06-17 16:58:04</t>
+          <t>2026-06-18 16:59:40</t>
         </is>
       </c>
     </row>
@@ -1243,28 +1243,28 @@
         <v>7</v>
       </c>
       <c r="H9" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="I9" t="n">
         <v>11</v>
       </c>
       <c r="J9" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="K9" t="n">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="L9" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="M9" t="n">
         <v>48</v>
       </c>
       <c r="N9" t="n">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="O9" t="n">
-        <v>151</v>
+        <v>165</v>
       </c>
       <c r="P9" t="n">
         <v>3</v>
@@ -1273,7 +1273,7 @@
         <v>3</v>
       </c>
       <c r="R9" t="n">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1297,16 +1297,16 @@
         <v>5</v>
       </c>
       <c r="Z9" t="n">
-        <v>36.57</v>
+        <v>36.6</v>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>1|11|21|30|40|48|34</t>
+          <t>7|11|16|39|44|48|15</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-06-17 16:58:04</t>
+          <t>2026-06-18 16:59:40</t>
         </is>
       </c>
     </row>
@@ -1337,28 +1337,28 @@
         <v>8</v>
       </c>
       <c r="H10" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I10" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="J10" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K10" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="L10" t="n">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="M10" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="N10" t="n">
         <v>8</v>
       </c>
       <c r="O10" t="n">
-        <v>155</v>
+        <v>175</v>
       </c>
       <c r="P10" t="n">
         <v>3</v>
@@ -1367,7 +1367,7 @@
         <v>3</v>
       </c>
       <c r="R10" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1391,16 +1391,16 @@
         <v>5</v>
       </c>
       <c r="Z10" t="n">
-        <v>36.15333333333334</v>
+        <v>36.18333333333334</v>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>9|11|26|30|33|46|8</t>
+          <t>10|17|27|33|40|48|8</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-06-17 16:58:04</t>
+          <t>2026-06-18 16:59:40</t>
         </is>
       </c>
     </row>
@@ -1434,22 +1434,22 @@
         <v>8</v>
       </c>
       <c r="I11" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="J11" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="K11" t="n">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="L11" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="M11" t="n">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="N11" t="n">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="O11" t="n">
         <v>171</v>
@@ -1461,7 +1461,7 @@
         <v>3</v>
       </c>
       <c r="R11" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1485,16 +1485,16 @@
         <v>5</v>
       </c>
       <c r="Z11" t="n">
-        <v>35.82</v>
+        <v>35.85</v>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>8|16|27|32|39|49|31</t>
+          <t>8|13|22|39|43|46|28</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-06-17 16:58:04</t>
+          <t>2026-06-18 16:59:40</t>
         </is>
       </c>
     </row>
@@ -1525,28 +1525,28 @@
         <v>10</v>
       </c>
       <c r="H12" t="n">
+        <v>4</v>
+      </c>
+      <c r="I12" t="n">
         <v>8</v>
       </c>
-      <c r="I12" t="n">
-        <v>13</v>
-      </c>
       <c r="J12" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="K12" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="L12" t="n">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="M12" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="N12" t="n">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="O12" t="n">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="P12" t="n">
         <v>3</v>
@@ -1555,7 +1555,7 @@
         <v>3</v>
       </c>
       <c r="R12" t="n">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1579,16 +1579,16 @@
         <v>5</v>
       </c>
       <c r="Z12" t="n">
-        <v>35.54727272727273</v>
+        <v>35.57727272727273</v>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>8|13|22|39|43|46|28</t>
+          <t>4|8|29|37|40|49|36</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-06-17 16:58:04</t>
+          <t>2026-06-18 16:59:40</t>
         </is>
       </c>
     </row>

--- a/data/exports/final_predictions/lotto_ensemble_predictions.xlsx
+++ b/data/exports/final_predictions/lotto_ensemble_predictions.xlsx
@@ -585,10 +585,10 @@
         <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="I2" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="J2" t="n">
         <v>44</v>
@@ -597,16 +597,16 @@
         <v>49</v>
       </c>
       <c r="L2" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="M2" t="n">
         <v>56</v>
       </c>
       <c r="N2" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="O2" t="n">
-        <v>214</v>
+        <v>206</v>
       </c>
       <c r="P2" t="n">
         <v>2</v>
@@ -615,7 +615,7 @@
         <v>4</v>
       </c>
       <c r="R2" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -643,12 +643,12 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>6|8|44|49|51|56|20</t>
+          <t>1|4|44|49|52|56|14</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-06-18 16:59:40</t>
+          <t>2026-06-19 14:46:37</t>
         </is>
       </c>
     </row>
@@ -679,28 +679,28 @@
         <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="I3" t="n">
         <v>12</v>
       </c>
       <c r="J3" t="n">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="K3" t="n">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="L3" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="M3" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="N3" t="n">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="O3" t="n">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="P3" t="n">
         <v>3</v>
@@ -709,7 +709,7 @@
         <v>3</v>
       </c>
       <c r="R3" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -737,12 +737,12 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>6|12|29|35|39|48|11</t>
+          <t>11|12|22|32|37|49|21</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-06-18 16:59:40</t>
+          <t>2026-06-19 14:46:37</t>
         </is>
       </c>
     </row>
@@ -773,28 +773,28 @@
         <v>2</v>
       </c>
       <c r="H4" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I4" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="J4" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="K4" t="n">
+        <v>33</v>
+      </c>
+      <c r="L4" t="n">
         <v>40</v>
       </c>
-      <c r="L4" t="n">
-        <v>43</v>
-      </c>
       <c r="M4" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="N4" t="n">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="O4" t="n">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="P4" t="n">
         <v>3</v>
@@ -803,7 +803,7 @@
         <v>3</v>
       </c>
       <c r="R4" t="n">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -831,12 +831,12 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>4|8|15|40|43|49|26</t>
+          <t>7|12|23|33|40|48|42</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-06-18 16:59:40</t>
+          <t>2026-06-19 14:46:37</t>
         </is>
       </c>
     </row>
@@ -867,28 +867,28 @@
         <v>3</v>
       </c>
       <c r="H5" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="I5" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="J5" t="n">
+        <v>18</v>
+      </c>
+      <c r="K5" t="n">
+        <v>32</v>
+      </c>
+      <c r="L5" t="n">
+        <v>39</v>
+      </c>
+      <c r="M5" t="n">
+        <v>47</v>
+      </c>
+      <c r="N5" t="n">
         <v>16</v>
       </c>
-      <c r="K5" t="n">
-        <v>33</v>
-      </c>
-      <c r="L5" t="n">
-        <v>37</v>
-      </c>
-      <c r="M5" t="n">
-        <v>49</v>
-      </c>
-      <c r="N5" t="n">
-        <v>10</v>
-      </c>
       <c r="O5" t="n">
-        <v>147</v>
+        <v>157</v>
       </c>
       <c r="P5" t="n">
         <v>3</v>
@@ -897,7 +897,7 @@
         <v>3</v>
       </c>
       <c r="R5" t="n">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -925,12 +925,12 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>4|8|16|33|37|49|10</t>
+          <t>8|13|18|32|39|47|16</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-06-18 16:59:40</t>
+          <t>2026-06-19 14:46:37</t>
         </is>
       </c>
     </row>
@@ -961,28 +961,28 @@
         <v>4</v>
       </c>
       <c r="H6" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="I6" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="J6" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="K6" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="L6" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="M6" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N6" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="O6" t="n">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="P6" t="n">
         <v>3</v>
@@ -991,7 +991,7 @@
         <v>3</v>
       </c>
       <c r="R6" t="n">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1019,12 +1019,12 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>9|13|15|32|40|48|8</t>
+          <t>2|8|23|38|43|47|16</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-06-18 16:59:40</t>
+          <t>2026-06-19 14:46:37</t>
         </is>
       </c>
     </row>
@@ -1055,28 +1055,28 @@
         <v>5</v>
       </c>
       <c r="H7" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I7" t="n">
         <v>11</v>
       </c>
       <c r="J7" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="K7" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="L7" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="M7" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="N7" t="n">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="O7" t="n">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="P7" t="n">
         <v>3</v>
@@ -1085,7 +1085,7 @@
         <v>3</v>
       </c>
       <c r="R7" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1113,12 +1113,12 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>8|11|24|36|43|49|34</t>
+          <t>7|11|20|40|44|47|27</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-06-18 16:59:40</t>
+          <t>2026-06-19 14:46:37</t>
         </is>
       </c>
     </row>
@@ -1149,37 +1149,37 @@
         <v>6</v>
       </c>
       <c r="H8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I8" t="n">
         <v>12</v>
       </c>
-      <c r="I8" t="n">
-        <v>13</v>
-      </c>
       <c r="J8" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="K8" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="L8" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="M8" t="n">
+        <v>49</v>
+      </c>
+      <c r="N8" t="n">
+        <v>9</v>
+      </c>
+      <c r="O8" t="n">
+        <v>153</v>
+      </c>
+      <c r="P8" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>3</v>
+      </c>
+      <c r="R8" t="n">
         <v>48</v>
-      </c>
-      <c r="N8" t="n">
-        <v>31</v>
-      </c>
-      <c r="O8" t="n">
-        <v>163</v>
-      </c>
-      <c r="P8" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>3</v>
-      </c>
-      <c r="R8" t="n">
-        <v>36</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1207,12 +1207,12 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>12|13|19|32|39|48|31</t>
+          <t>1|12|15|36|40|49|9</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-06-18 16:59:40</t>
+          <t>2026-06-19 14:46:37</t>
         </is>
       </c>
     </row>
@@ -1243,28 +1243,28 @@
         <v>7</v>
       </c>
       <c r="H9" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I9" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="J9" t="n">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="K9" t="n">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="L9" t="n">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="M9" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="N9" t="n">
-        <v>15</v>
+        <v>43</v>
       </c>
       <c r="O9" t="n">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="P9" t="n">
         <v>3</v>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>7|11|16|39|44|48|15</t>
+          <t>5|8|27|32|41|46|43</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-06-18 16:59:40</t>
+          <t>2026-06-19 14:46:37</t>
         </is>
       </c>
     </row>
@@ -1337,28 +1337,28 @@
         <v>8</v>
       </c>
       <c r="H10" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I10" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="J10" t="n">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="K10" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="L10" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="M10" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="N10" t="n">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="O10" t="n">
-        <v>175</v>
+        <v>161</v>
       </c>
       <c r="P10" t="n">
         <v>3</v>
@@ -1367,7 +1367,7 @@
         <v>3</v>
       </c>
       <c r="R10" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1395,12 +1395,12 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>10|17|27|33|40|48|8</t>
+          <t>8|11|15|36|42|49|28</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-06-18 16:59:40</t>
+          <t>2026-06-19 14:46:37</t>
         </is>
       </c>
     </row>
@@ -1434,25 +1434,25 @@
         <v>8</v>
       </c>
       <c r="I11" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="J11" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="K11" t="n">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="L11" t="n">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="M11" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="N11" t="n">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="O11" t="n">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="P11" t="n">
         <v>3</v>
@@ -1461,7 +1461,7 @@
         <v>3</v>
       </c>
       <c r="R11" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1489,12 +1489,12 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>8|13|22|39|43|46|28</t>
+          <t>8|15|27|32|36|49|12</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-06-18 16:59:40</t>
+          <t>2026-06-19 14:46:37</t>
         </is>
       </c>
     </row>
@@ -1525,28 +1525,28 @@
         <v>10</v>
       </c>
       <c r="H12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I12" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J12" t="n">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="K12" t="n">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="L12" t="n">
         <v>40</v>
       </c>
       <c r="M12" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="N12" t="n">
-        <v>36</v>
+        <v>15</v>
       </c>
       <c r="O12" t="n">
-        <v>167</v>
+        <v>151</v>
       </c>
       <c r="P12" t="n">
         <v>3</v>
@@ -1583,12 +1583,12 @@
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>4|8|29|37|40|49|36</t>
+          <t>3|7|21|32|40|48|15</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-06-18 16:59:40</t>
+          <t>2026-06-19 14:46:37</t>
         </is>
       </c>
     </row>

--- a/data/exports/final_predictions/lotto_ensemble_predictions.xlsx
+++ b/data/exports/final_predictions/lotto_ensemble_predictions.xlsx
@@ -585,10 +585,10 @@
         <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I2" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="J2" t="n">
         <v>44</v>
@@ -597,16 +597,16 @@
         <v>49</v>
       </c>
       <c r="L2" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="M2" t="n">
         <v>56</v>
       </c>
       <c r="N2" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="O2" t="n">
-        <v>206</v>
+        <v>214</v>
       </c>
       <c r="P2" t="n">
         <v>2</v>
@@ -615,7 +615,7 @@
         <v>4</v>
       </c>
       <c r="R2" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -643,12 +643,12 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1|4|44|49|52|56|14</t>
+          <t>6|8|44|49|51|56|20</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-06-19 14:46:37</t>
+          <t>2026-06-20 11:46:11</t>
         </is>
       </c>
     </row>
@@ -679,28 +679,28 @@
         <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="I3" t="n">
         <v>12</v>
       </c>
       <c r="J3" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="K3" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="L3" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="M3" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="N3" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="O3" t="n">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="P3" t="n">
         <v>3</v>
@@ -709,7 +709,7 @@
         <v>3</v>
       </c>
       <c r="R3" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -737,12 +737,12 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>11|12|22|32|37|49|21</t>
+          <t>6|12|29|35|39|48|11</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-06-19 14:46:37</t>
+          <t>2026-06-20 11:46:11</t>
         </is>
       </c>
     </row>
@@ -773,28 +773,28 @@
         <v>2</v>
       </c>
       <c r="H4" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="I4" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="J4" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="K4" t="n">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="L4" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="M4" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="N4" t="n">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="O4" t="n">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="P4" t="n">
         <v>3</v>
@@ -803,7 +803,7 @@
         <v>3</v>
       </c>
       <c r="R4" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -831,12 +831,12 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>7|12|23|33|40|48|42</t>
+          <t>4|8|15|40|43|49|26</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-06-19 14:46:37</t>
+          <t>2026-06-20 11:46:11</t>
         </is>
       </c>
     </row>
@@ -867,28 +867,28 @@
         <v>3</v>
       </c>
       <c r="H5" t="n">
+        <v>4</v>
+      </c>
+      <c r="I5" t="n">
         <v>8</v>
       </c>
-      <c r="I5" t="n">
-        <v>13</v>
-      </c>
       <c r="J5" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="K5" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="L5" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="M5" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="N5" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="O5" t="n">
-        <v>157</v>
+        <v>147</v>
       </c>
       <c r="P5" t="n">
         <v>3</v>
@@ -897,7 +897,7 @@
         <v>3</v>
       </c>
       <c r="R5" t="n">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -925,12 +925,12 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>8|13|18|32|39|47|16</t>
+          <t>4|8|16|33|37|49|10</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-06-19 14:46:37</t>
+          <t>2026-06-20 11:46:11</t>
         </is>
       </c>
     </row>
@@ -961,28 +961,28 @@
         <v>4</v>
       </c>
       <c r="H6" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="I6" t="n">
+        <v>13</v>
+      </c>
+      <c r="J6" t="n">
+        <v>15</v>
+      </c>
+      <c r="K6" t="n">
+        <v>32</v>
+      </c>
+      <c r="L6" t="n">
+        <v>40</v>
+      </c>
+      <c r="M6" t="n">
+        <v>48</v>
+      </c>
+      <c r="N6" t="n">
         <v>8</v>
       </c>
-      <c r="J6" t="n">
-        <v>23</v>
-      </c>
-      <c r="K6" t="n">
-        <v>38</v>
-      </c>
-      <c r="L6" t="n">
-        <v>43</v>
-      </c>
-      <c r="M6" t="n">
-        <v>47</v>
-      </c>
-      <c r="N6" t="n">
-        <v>16</v>
-      </c>
       <c r="O6" t="n">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="P6" t="n">
         <v>3</v>
@@ -991,7 +991,7 @@
         <v>3</v>
       </c>
       <c r="R6" t="n">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1019,12 +1019,12 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2|8|23|38|43|47|16</t>
+          <t>9|13|15|32|40|48|8</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-06-19 14:46:37</t>
+          <t>2026-06-20 11:46:11</t>
         </is>
       </c>
     </row>
@@ -1055,28 +1055,28 @@
         <v>5</v>
       </c>
       <c r="H7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I7" t="n">
         <v>11</v>
       </c>
       <c r="J7" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="K7" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="L7" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="M7" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="N7" t="n">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="O7" t="n">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="P7" t="n">
         <v>3</v>
@@ -1085,7 +1085,7 @@
         <v>3</v>
       </c>
       <c r="R7" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1113,12 +1113,12 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>7|11|20|40|44|47|27</t>
+          <t>8|11|24|36|43|49|34</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-06-19 14:46:37</t>
+          <t>2026-06-20 11:46:11</t>
         </is>
       </c>
     </row>
@@ -1149,37 +1149,37 @@
         <v>6</v>
       </c>
       <c r="H8" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="I8" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J8" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="K8" t="n">
+        <v>32</v>
+      </c>
+      <c r="L8" t="n">
+        <v>39</v>
+      </c>
+      <c r="M8" t="n">
+        <v>48</v>
+      </c>
+      <c r="N8" t="n">
+        <v>31</v>
+      </c>
+      <c r="O8" t="n">
+        <v>163</v>
+      </c>
+      <c r="P8" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>3</v>
+      </c>
+      <c r="R8" t="n">
         <v>36</v>
-      </c>
-      <c r="L8" t="n">
-        <v>40</v>
-      </c>
-      <c r="M8" t="n">
-        <v>49</v>
-      </c>
-      <c r="N8" t="n">
-        <v>9</v>
-      </c>
-      <c r="O8" t="n">
-        <v>153</v>
-      </c>
-      <c r="P8" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>3</v>
-      </c>
-      <c r="R8" t="n">
-        <v>48</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1207,12 +1207,12 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>1|12|15|36|40|49|9</t>
+          <t>12|13|19|32|39|48|31</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-06-19 14:46:37</t>
+          <t>2026-06-20 11:46:11</t>
         </is>
       </c>
     </row>
@@ -1243,28 +1243,28 @@
         <v>7</v>
       </c>
       <c r="H9" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I9" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="J9" t="n">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="K9" t="n">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="L9" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="M9" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="N9" t="n">
-        <v>43</v>
+        <v>15</v>
       </c>
       <c r="O9" t="n">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="P9" t="n">
         <v>3</v>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>5|8|27|32|41|46|43</t>
+          <t>7|11|16|39|44|48|15</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-06-19 14:46:37</t>
+          <t>2026-06-20 11:46:11</t>
         </is>
       </c>
     </row>
@@ -1337,28 +1337,28 @@
         <v>8</v>
       </c>
       <c r="H10" t="n">
+        <v>10</v>
+      </c>
+      <c r="I10" t="n">
+        <v>17</v>
+      </c>
+      <c r="J10" t="n">
+        <v>27</v>
+      </c>
+      <c r="K10" t="n">
+        <v>33</v>
+      </c>
+      <c r="L10" t="n">
+        <v>40</v>
+      </c>
+      <c r="M10" t="n">
+        <v>48</v>
+      </c>
+      <c r="N10" t="n">
         <v>8</v>
       </c>
-      <c r="I10" t="n">
-        <v>11</v>
-      </c>
-      <c r="J10" t="n">
-        <v>15</v>
-      </c>
-      <c r="K10" t="n">
-        <v>36</v>
-      </c>
-      <c r="L10" t="n">
-        <v>42</v>
-      </c>
-      <c r="M10" t="n">
-        <v>49</v>
-      </c>
-      <c r="N10" t="n">
-        <v>28</v>
-      </c>
       <c r="O10" t="n">
-        <v>161</v>
+        <v>175</v>
       </c>
       <c r="P10" t="n">
         <v>3</v>
@@ -1367,7 +1367,7 @@
         <v>3</v>
       </c>
       <c r="R10" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1395,12 +1395,12 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>8|11|15|36|42|49|28</t>
+          <t>10|17|27|33|40|48|8</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-06-19 14:46:37</t>
+          <t>2026-06-20 11:46:11</t>
         </is>
       </c>
     </row>
@@ -1434,25 +1434,25 @@
         <v>8</v>
       </c>
       <c r="I11" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="J11" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="K11" t="n">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="L11" t="n">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="M11" t="n">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="N11" t="n">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="O11" t="n">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="P11" t="n">
         <v>3</v>
@@ -1461,7 +1461,7 @@
         <v>3</v>
       </c>
       <c r="R11" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1489,12 +1489,12 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>8|15|27|32|36|49|12</t>
+          <t>8|13|22|39|43|46|28</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-06-19 14:46:37</t>
+          <t>2026-06-20 11:46:11</t>
         </is>
       </c>
     </row>
@@ -1525,28 +1525,28 @@
         <v>10</v>
       </c>
       <c r="H12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J12" t="n">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="K12" t="n">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="L12" t="n">
         <v>40</v>
       </c>
       <c r="M12" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="N12" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="O12" t="n">
-        <v>151</v>
+        <v>167</v>
       </c>
       <c r="P12" t="n">
         <v>3</v>
@@ -1583,12 +1583,12 @@
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>3|7|21|32|40|48|15</t>
+          <t>4|8|29|37|40|49|36</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-06-19 14:46:37</t>
+          <t>2026-06-20 11:46:11</t>
         </is>
       </c>
     </row>

--- a/data/exports/final_predictions/lotto_ensemble_predictions.xlsx
+++ b/data/exports/final_predictions/lotto_ensemble_predictions.xlsx
@@ -585,37 +585,37 @@
         <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I2" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="J2" t="n">
-        <v>44</v>
+        <v>13</v>
       </c>
       <c r="K2" t="n">
-        <v>49</v>
+        <v>15</v>
       </c>
       <c r="L2" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="M2" t="n">
         <v>56</v>
       </c>
       <c r="N2" t="n">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="O2" t="n">
-        <v>214</v>
+        <v>155</v>
       </c>
       <c r="P2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R2" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -639,16 +639,16 @@
         <v>8</v>
       </c>
       <c r="Z2" t="n">
-        <v>73.84999999999999</v>
+        <v>73.77</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>6|8|44|49|51|56|20</t>
+          <t>8|11|13|15|52|56|48</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-06-20 11:46:11</t>
+          <t>2026-06-21 12:32:28</t>
         </is>
       </c>
     </row>
@@ -679,28 +679,28 @@
         <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I3" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J3" t="n">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="K3" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="L3" t="n">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="M3" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="N3" t="n">
-        <v>11</v>
+        <v>50</v>
       </c>
       <c r="O3" t="n">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="P3" t="n">
         <v>3</v>
@@ -709,7 +709,7 @@
         <v>3</v>
       </c>
       <c r="R3" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -733,16 +733,16 @@
         <v>5</v>
       </c>
       <c r="Z3" t="n">
-        <v>47.85</v>
+        <v>47.77</v>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>6|12|29|35|39|48|11</t>
+          <t>8|11|15|40|44|49|50</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-06-20 11:46:11</t>
+          <t>2026-06-21 12:32:28</t>
         </is>
       </c>
     </row>
@@ -791,7 +791,7 @@
         <v>49</v>
       </c>
       <c r="N4" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="O4" t="n">
         <v>159</v>
@@ -827,16 +827,16 @@
         <v>5</v>
       </c>
       <c r="Z4" t="n">
-        <v>42.85</v>
+        <v>42.77</v>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>4|8|15|40|43|49|26</t>
+          <t>4|8|15|40|43|49|27</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-06-20 11:46:11</t>
+          <t>2026-06-21 12:32:28</t>
         </is>
       </c>
     </row>
@@ -870,25 +870,25 @@
         <v>4</v>
       </c>
       <c r="I5" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J5" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="K5" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="L5" t="n">
+        <v>39</v>
+      </c>
+      <c r="M5" t="n">
+        <v>46</v>
+      </c>
+      <c r="N5" t="n">
         <v>37</v>
       </c>
-      <c r="M5" t="n">
-        <v>49</v>
-      </c>
-      <c r="N5" t="n">
-        <v>10</v>
-      </c>
       <c r="O5" t="n">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="P5" t="n">
         <v>3</v>
@@ -897,7 +897,7 @@
         <v>3</v>
       </c>
       <c r="R5" t="n">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -921,16 +921,16 @@
         <v>5</v>
       </c>
       <c r="Z5" t="n">
-        <v>40.35</v>
+        <v>40.27</v>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>4|8|16|33|37|49|10</t>
+          <t>4|7|21|32|39|46|37</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-06-20 11:46:11</t>
+          <t>2026-06-21 12:32:28</t>
         </is>
       </c>
     </row>
@@ -961,16 +961,16 @@
         <v>4</v>
       </c>
       <c r="H6" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="I6" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="J6" t="n">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="K6" t="n">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="L6" t="n">
         <v>40</v>
@@ -979,10 +979,10 @@
         <v>48</v>
       </c>
       <c r="N6" t="n">
-        <v>8</v>
+        <v>34</v>
       </c>
       <c r="O6" t="n">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="P6" t="n">
         <v>3</v>
@@ -991,7 +991,7 @@
         <v>3</v>
       </c>
       <c r="R6" t="n">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1015,16 +1015,16 @@
         <v>5</v>
       </c>
       <c r="Z6" t="n">
-        <v>38.85</v>
+        <v>38.77</v>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>9|13|15|32|40|48|8</t>
+          <t>2|11|27|39|40|48|34</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-06-20 11:46:11</t>
+          <t>2026-06-21 12:32:28</t>
         </is>
       </c>
     </row>
@@ -1055,28 +1055,28 @@
         <v>5</v>
       </c>
       <c r="H7" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I7" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="J7" t="n">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="K7" t="n">
+        <v>32</v>
+      </c>
+      <c r="L7" t="n">
         <v>36</v>
-      </c>
-      <c r="L7" t="n">
-        <v>43</v>
       </c>
       <c r="M7" t="n">
         <v>49</v>
       </c>
       <c r="N7" t="n">
-        <v>34</v>
+        <v>58</v>
       </c>
       <c r="O7" t="n">
-        <v>171</v>
+        <v>151</v>
       </c>
       <c r="P7" t="n">
         <v>3</v>
@@ -1085,7 +1085,7 @@
         <v>3</v>
       </c>
       <c r="R7" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1109,16 +1109,16 @@
         <v>5</v>
       </c>
       <c r="Z7" t="n">
-        <v>37.85</v>
+        <v>37.77</v>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>8|11|24|36|43|49|34</t>
+          <t>6|13|15|32|36|49|58</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-06-20 11:46:11</t>
+          <t>2026-06-21 12:32:28</t>
         </is>
       </c>
     </row>
@@ -1149,37 +1149,37 @@
         <v>6</v>
       </c>
       <c r="H8" t="n">
+        <v>8</v>
+      </c>
+      <c r="I8" t="n">
         <v>12</v>
       </c>
-      <c r="I8" t="n">
-        <v>13</v>
-      </c>
       <c r="J8" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="K8" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="L8" t="n">
+        <v>38</v>
+      </c>
+      <c r="M8" t="n">
+        <v>47</v>
+      </c>
+      <c r="N8" t="n">
+        <v>52</v>
+      </c>
+      <c r="O8" t="n">
+        <v>155</v>
+      </c>
+      <c r="P8" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>3</v>
+      </c>
+      <c r="R8" t="n">
         <v>39</v>
-      </c>
-      <c r="M8" t="n">
-        <v>48</v>
-      </c>
-      <c r="N8" t="n">
-        <v>31</v>
-      </c>
-      <c r="O8" t="n">
-        <v>163</v>
-      </c>
-      <c r="P8" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>3</v>
-      </c>
-      <c r="R8" t="n">
-        <v>36</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1203,16 +1203,16 @@
         <v>5</v>
       </c>
       <c r="Z8" t="n">
-        <v>37.13571428571429</v>
+        <v>37.05571428571429</v>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>12|13|19|32|39|48|31</t>
+          <t>8|12|15|35|38|47|52</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-06-20 11:46:11</t>
+          <t>2026-06-21 12:32:28</t>
         </is>
       </c>
     </row>
@@ -1243,28 +1243,28 @@
         <v>7</v>
       </c>
       <c r="H9" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="I9" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="J9" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="K9" t="n">
+        <v>31</v>
+      </c>
+      <c r="L9" t="n">
+        <v>33</v>
+      </c>
+      <c r="M9" t="n">
+        <v>46</v>
+      </c>
+      <c r="N9" t="n">
         <v>39</v>
       </c>
-      <c r="L9" t="n">
-        <v>44</v>
-      </c>
-      <c r="M9" t="n">
-        <v>48</v>
-      </c>
-      <c r="N9" t="n">
-        <v>15</v>
-      </c>
       <c r="O9" t="n">
-        <v>165</v>
+        <v>143</v>
       </c>
       <c r="P9" t="n">
         <v>3</v>
@@ -1273,7 +1273,7 @@
         <v>3</v>
       </c>
       <c r="R9" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1297,16 +1297,16 @@
         <v>5</v>
       </c>
       <c r="Z9" t="n">
-        <v>36.6</v>
+        <v>36.52</v>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>7|11|16|39|44|48|15</t>
+          <t>4|8|21|31|33|46|39</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-06-20 11:46:11</t>
+          <t>2026-06-21 12:32:28</t>
         </is>
       </c>
     </row>
@@ -1337,28 +1337,28 @@
         <v>8</v>
       </c>
       <c r="H10" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="I10" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="J10" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="K10" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="L10" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="M10" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="N10" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="O10" t="n">
-        <v>175</v>
+        <v>159</v>
       </c>
       <c r="P10" t="n">
         <v>3</v>
@@ -1367,7 +1367,7 @@
         <v>3</v>
       </c>
       <c r="R10" t="n">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1391,16 +1391,16 @@
         <v>5</v>
       </c>
       <c r="Z10" t="n">
-        <v>36.18333333333334</v>
+        <v>36.10333333333333</v>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>10|17|27|33|40|48|8</t>
+          <t>4|13|25|32|36|49|16</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-06-20 11:46:11</t>
+          <t>2026-06-21 12:32:28</t>
         </is>
       </c>
     </row>
@@ -1431,28 +1431,28 @@
         <v>9</v>
       </c>
       <c r="H11" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="I11" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="J11" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="K11" t="n">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="L11" t="n">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="M11" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="N11" t="n">
-        <v>28</v>
+        <v>41</v>
       </c>
       <c r="O11" t="n">
-        <v>171</v>
+        <v>147</v>
       </c>
       <c r="P11" t="n">
         <v>3</v>
@@ -1461,7 +1461,7 @@
         <v>3</v>
       </c>
       <c r="R11" t="n">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1485,16 +1485,16 @@
         <v>5</v>
       </c>
       <c r="Z11" t="n">
-        <v>35.85</v>
+        <v>35.77</v>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>8|13|22|39|43|46|28</t>
+          <t>3|11|15|30|40|48|41</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-06-20 11:46:11</t>
+          <t>2026-06-21 12:32:28</t>
         </is>
       </c>
     </row>
@@ -1525,28 +1525,28 @@
         <v>10</v>
       </c>
       <c r="H12" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="I12" t="n">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="J12" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="K12" t="n">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="L12" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="M12" t="n">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="N12" t="n">
-        <v>36</v>
+        <v>3</v>
       </c>
       <c r="O12" t="n">
-        <v>167</v>
+        <v>177</v>
       </c>
       <c r="P12" t="n">
         <v>3</v>
@@ -1555,7 +1555,7 @@
         <v>3</v>
       </c>
       <c r="R12" t="n">
-        <v>45</v>
+        <v>33</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1579,16 +1579,16 @@
         <v>5</v>
       </c>
       <c r="Z12" t="n">
-        <v>35.57727272727273</v>
+        <v>35.49727272727273</v>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>4|8|29|37|40|49|36</t>
+          <t>13|21|24|32|41|46|3</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-06-20 11:46:11</t>
+          <t>2026-06-21 12:32:28</t>
         </is>
       </c>
     </row>

--- a/data/exports/final_predictions/lotto_ensemble_predictions.xlsx
+++ b/data/exports/final_predictions/lotto_ensemble_predictions.xlsx
@@ -648,7 +648,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-06-21 12:32:28</t>
+          <t>2026-06-22 19:06:49</t>
         </is>
       </c>
     </row>
@@ -742,7 +742,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-06-21 12:32:28</t>
+          <t>2026-06-22 19:06:49</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-06-21 12:32:28</t>
+          <t>2026-06-22 19:06:49</t>
         </is>
       </c>
     </row>
@@ -930,7 +930,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-06-21 12:32:28</t>
+          <t>2026-06-22 19:06:49</t>
         </is>
       </c>
     </row>
@@ -1024,7 +1024,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-06-21 12:32:28</t>
+          <t>2026-06-22 19:06:49</t>
         </is>
       </c>
     </row>
@@ -1118,7 +1118,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-06-21 12:32:28</t>
+          <t>2026-06-22 19:06:49</t>
         </is>
       </c>
     </row>
@@ -1212,7 +1212,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-06-21 12:32:28</t>
+          <t>2026-06-22 19:06:49</t>
         </is>
       </c>
     </row>
@@ -1306,7 +1306,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-06-21 12:32:28</t>
+          <t>2026-06-22 19:06:49</t>
         </is>
       </c>
     </row>
@@ -1400,7 +1400,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-06-21 12:32:28</t>
+          <t>2026-06-22 19:06:49</t>
         </is>
       </c>
     </row>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-06-21 12:32:28</t>
+          <t>2026-06-22 19:06:49</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-06-21 12:32:28</t>
+          <t>2026-06-22 19:06:49</t>
         </is>
       </c>
     </row>

--- a/data/exports/final_predictions/lotto_ensemble_predictions.xlsx
+++ b/data/exports/final_predictions/lotto_ensemble_predictions.xlsx
@@ -648,7 +648,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-06-22 19:06:49</t>
+          <t>2026-06-23 08:10:42</t>
         </is>
       </c>
     </row>
@@ -742,7 +742,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-06-22 19:06:49</t>
+          <t>2026-06-23 08:10:42</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-06-22 19:06:49</t>
+          <t>2026-06-23 08:10:42</t>
         </is>
       </c>
     </row>
@@ -930,7 +930,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-06-22 19:06:49</t>
+          <t>2026-06-23 08:10:42</t>
         </is>
       </c>
     </row>
@@ -1024,7 +1024,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-06-22 19:06:49</t>
+          <t>2026-06-23 08:10:42</t>
         </is>
       </c>
     </row>
@@ -1118,7 +1118,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-06-22 19:06:49</t>
+          <t>2026-06-23 08:10:42</t>
         </is>
       </c>
     </row>
@@ -1212,7 +1212,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-06-22 19:06:49</t>
+          <t>2026-06-23 08:10:42</t>
         </is>
       </c>
     </row>
@@ -1306,7 +1306,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-06-22 19:06:49</t>
+          <t>2026-06-23 08:10:42</t>
         </is>
       </c>
     </row>
@@ -1400,7 +1400,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-06-22 19:06:49</t>
+          <t>2026-06-23 08:10:42</t>
         </is>
       </c>
     </row>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-06-22 19:06:49</t>
+          <t>2026-06-23 08:10:42</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-06-22 19:06:49</t>
+          <t>2026-06-23 08:10:42</t>
         </is>
       </c>
     </row>

--- a/data/exports/final_predictions/lotto_ensemble_predictions.xlsx
+++ b/data/exports/final_predictions/lotto_ensemble_predictions.xlsx
@@ -648,7 +648,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-06-23 08:10:42</t>
+          <t>2026-06-24 08:08:34</t>
         </is>
       </c>
     </row>
@@ -742,7 +742,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-06-23 08:10:42</t>
+          <t>2026-06-24 08:08:34</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-06-23 08:10:42</t>
+          <t>2026-06-24 08:08:34</t>
         </is>
       </c>
     </row>
@@ -930,7 +930,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-06-23 08:10:42</t>
+          <t>2026-06-24 08:08:34</t>
         </is>
       </c>
     </row>
@@ -1024,7 +1024,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-06-23 08:10:42</t>
+          <t>2026-06-24 08:08:34</t>
         </is>
       </c>
     </row>
@@ -1118,7 +1118,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-06-23 08:10:42</t>
+          <t>2026-06-24 08:08:34</t>
         </is>
       </c>
     </row>
@@ -1212,7 +1212,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-06-23 08:10:42</t>
+          <t>2026-06-24 08:08:34</t>
         </is>
       </c>
     </row>
@@ -1306,7 +1306,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-06-23 08:10:42</t>
+          <t>2026-06-24 08:08:34</t>
         </is>
       </c>
     </row>
@@ -1400,7 +1400,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-06-23 08:10:42</t>
+          <t>2026-06-24 08:08:34</t>
         </is>
       </c>
     </row>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-06-23 08:10:42</t>
+          <t>2026-06-24 08:08:34</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-06-23 08:10:42</t>
+          <t>2026-06-24 08:08:34</t>
         </is>
       </c>
     </row>

--- a/data/exports/final_predictions/lotto_ensemble_predictions.xlsx
+++ b/data/exports/final_predictions/lotto_ensemble_predictions.xlsx
@@ -585,37 +585,37 @@
         <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="I2" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="J2" t="n">
-        <v>13</v>
+        <v>44</v>
       </c>
       <c r="K2" t="n">
-        <v>15</v>
+        <v>49</v>
       </c>
       <c r="L2" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="M2" t="n">
         <v>56</v>
       </c>
       <c r="N2" t="n">
-        <v>48</v>
+        <v>22</v>
       </c>
       <c r="O2" t="n">
-        <v>155</v>
+        <v>206</v>
       </c>
       <c r="P2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R2" t="n">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -639,16 +639,16 @@
         <v>8</v>
       </c>
       <c r="Z2" t="n">
-        <v>73.77</v>
+        <v>73.8</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>8|11|13|15|52|56|48</t>
+          <t>2|4|44|49|51|56|22</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-06-24 08:08:34</t>
+          <t>2026-06-25 08:06:43</t>
         </is>
       </c>
     </row>
@@ -679,28 +679,28 @@
         <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="I3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J3" t="n">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="K3" t="n">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="L3" t="n">
         <v>44</v>
       </c>
       <c r="M3" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="N3" t="n">
-        <v>50</v>
+        <v>9</v>
       </c>
       <c r="O3" t="n">
-        <v>167</v>
+        <v>175</v>
       </c>
       <c r="P3" t="n">
         <v>3</v>
@@ -709,7 +709,7 @@
         <v>3</v>
       </c>
       <c r="R3" t="n">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -733,16 +733,16 @@
         <v>5</v>
       </c>
       <c r="Z3" t="n">
-        <v>47.77</v>
+        <v>47.8</v>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>8|11|15|40|44|49|50</t>
+          <t>11|12|27|33|44|48|9</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:08:34</t>
+          <t>2026-06-25 08:06:43</t>
         </is>
       </c>
     </row>
@@ -773,37 +773,37 @@
         <v>2</v>
       </c>
       <c r="H4" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="I4" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="J4" t="n">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="K4" t="n">
+        <v>33</v>
+      </c>
+      <c r="L4" t="n">
+        <v>37</v>
+      </c>
+      <c r="M4" t="n">
+        <v>48</v>
+      </c>
+      <c r="N4" t="n">
+        <v>43</v>
+      </c>
+      <c r="O4" t="n">
+        <v>165</v>
+      </c>
+      <c r="P4" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>3</v>
+      </c>
+      <c r="R4" t="n">
         <v>40</v>
-      </c>
-      <c r="L4" t="n">
-        <v>43</v>
-      </c>
-      <c r="M4" t="n">
-        <v>49</v>
-      </c>
-      <c r="N4" t="n">
-        <v>27</v>
-      </c>
-      <c r="O4" t="n">
-        <v>159</v>
-      </c>
-      <c r="P4" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>3</v>
-      </c>
-      <c r="R4" t="n">
-        <v>45</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -827,16 +827,16 @@
         <v>5</v>
       </c>
       <c r="Z4" t="n">
-        <v>42.77</v>
+        <v>42.8</v>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>4|8|15|40|43|49|27</t>
+          <t>8|12|27|33|37|48|43</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-06-24 08:08:34</t>
+          <t>2026-06-25 08:06:43</t>
         </is>
       </c>
     </row>
@@ -870,25 +870,25 @@
         <v>4</v>
       </c>
       <c r="I5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J5" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="K5" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="L5" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="M5" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="N5" t="n">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="O5" t="n">
-        <v>149</v>
+        <v>159</v>
       </c>
       <c r="P5" t="n">
         <v>3</v>
@@ -897,7 +897,7 @@
         <v>3</v>
       </c>
       <c r="R5" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -921,16 +921,16 @@
         <v>5</v>
       </c>
       <c r="Z5" t="n">
-        <v>40.27</v>
+        <v>40.3</v>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>4|7|21|32|39|46|37</t>
+          <t>4|8|15|40|43|49|27</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-06-24 08:08:34</t>
+          <t>2026-06-25 08:06:43</t>
         </is>
       </c>
     </row>
@@ -961,28 +961,28 @@
         <v>4</v>
       </c>
       <c r="H6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I6" t="n">
+        <v>8</v>
+      </c>
+      <c r="J6" t="n">
+        <v>16</v>
+      </c>
+      <c r="K6" t="n">
+        <v>33</v>
+      </c>
+      <c r="L6" t="n">
+        <v>36</v>
+      </c>
+      <c r="M6" t="n">
+        <v>49</v>
+      </c>
+      <c r="N6" t="n">
         <v>11</v>
       </c>
-      <c r="J6" t="n">
-        <v>27</v>
-      </c>
-      <c r="K6" t="n">
-        <v>39</v>
-      </c>
-      <c r="L6" t="n">
-        <v>40</v>
-      </c>
-      <c r="M6" t="n">
-        <v>48</v>
-      </c>
-      <c r="N6" t="n">
-        <v>34</v>
-      </c>
       <c r="O6" t="n">
-        <v>167</v>
+        <v>145</v>
       </c>
       <c r="P6" t="n">
         <v>3</v>
@@ -1015,16 +1015,16 @@
         <v>5</v>
       </c>
       <c r="Z6" t="n">
-        <v>38.77</v>
+        <v>38.8</v>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2|11|27|39|40|48|34</t>
+          <t>3|8|16|33|36|49|11</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-06-24 08:08:34</t>
+          <t>2026-06-25 08:06:43</t>
         </is>
       </c>
     </row>
@@ -1055,28 +1055,28 @@
         <v>5</v>
       </c>
       <c r="H7" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="I7" t="n">
         <v>13</v>
       </c>
       <c r="J7" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="K7" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="L7" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="M7" t="n">
         <v>49</v>
       </c>
       <c r="N7" t="n">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="O7" t="n">
-        <v>151</v>
+        <v>179</v>
       </c>
       <c r="P7" t="n">
         <v>3</v>
@@ -1085,7 +1085,7 @@
         <v>3</v>
       </c>
       <c r="R7" t="n">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1109,16 +1109,16 @@
         <v>5</v>
       </c>
       <c r="Z7" t="n">
-        <v>37.77</v>
+        <v>37.8</v>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>6|13|15|32|36|49|58</t>
+          <t>12|13|23|40|42|49|53</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-06-24 08:08:34</t>
+          <t>2026-06-25 08:06:43</t>
         </is>
       </c>
     </row>
@@ -1152,25 +1152,25 @@
         <v>8</v>
       </c>
       <c r="I8" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="J8" t="n">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="K8" t="n">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="L8" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="M8" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="N8" t="n">
-        <v>52</v>
+        <v>6</v>
       </c>
       <c r="O8" t="n">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="P8" t="n">
         <v>3</v>
@@ -1179,7 +1179,7 @@
         <v>3</v>
       </c>
       <c r="R8" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1203,16 +1203,16 @@
         <v>5</v>
       </c>
       <c r="Z8" t="n">
-        <v>37.05571428571429</v>
+        <v>37.08571428571428</v>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>8|12|15|35|38|47|52</t>
+          <t>8|16|27|31|32|49|6</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-06-24 08:08:34</t>
+          <t>2026-06-25 08:06:43</t>
         </is>
       </c>
     </row>
@@ -1249,22 +1249,22 @@
         <v>8</v>
       </c>
       <c r="J9" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="K9" t="n">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="L9" t="n">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="M9" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="N9" t="n">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="O9" t="n">
-        <v>143</v>
+        <v>161</v>
       </c>
       <c r="P9" t="n">
         <v>3</v>
@@ -1273,7 +1273,7 @@
         <v>3</v>
       </c>
       <c r="R9" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1297,16 +1297,16 @@
         <v>5</v>
       </c>
       <c r="Z9" t="n">
-        <v>36.52</v>
+        <v>36.55</v>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>4|8|21|31|33|46|39</t>
+          <t>4|8|27|36|39|47|53</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-06-24 08:08:34</t>
+          <t>2026-06-25 08:06:43</t>
         </is>
       </c>
     </row>
@@ -1340,25 +1340,25 @@
         <v>4</v>
       </c>
       <c r="I10" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="J10" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="K10" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="L10" t="n">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="M10" t="n">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="N10" t="n">
-        <v>16</v>
+        <v>39</v>
       </c>
       <c r="O10" t="n">
-        <v>159</v>
+        <v>143</v>
       </c>
       <c r="P10" t="n">
         <v>3</v>
@@ -1367,7 +1367,7 @@
         <v>3</v>
       </c>
       <c r="R10" t="n">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1391,16 +1391,16 @@
         <v>5</v>
       </c>
       <c r="Z10" t="n">
-        <v>36.10333333333333</v>
+        <v>36.13333333333333</v>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>4|13|25|32|36|49|16</t>
+          <t>4|8|21|31|33|46|39</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-06-24 08:08:34</t>
+          <t>2026-06-25 08:06:43</t>
         </is>
       </c>
     </row>
@@ -1431,28 +1431,28 @@
         <v>9</v>
       </c>
       <c r="H11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I11" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="J11" t="n">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="K11" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="L11" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="M11" t="n">
+        <v>49</v>
+      </c>
+      <c r="N11" t="n">
         <v>48</v>
       </c>
-      <c r="N11" t="n">
-        <v>41</v>
-      </c>
       <c r="O11" t="n">
-        <v>147</v>
+        <v>175</v>
       </c>
       <c r="P11" t="n">
         <v>3</v>
@@ -1461,7 +1461,7 @@
         <v>3</v>
       </c>
       <c r="R11" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1485,16 +1485,16 @@
         <v>5</v>
       </c>
       <c r="Z11" t="n">
-        <v>35.77</v>
+        <v>35.8</v>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>3|11|15|30|40|48|41</t>
+          <t>1|22|29|32|42|49|48</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-06-24 08:08:34</t>
+          <t>2026-06-25 08:06:43</t>
         </is>
       </c>
     </row>
@@ -1579,7 +1579,7 @@
         <v>5</v>
       </c>
       <c r="Z12" t="n">
-        <v>35.49727272727273</v>
+        <v>35.52727272727273</v>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-06-24 08:08:34</t>
+          <t>2026-06-25 08:06:43</t>
         </is>
       </c>
     </row>

--- a/data/exports/final_predictions/lotto_ensemble_predictions.xlsx
+++ b/data/exports/final_predictions/lotto_ensemble_predictions.xlsx
@@ -648,7 +648,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-06-25 08:06:43</t>
+          <t>2026-06-26 08:17:50</t>
         </is>
       </c>
     </row>
@@ -742,7 +742,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-06-25 08:06:43</t>
+          <t>2026-06-26 08:17:50</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-06-25 08:06:43</t>
+          <t>2026-06-26 08:17:50</t>
         </is>
       </c>
     </row>
@@ -930,7 +930,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-06-25 08:06:43</t>
+          <t>2026-06-26 08:17:50</t>
         </is>
       </c>
     </row>
@@ -1024,7 +1024,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-06-25 08:06:43</t>
+          <t>2026-06-26 08:17:50</t>
         </is>
       </c>
     </row>
@@ -1118,7 +1118,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-06-25 08:06:43</t>
+          <t>2026-06-26 08:17:50</t>
         </is>
       </c>
     </row>
@@ -1212,7 +1212,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-06-25 08:06:43</t>
+          <t>2026-06-26 08:17:50</t>
         </is>
       </c>
     </row>
@@ -1306,7 +1306,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-06-25 08:06:43</t>
+          <t>2026-06-26 08:17:50</t>
         </is>
       </c>
     </row>
@@ -1400,7 +1400,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-06-25 08:06:43</t>
+          <t>2026-06-26 08:17:50</t>
         </is>
       </c>
     </row>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-06-25 08:06:43</t>
+          <t>2026-06-26 08:17:50</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-06-25 08:06:43</t>
+          <t>2026-06-26 08:17:50</t>
         </is>
       </c>
     </row>

--- a/data/exports/final_predictions/lotto_ensemble_predictions.xlsx
+++ b/data/exports/final_predictions/lotto_ensemble_predictions.xlsx
@@ -648,7 +648,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-06-26 08:17:50</t>
+          <t>2026-06-27 07:35:27</t>
         </is>
       </c>
     </row>
@@ -742,7 +742,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-06-26 08:17:50</t>
+          <t>2026-06-27 07:35:27</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-06-26 08:17:50</t>
+          <t>2026-06-27 07:35:27</t>
         </is>
       </c>
     </row>
@@ -930,7 +930,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-06-26 08:17:50</t>
+          <t>2026-06-27 07:35:27</t>
         </is>
       </c>
     </row>
@@ -1024,7 +1024,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-06-26 08:17:50</t>
+          <t>2026-06-27 07:35:27</t>
         </is>
       </c>
     </row>
@@ -1118,7 +1118,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-06-26 08:17:50</t>
+          <t>2026-06-27 07:35:27</t>
         </is>
       </c>
     </row>
@@ -1212,7 +1212,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-06-26 08:17:50</t>
+          <t>2026-06-27 07:35:27</t>
         </is>
       </c>
     </row>
@@ -1306,7 +1306,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-06-26 08:17:50</t>
+          <t>2026-06-27 07:35:27</t>
         </is>
       </c>
     </row>
@@ -1400,7 +1400,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-06-26 08:17:50</t>
+          <t>2026-06-27 07:35:27</t>
         </is>
       </c>
     </row>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-06-26 08:17:50</t>
+          <t>2026-06-27 07:35:27</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-06-26 08:17:50</t>
+          <t>2026-06-27 07:35:27</t>
         </is>
       </c>
     </row>

--- a/data/exports/final_predictions/lotto_ensemble_predictions.xlsx
+++ b/data/exports/final_predictions/lotto_ensemble_predictions.xlsx
@@ -603,7 +603,7 @@
         <v>56</v>
       </c>
       <c r="N2" t="n">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="O2" t="n">
         <v>206</v>
@@ -639,16 +639,16 @@
         <v>8</v>
       </c>
       <c r="Z2" t="n">
-        <v>73.8</v>
+        <v>73.81</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2|4|44|49|51|56|22</t>
+          <t>2|4|44|49|51|56|10</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-06-27 07:35:27</t>
+          <t>2026-06-28 08:11:19</t>
         </is>
       </c>
     </row>
@@ -679,28 +679,28 @@
         <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="I3" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="J3" t="n">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="K3" t="n">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="L3" t="n">
         <v>44</v>
       </c>
       <c r="M3" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="N3" t="n">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="O3" t="n">
-        <v>175</v>
+        <v>161</v>
       </c>
       <c r="P3" t="n">
         <v>3</v>
@@ -709,7 +709,7 @@
         <v>3</v>
       </c>
       <c r="R3" t="n">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -733,16 +733,16 @@
         <v>5</v>
       </c>
       <c r="Z3" t="n">
-        <v>47.8</v>
+        <v>47.81</v>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>11|12|27|33|44|48|9</t>
+          <t>5|8|15|40|44|49|28</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-06-27 07:35:27</t>
+          <t>2026-06-28 08:11:19</t>
         </is>
       </c>
     </row>
@@ -773,25 +773,25 @@
         <v>2</v>
       </c>
       <c r="H4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I4" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J4" t="n">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="K4" t="n">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="L4" t="n">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="M4" t="n">
         <v>48</v>
       </c>
       <c r="N4" t="n">
-        <v>43</v>
+        <v>17</v>
       </c>
       <c r="O4" t="n">
         <v>165</v>
@@ -803,7 +803,7 @@
         <v>3</v>
       </c>
       <c r="R4" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -827,16 +827,16 @@
         <v>5</v>
       </c>
       <c r="Z4" t="n">
-        <v>42.8</v>
+        <v>42.81</v>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>8|12|27|33|37|48|43</t>
+          <t>7|11|16|39|44|48|17</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-06-27 07:35:27</t>
+          <t>2026-06-28 08:11:19</t>
         </is>
       </c>
     </row>
@@ -867,28 +867,28 @@
         <v>3</v>
       </c>
       <c r="H5" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I5" t="n">
         <v>8</v>
       </c>
       <c r="J5" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="K5" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="L5" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="M5" t="n">
         <v>49</v>
       </c>
       <c r="N5" t="n">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="O5" t="n">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="P5" t="n">
         <v>3</v>
@@ -897,7 +897,7 @@
         <v>3</v>
       </c>
       <c r="R5" t="n">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -921,16 +921,16 @@
         <v>5</v>
       </c>
       <c r="Z5" t="n">
-        <v>40.3</v>
+        <v>40.31</v>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>4|8|15|40|43|49|27</t>
+          <t>7|8|17|38|42|49|9</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-06-27 07:35:27</t>
+          <t>2026-06-28 08:11:19</t>
         </is>
       </c>
     </row>
@@ -961,28 +961,28 @@
         <v>4</v>
       </c>
       <c r="H6" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I6" t="n">
         <v>8</v>
       </c>
       <c r="J6" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="K6" t="n">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="L6" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="M6" t="n">
         <v>49</v>
       </c>
       <c r="N6" t="n">
-        <v>11</v>
+        <v>41</v>
       </c>
       <c r="O6" t="n">
-        <v>145</v>
+        <v>167</v>
       </c>
       <c r="P6" t="n">
         <v>3</v>
@@ -991,7 +991,7 @@
         <v>3</v>
       </c>
       <c r="R6" t="n">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1015,16 +1015,16 @@
         <v>5</v>
       </c>
       <c r="Z6" t="n">
-        <v>38.8</v>
+        <v>38.81</v>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>3|8|16|33|36|49|11</t>
+          <t>6|8|25|39|40|49|41</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-06-27 07:35:27</t>
+          <t>2026-06-28 08:11:19</t>
         </is>
       </c>
     </row>
@@ -1055,16 +1055,16 @@
         <v>5</v>
       </c>
       <c r="H7" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="I7" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="J7" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="K7" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="L7" t="n">
         <v>42</v>
@@ -1073,10 +1073,10 @@
         <v>49</v>
       </c>
       <c r="N7" t="n">
-        <v>53</v>
+        <v>41</v>
       </c>
       <c r="O7" t="n">
-        <v>179</v>
+        <v>169</v>
       </c>
       <c r="P7" t="n">
         <v>3</v>
@@ -1085,7 +1085,7 @@
         <v>3</v>
       </c>
       <c r="R7" t="n">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1109,16 +1109,16 @@
         <v>5</v>
       </c>
       <c r="Z7" t="n">
-        <v>37.8</v>
+        <v>37.81</v>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>12|13|23|40|42|49|53</t>
+          <t>2|11|27|38|42|49|41</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-06-27 07:35:27</t>
+          <t>2026-06-28 08:11:19</t>
         </is>
       </c>
     </row>
@@ -1149,28 +1149,28 @@
         <v>6</v>
       </c>
       <c r="H8" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="I8" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="J8" t="n">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="K8" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="L8" t="n">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="M8" t="n">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="N8" t="n">
-        <v>6</v>
+        <v>42</v>
       </c>
       <c r="O8" t="n">
-        <v>163</v>
+        <v>145</v>
       </c>
       <c r="P8" t="n">
         <v>3</v>
@@ -1179,7 +1179,7 @@
         <v>3</v>
       </c>
       <c r="R8" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1203,16 +1203,16 @@
         <v>5</v>
       </c>
       <c r="Z8" t="n">
-        <v>37.08571428571428</v>
+        <v>37.09571428571429</v>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>8|16|27|31|32|49|6</t>
+          <t>1|7|20|32|39|46|42</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-06-27 07:35:27</t>
+          <t>2026-06-28 08:11:19</t>
         </is>
       </c>
     </row>
@@ -1243,28 +1243,28 @@
         <v>7</v>
       </c>
       <c r="H9" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="I9" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="J9" t="n">
         <v>27</v>
       </c>
       <c r="K9" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="L9" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="M9" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="N9" t="n">
-        <v>53</v>
+        <v>25</v>
       </c>
       <c r="O9" t="n">
-        <v>161</v>
+        <v>171</v>
       </c>
       <c r="P9" t="n">
         <v>3</v>
@@ -1273,7 +1273,7 @@
         <v>3</v>
       </c>
       <c r="R9" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1297,16 +1297,16 @@
         <v>5</v>
       </c>
       <c r="Z9" t="n">
-        <v>36.55</v>
+        <v>36.56</v>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>4|8|27|36|39|47|53</t>
+          <t>8|18|27|32|37|49|25</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-06-27 07:35:27</t>
+          <t>2026-06-28 08:11:19</t>
         </is>
       </c>
     </row>
@@ -1337,28 +1337,28 @@
         <v>8</v>
       </c>
       <c r="H10" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="I10" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="J10" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="K10" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="L10" t="n">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="M10" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="N10" t="n">
-        <v>39</v>
+        <v>18</v>
       </c>
       <c r="O10" t="n">
-        <v>143</v>
+        <v>157</v>
       </c>
       <c r="P10" t="n">
         <v>3</v>
@@ -1367,7 +1367,7 @@
         <v>3</v>
       </c>
       <c r="R10" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1391,16 +1391,16 @@
         <v>5</v>
       </c>
       <c r="Z10" t="n">
-        <v>36.13333333333333</v>
+        <v>36.14333333333333</v>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>4|8|21|31|33|46|39</t>
+          <t>8|12|19|33|37|48|18</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-06-27 07:35:27</t>
+          <t>2026-06-28 08:11:19</t>
         </is>
       </c>
     </row>
@@ -1431,25 +1431,25 @@
         <v>9</v>
       </c>
       <c r="H11" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="I11" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="J11" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="K11" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="L11" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="M11" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="N11" t="n">
-        <v>48</v>
+        <v>2</v>
       </c>
       <c r="O11" t="n">
         <v>175</v>
@@ -1461,7 +1461,7 @@
         <v>3</v>
       </c>
       <c r="R11" t="n">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1485,16 +1485,16 @@
         <v>5</v>
       </c>
       <c r="Z11" t="n">
-        <v>35.8</v>
+        <v>35.81</v>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>1|22|29|32|42|49|48</t>
+          <t>12|14|27|31|43|48|2</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-06-27 07:35:27</t>
+          <t>2026-06-28 08:11:19</t>
         </is>
       </c>
     </row>
@@ -1525,28 +1525,28 @@
         <v>10</v>
       </c>
       <c r="H12" t="n">
+        <v>6</v>
+      </c>
+      <c r="I12" t="n">
+        <v>12</v>
+      </c>
+      <c r="J12" t="n">
+        <v>29</v>
+      </c>
+      <c r="K12" t="n">
+        <v>36</v>
+      </c>
+      <c r="L12" t="n">
+        <v>39</v>
+      </c>
+      <c r="M12" t="n">
+        <v>49</v>
+      </c>
+      <c r="N12" t="n">
         <v>13</v>
       </c>
-      <c r="I12" t="n">
-        <v>21</v>
-      </c>
-      <c r="J12" t="n">
-        <v>24</v>
-      </c>
-      <c r="K12" t="n">
-        <v>32</v>
-      </c>
-      <c r="L12" t="n">
-        <v>41</v>
-      </c>
-      <c r="M12" t="n">
-        <v>46</v>
-      </c>
-      <c r="N12" t="n">
-        <v>3</v>
-      </c>
       <c r="O12" t="n">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="P12" t="n">
         <v>3</v>
@@ -1555,7 +1555,7 @@
         <v>3</v>
       </c>
       <c r="R12" t="n">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1579,16 +1579,16 @@
         <v>5</v>
       </c>
       <c r="Z12" t="n">
-        <v>35.52727272727273</v>
+        <v>35.53727272727272</v>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>13|21|24|32|41|46|3</t>
+          <t>6|12|29|36|39|49|13</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-06-27 07:35:27</t>
+          <t>2026-06-28 08:11:19</t>
         </is>
       </c>
     </row>

--- a/data/exports/final_predictions/lotto_ensemble_predictions.xlsx
+++ b/data/exports/final_predictions/lotto_ensemble_predictions.xlsx
@@ -648,7 +648,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-06-28 08:11:19</t>
+          <t>2026-06-29 09:24:12</t>
         </is>
       </c>
     </row>
@@ -742,7 +742,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-06-28 08:11:19</t>
+          <t>2026-06-29 09:24:12</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-06-28 08:11:19</t>
+          <t>2026-06-29 09:24:12</t>
         </is>
       </c>
     </row>
@@ -930,7 +930,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-06-28 08:11:19</t>
+          <t>2026-06-29 09:24:12</t>
         </is>
       </c>
     </row>
@@ -1024,7 +1024,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-06-28 08:11:19</t>
+          <t>2026-06-29 09:24:12</t>
         </is>
       </c>
     </row>
@@ -1118,7 +1118,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-06-28 08:11:19</t>
+          <t>2026-06-29 09:24:12</t>
         </is>
       </c>
     </row>
@@ -1212,7 +1212,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-06-28 08:11:19</t>
+          <t>2026-06-29 09:24:12</t>
         </is>
       </c>
     </row>
@@ -1306,7 +1306,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-06-28 08:11:19</t>
+          <t>2026-06-29 09:24:12</t>
         </is>
       </c>
     </row>
@@ -1400,7 +1400,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-06-28 08:11:19</t>
+          <t>2026-06-29 09:24:12</t>
         </is>
       </c>
     </row>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-06-28 08:11:19</t>
+          <t>2026-06-29 09:24:12</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-06-28 08:11:19</t>
+          <t>2026-06-29 09:24:12</t>
         </is>
       </c>
     </row>

--- a/data/exports/final_predictions/lotto_ensemble_predictions.xlsx
+++ b/data/exports/final_predictions/lotto_ensemble_predictions.xlsx
@@ -585,7 +585,7 @@
         <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I2" t="n">
         <v>4</v>
@@ -597,13 +597,13 @@
         <v>49</v>
       </c>
       <c r="L2" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="M2" t="n">
         <v>56</v>
       </c>
       <c r="N2" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="O2" t="n">
         <v>206</v>
@@ -615,7 +615,7 @@
         <v>4</v>
       </c>
       <c r="R2" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -639,16 +639,16 @@
         <v>8</v>
       </c>
       <c r="Z2" t="n">
-        <v>73.81</v>
+        <v>73.84999999999999</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2|4|44|49|51|56|10</t>
+          <t>1|4|44|49|52|56|14</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-06-29 09:24:12</t>
+          <t>2026-06-30 08:14:15</t>
         </is>
       </c>
     </row>
@@ -679,28 +679,28 @@
         <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="I3" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="J3" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="K3" t="n">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="L3" t="n">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="M3" t="n">
         <v>49</v>
       </c>
       <c r="N3" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="O3" t="n">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="P3" t="n">
         <v>3</v>
@@ -709,7 +709,7 @@
         <v>3</v>
       </c>
       <c r="R3" t="n">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -733,16 +733,16 @@
         <v>5</v>
       </c>
       <c r="Z3" t="n">
-        <v>47.81</v>
+        <v>47.85</v>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>5|8|15|40|44|49|28</t>
+          <t>11|12|22|32|37|49|21</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-06-29 09:24:12</t>
+          <t>2026-06-30 08:14:15</t>
         </is>
       </c>
     </row>
@@ -776,25 +776,25 @@
         <v>7</v>
       </c>
       <c r="I4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J4" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="K4" t="n">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="L4" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="M4" t="n">
         <v>48</v>
       </c>
       <c r="N4" t="n">
-        <v>17</v>
+        <v>42</v>
       </c>
       <c r="O4" t="n">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="P4" t="n">
         <v>3</v>
@@ -827,16 +827,16 @@
         <v>5</v>
       </c>
       <c r="Z4" t="n">
-        <v>42.81</v>
+        <v>42.85</v>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>7|11|16|39|44|48|17</t>
+          <t>7|12|23|33|40|48|42</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-06-29 09:24:12</t>
+          <t>2026-06-30 08:14:15</t>
         </is>
       </c>
     </row>
@@ -867,28 +867,28 @@
         <v>3</v>
       </c>
       <c r="H5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I5" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="J5" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K5" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="L5" t="n">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="M5" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="N5" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="O5" t="n">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="P5" t="n">
         <v>3</v>
@@ -897,7 +897,7 @@
         <v>3</v>
       </c>
       <c r="R5" t="n">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -921,16 +921,16 @@
         <v>5</v>
       </c>
       <c r="Z5" t="n">
-        <v>40.31</v>
+        <v>40.35</v>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>7|8|17|38|42|49|9</t>
+          <t>8|13|18|32|39|47|16</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-06-29 09:24:12</t>
+          <t>2026-06-30 08:14:15</t>
         </is>
       </c>
     </row>
@@ -961,28 +961,28 @@
         <v>4</v>
       </c>
       <c r="H6" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I6" t="n">
         <v>8</v>
       </c>
       <c r="J6" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="K6" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="L6" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="M6" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="N6" t="n">
-        <v>41</v>
+        <v>16</v>
       </c>
       <c r="O6" t="n">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="P6" t="n">
         <v>3</v>
@@ -991,7 +991,7 @@
         <v>3</v>
       </c>
       <c r="R6" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1015,16 +1015,16 @@
         <v>5</v>
       </c>
       <c r="Z6" t="n">
-        <v>38.81</v>
+        <v>38.85</v>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>6|8|25|39|40|49|41</t>
+          <t>2|8|23|38|43|47|16</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-06-29 09:24:12</t>
+          <t>2026-06-30 08:14:15</t>
         </is>
       </c>
     </row>
@@ -1055,25 +1055,25 @@
         <v>5</v>
       </c>
       <c r="H7" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="I7" t="n">
         <v>11</v>
       </c>
       <c r="J7" t="n">
+        <v>20</v>
+      </c>
+      <c r="K7" t="n">
+        <v>40</v>
+      </c>
+      <c r="L7" t="n">
+        <v>44</v>
+      </c>
+      <c r="M7" t="n">
+        <v>47</v>
+      </c>
+      <c r="N7" t="n">
         <v>27</v>
-      </c>
-      <c r="K7" t="n">
-        <v>38</v>
-      </c>
-      <c r="L7" t="n">
-        <v>42</v>
-      </c>
-      <c r="M7" t="n">
-        <v>49</v>
-      </c>
-      <c r="N7" t="n">
-        <v>41</v>
       </c>
       <c r="O7" t="n">
         <v>169</v>
@@ -1085,7 +1085,7 @@
         <v>3</v>
       </c>
       <c r="R7" t="n">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1109,16 +1109,16 @@
         <v>5</v>
       </c>
       <c r="Z7" t="n">
-        <v>37.81</v>
+        <v>37.85</v>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2|11|27|38|42|49|41</t>
+          <t>7|11|20|40|44|47|27</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-06-29 09:24:12</t>
+          <t>2026-06-30 08:14:15</t>
         </is>
       </c>
     </row>
@@ -1152,25 +1152,25 @@
         <v>1</v>
       </c>
       <c r="I8" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="J8" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="K8" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="L8" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="M8" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="N8" t="n">
-        <v>42</v>
+        <v>9</v>
       </c>
       <c r="O8" t="n">
-        <v>145</v>
+        <v>153</v>
       </c>
       <c r="P8" t="n">
         <v>3</v>
@@ -1179,7 +1179,7 @@
         <v>3</v>
       </c>
       <c r="R8" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1203,16 +1203,16 @@
         <v>5</v>
       </c>
       <c r="Z8" t="n">
-        <v>37.09571428571429</v>
+        <v>37.13571428571429</v>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>1|7|20|32|39|46|42</t>
+          <t>1|12|15|36|40|49|9</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-06-29 09:24:12</t>
+          <t>2026-06-30 08:14:15</t>
         </is>
       </c>
     </row>
@@ -1243,10 +1243,10 @@
         <v>7</v>
       </c>
       <c r="H9" t="n">
+        <v>5</v>
+      </c>
+      <c r="I9" t="n">
         <v>8</v>
-      </c>
-      <c r="I9" t="n">
-        <v>18</v>
       </c>
       <c r="J9" t="n">
         <v>27</v>
@@ -1255,16 +1255,16 @@
         <v>32</v>
       </c>
       <c r="L9" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="M9" t="n">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="N9" t="n">
-        <v>25</v>
+        <v>43</v>
       </c>
       <c r="O9" t="n">
-        <v>171</v>
+        <v>159</v>
       </c>
       <c r="P9" t="n">
         <v>3</v>
@@ -1297,16 +1297,16 @@
         <v>5</v>
       </c>
       <c r="Z9" t="n">
-        <v>36.56</v>
+        <v>36.6</v>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>8|18|27|32|37|49|25</t>
+          <t>5|8|27|32|41|46|43</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-06-29 09:24:12</t>
+          <t>2026-06-30 08:14:15</t>
         </is>
       </c>
     </row>
@@ -1340,25 +1340,25 @@
         <v>8</v>
       </c>
       <c r="I10" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J10" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="K10" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="L10" t="n">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="M10" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="N10" t="n">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="O10" t="n">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="P10" t="n">
         <v>3</v>
@@ -1367,7 +1367,7 @@
         <v>3</v>
       </c>
       <c r="R10" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1391,16 +1391,16 @@
         <v>5</v>
       </c>
       <c r="Z10" t="n">
-        <v>36.14333333333333</v>
+        <v>36.18333333333334</v>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>8|12|19|33|37|48|18</t>
+          <t>8|11|15|36|42|49|28</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-06-29 09:24:12</t>
+          <t>2026-06-30 08:14:15</t>
         </is>
       </c>
     </row>
@@ -1431,28 +1431,28 @@
         <v>9</v>
       </c>
       <c r="H11" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="I11" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J11" t="n">
         <v>27</v>
       </c>
       <c r="K11" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="L11" t="n">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="M11" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="N11" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="O11" t="n">
-        <v>175</v>
+        <v>167</v>
       </c>
       <c r="P11" t="n">
         <v>3</v>
@@ -1461,7 +1461,7 @@
         <v>3</v>
       </c>
       <c r="R11" t="n">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1485,16 +1485,16 @@
         <v>5</v>
       </c>
       <c r="Z11" t="n">
-        <v>35.81</v>
+        <v>35.85</v>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>12|14|27|31|43|48|2</t>
+          <t>8|15|27|32|36|49|12</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-06-29 09:24:12</t>
+          <t>2026-06-30 08:14:15</t>
         </is>
       </c>
     </row>
@@ -1525,28 +1525,28 @@
         <v>10</v>
       </c>
       <c r="H12" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I12" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="J12" t="n">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="K12" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="L12" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="M12" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="N12" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="O12" t="n">
-        <v>171</v>
+        <v>151</v>
       </c>
       <c r="P12" t="n">
         <v>3</v>
@@ -1555,7 +1555,7 @@
         <v>3</v>
       </c>
       <c r="R12" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1579,16 +1579,16 @@
         <v>5</v>
       </c>
       <c r="Z12" t="n">
-        <v>35.53727272727272</v>
+        <v>35.57727272727273</v>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>6|12|29|36|39|49|13</t>
+          <t>3|7|21|32|40|48|15</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-06-29 09:24:12</t>
+          <t>2026-06-30 08:14:15</t>
         </is>
       </c>
     </row>

--- a/data/exports/final_predictions/lotto_ensemble_predictions.xlsx
+++ b/data/exports/final_predictions/lotto_ensemble_predictions.xlsx
@@ -585,7 +585,7 @@
         <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I2" t="n">
         <v>4</v>
@@ -597,13 +597,13 @@
         <v>49</v>
       </c>
       <c r="L2" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="M2" t="n">
         <v>56</v>
       </c>
       <c r="N2" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="O2" t="n">
         <v>206</v>
@@ -615,7 +615,7 @@
         <v>4</v>
       </c>
       <c r="R2" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -639,16 +639,16 @@
         <v>8</v>
       </c>
       <c r="Z2" t="n">
-        <v>73.84999999999999</v>
+        <v>73.81</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1|4|44|49|52|56|14</t>
+          <t>2|4|44|49|51|56|10</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-06-30 08:14:15</t>
+          <t>2026-07-01 08:43:56</t>
         </is>
       </c>
     </row>
@@ -679,28 +679,28 @@
         <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="I3" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="J3" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="K3" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="L3" t="n">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="M3" t="n">
         <v>49</v>
       </c>
       <c r="N3" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="O3" t="n">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="P3" t="n">
         <v>3</v>
@@ -709,7 +709,7 @@
         <v>3</v>
       </c>
       <c r="R3" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -733,16 +733,16 @@
         <v>5</v>
       </c>
       <c r="Z3" t="n">
-        <v>47.85</v>
+        <v>47.81</v>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>11|12|22|32|37|49|21</t>
+          <t>5|8|15|40|44|49|28</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-06-30 08:14:15</t>
+          <t>2026-07-01 08:43:56</t>
         </is>
       </c>
     </row>
@@ -776,25 +776,25 @@
         <v>7</v>
       </c>
       <c r="I4" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J4" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="K4" t="n">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="L4" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="M4" t="n">
         <v>48</v>
       </c>
       <c r="N4" t="n">
-        <v>42</v>
+        <v>17</v>
       </c>
       <c r="O4" t="n">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="P4" t="n">
         <v>3</v>
@@ -827,16 +827,16 @@
         <v>5</v>
       </c>
       <c r="Z4" t="n">
-        <v>42.85</v>
+        <v>42.81</v>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>7|12|23|33|40|48|42</t>
+          <t>7|11|16|39|44|48|17</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-06-30 08:14:15</t>
+          <t>2026-07-01 08:43:56</t>
         </is>
       </c>
     </row>
@@ -867,28 +867,28 @@
         <v>3</v>
       </c>
       <c r="H5" t="n">
+        <v>7</v>
+      </c>
+      <c r="I5" t="n">
         <v>8</v>
       </c>
-      <c r="I5" t="n">
-        <v>13</v>
-      </c>
       <c r="J5" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K5" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="L5" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="M5" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="N5" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="O5" t="n">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="P5" t="n">
         <v>3</v>
@@ -897,7 +897,7 @@
         <v>3</v>
       </c>
       <c r="R5" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -921,16 +921,16 @@
         <v>5</v>
       </c>
       <c r="Z5" t="n">
-        <v>40.35</v>
+        <v>40.31</v>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>8|13|18|32|39|47|16</t>
+          <t>7|8|17|38|42|49|9</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-06-30 08:14:15</t>
+          <t>2026-07-01 08:43:56</t>
         </is>
       </c>
     </row>
@@ -961,37 +961,37 @@
         <v>4</v>
       </c>
       <c r="H6" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I6" t="n">
         <v>8</v>
       </c>
       <c r="J6" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="K6" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L6" t="n">
+        <v>40</v>
+      </c>
+      <c r="M6" t="n">
+        <v>49</v>
+      </c>
+      <c r="N6" t="n">
+        <v>41</v>
+      </c>
+      <c r="O6" t="n">
+        <v>167</v>
+      </c>
+      <c r="P6" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>3</v>
+      </c>
+      <c r="R6" t="n">
         <v>43</v>
-      </c>
-      <c r="M6" t="n">
-        <v>47</v>
-      </c>
-      <c r="N6" t="n">
-        <v>16</v>
-      </c>
-      <c r="O6" t="n">
-        <v>161</v>
-      </c>
-      <c r="P6" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>3</v>
-      </c>
-      <c r="R6" t="n">
-        <v>45</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1015,16 +1015,16 @@
         <v>5</v>
       </c>
       <c r="Z6" t="n">
-        <v>38.85</v>
+        <v>38.81</v>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2|8|23|38|43|47|16</t>
+          <t>6|8|25|39|40|49|41</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-06-30 08:14:15</t>
+          <t>2026-07-01 08:43:56</t>
         </is>
       </c>
     </row>
@@ -1055,25 +1055,25 @@
         <v>5</v>
       </c>
       <c r="H7" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="I7" t="n">
         <v>11</v>
       </c>
       <c r="J7" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="K7" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="L7" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="M7" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="N7" t="n">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="O7" t="n">
         <v>169</v>
@@ -1085,7 +1085,7 @@
         <v>3</v>
       </c>
       <c r="R7" t="n">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1109,16 +1109,16 @@
         <v>5</v>
       </c>
       <c r="Z7" t="n">
-        <v>37.85</v>
+        <v>37.81</v>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>7|11|20|40|44|47|27</t>
+          <t>2|11|27|38|42|49|41</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-06-30 08:14:15</t>
+          <t>2026-07-01 08:43:56</t>
         </is>
       </c>
     </row>
@@ -1152,25 +1152,25 @@
         <v>1</v>
       </c>
       <c r="I8" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="J8" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="K8" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="L8" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="M8" t="n">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="N8" t="n">
-        <v>9</v>
+        <v>42</v>
       </c>
       <c r="O8" t="n">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="P8" t="n">
         <v>3</v>
@@ -1179,7 +1179,7 @@
         <v>3</v>
       </c>
       <c r="R8" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1203,16 +1203,16 @@
         <v>5</v>
       </c>
       <c r="Z8" t="n">
-        <v>37.13571428571429</v>
+        <v>37.09571428571429</v>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>1|12|15|36|40|49|9</t>
+          <t>1|7|20|32|39|46|42</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-06-30 08:14:15</t>
+          <t>2026-07-01 08:43:56</t>
         </is>
       </c>
     </row>
@@ -1243,10 +1243,10 @@
         <v>7</v>
       </c>
       <c r="H9" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="I9" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="J9" t="n">
         <v>27</v>
@@ -1255,16 +1255,16 @@
         <v>32</v>
       </c>
       <c r="L9" t="n">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="M9" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="N9" t="n">
-        <v>43</v>
+        <v>25</v>
       </c>
       <c r="O9" t="n">
-        <v>159</v>
+        <v>171</v>
       </c>
       <c r="P9" t="n">
         <v>3</v>
@@ -1297,16 +1297,16 @@
         <v>5</v>
       </c>
       <c r="Z9" t="n">
-        <v>36.6</v>
+        <v>36.56</v>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>5|8|27|32|41|46|43</t>
+          <t>8|18|27|32|37|49|25</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-06-30 08:14:15</t>
+          <t>2026-07-01 08:43:56</t>
         </is>
       </c>
     </row>
@@ -1340,25 +1340,25 @@
         <v>8</v>
       </c>
       <c r="I10" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J10" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="K10" t="n">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="L10" t="n">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="M10" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="N10" t="n">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="O10" t="n">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="P10" t="n">
         <v>3</v>
@@ -1367,7 +1367,7 @@
         <v>3</v>
       </c>
       <c r="R10" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1391,16 +1391,16 @@
         <v>5</v>
       </c>
       <c r="Z10" t="n">
-        <v>36.18333333333334</v>
+        <v>36.14333333333333</v>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>8|11|15|36|42|49|28</t>
+          <t>8|12|19|33|37|48|18</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-06-30 08:14:15</t>
+          <t>2026-07-01 08:43:56</t>
         </is>
       </c>
     </row>
@@ -1431,37 +1431,37 @@
         <v>9</v>
       </c>
       <c r="H11" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="I11" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J11" t="n">
         <v>27</v>
       </c>
       <c r="K11" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="L11" t="n">
+        <v>43</v>
+      </c>
+      <c r="M11" t="n">
+        <v>48</v>
+      </c>
+      <c r="N11" t="n">
+        <v>2</v>
+      </c>
+      <c r="O11" t="n">
+        <v>175</v>
+      </c>
+      <c r="P11" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>3</v>
+      </c>
+      <c r="R11" t="n">
         <v>36</v>
-      </c>
-      <c r="M11" t="n">
-        <v>49</v>
-      </c>
-      <c r="N11" t="n">
-        <v>12</v>
-      </c>
-      <c r="O11" t="n">
-        <v>167</v>
-      </c>
-      <c r="P11" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>3</v>
-      </c>
-      <c r="R11" t="n">
-        <v>41</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1485,16 +1485,16 @@
         <v>5</v>
       </c>
       <c r="Z11" t="n">
-        <v>35.85</v>
+        <v>35.81</v>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>8|15|27|32|36|49|12</t>
+          <t>12|14|27|31|43|48|2</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-06-30 08:14:15</t>
+          <t>2026-07-01 08:43:56</t>
         </is>
       </c>
     </row>
@@ -1525,28 +1525,28 @@
         <v>10</v>
       </c>
       <c r="H12" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I12" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="J12" t="n">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="K12" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="L12" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="M12" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="N12" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="O12" t="n">
-        <v>151</v>
+        <v>171</v>
       </c>
       <c r="P12" t="n">
         <v>3</v>
@@ -1555,7 +1555,7 @@
         <v>3</v>
       </c>
       <c r="R12" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1579,16 +1579,16 @@
         <v>5</v>
       </c>
       <c r="Z12" t="n">
-        <v>35.57727272727273</v>
+        <v>35.53727272727272</v>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>3|7|21|32|40|48|15</t>
+          <t>6|12|29|36|39|49|13</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-06-30 08:14:15</t>
+          <t>2026-07-01 08:43:56</t>
         </is>
       </c>
     </row>

--- a/data/exports/final_predictions/lotto_ensemble_predictions.xlsx
+++ b/data/exports/final_predictions/lotto_ensemble_predictions.xlsx
@@ -603,7 +603,7 @@
         <v>56</v>
       </c>
       <c r="N2" t="n">
-        <v>10</v>
+        <v>54</v>
       </c>
       <c r="O2" t="n">
         <v>206</v>
@@ -639,16 +639,16 @@
         <v>8</v>
       </c>
       <c r="Z2" t="n">
-        <v>73.81</v>
+        <v>73.84</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2|4|44|49|51|56|10</t>
+          <t>2|4|44|49|51|56|54</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-07-01 08:43:56</t>
+          <t>2026-07-02 07:59:38</t>
         </is>
       </c>
     </row>
@@ -679,28 +679,28 @@
         <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I3" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="J3" t="n">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="K3" t="n">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="L3" t="n">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="M3" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="N3" t="n">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="O3" t="n">
-        <v>161</v>
+        <v>169</v>
       </c>
       <c r="P3" t="n">
         <v>3</v>
@@ -709,7 +709,7 @@
         <v>3</v>
       </c>
       <c r="R3" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -733,16 +733,16 @@
         <v>5</v>
       </c>
       <c r="Z3" t="n">
-        <v>47.81</v>
+        <v>47.84</v>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>5|8|15|40|44|49|28</t>
+          <t>6|12|29|35|39|48|13</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-07-01 08:43:56</t>
+          <t>2026-07-02 07:59:38</t>
         </is>
       </c>
     </row>
@@ -773,28 +773,28 @@
         <v>2</v>
       </c>
       <c r="H4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I4" t="n">
         <v>11</v>
       </c>
       <c r="J4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K4" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="L4" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="M4" t="n">
         <v>48</v>
       </c>
       <c r="N4" t="n">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="O4" t="n">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="P4" t="n">
         <v>3</v>
@@ -803,7 +803,7 @@
         <v>3</v>
       </c>
       <c r="R4" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -827,16 +827,16 @@
         <v>5</v>
       </c>
       <c r="Z4" t="n">
-        <v>42.81</v>
+        <v>42.84</v>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>7|11|16|39|44|48|17</t>
+          <t>8|11|17|36|43|48|39</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-07-01 08:43:56</t>
+          <t>2026-07-02 07:59:38</t>
         </is>
       </c>
     </row>
@@ -867,28 +867,28 @@
         <v>3</v>
       </c>
       <c r="H5" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I5" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="J5" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="K5" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="L5" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="M5" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="N5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O5" t="n">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="P5" t="n">
         <v>3</v>
@@ -897,7 +897,7 @@
         <v>3</v>
       </c>
       <c r="R5" t="n">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -921,16 +921,16 @@
         <v>5</v>
       </c>
       <c r="Z5" t="n">
-        <v>40.31</v>
+        <v>40.34</v>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>7|8|17|38|42|49|9</t>
+          <t>9|13|15|32|40|48|10</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-07-01 08:43:56</t>
+          <t>2026-07-02 07:59:38</t>
         </is>
       </c>
     </row>
@@ -961,28 +961,28 @@
         <v>4</v>
       </c>
       <c r="H6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I6" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="J6" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="K6" t="n">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="L6" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="M6" t="n">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="N6" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="O6" t="n">
-        <v>167</v>
+        <v>157</v>
       </c>
       <c r="P6" t="n">
         <v>3</v>
@@ -991,7 +991,7 @@
         <v>3</v>
       </c>
       <c r="R6" t="n">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1015,16 +1015,16 @@
         <v>5</v>
       </c>
       <c r="Z6" t="n">
-        <v>38.81</v>
+        <v>38.84</v>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>6|8|25|39|40|49|41</t>
+          <t>7|11|20|30|44|45|38</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-07-01 08:43:56</t>
+          <t>2026-07-02 07:59:38</t>
         </is>
       </c>
     </row>
@@ -1055,28 +1055,28 @@
         <v>5</v>
       </c>
       <c r="H7" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="I7" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J7" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K7" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L7" t="n">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="M7" t="n">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="N7" t="n">
-        <v>41</v>
+        <v>18</v>
       </c>
       <c r="O7" t="n">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="P7" t="n">
         <v>3</v>
@@ -1085,7 +1085,7 @@
         <v>3</v>
       </c>
       <c r="R7" t="n">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1109,16 +1109,16 @@
         <v>5</v>
       </c>
       <c r="Z7" t="n">
-        <v>37.81</v>
+        <v>37.84</v>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2|11|27|38|42|49|41</t>
+          <t>11|12|28|37|39|46|18</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-07-01 08:43:56</t>
+          <t>2026-07-02 07:59:38</t>
         </is>
       </c>
     </row>
@@ -1149,28 +1149,28 @@
         <v>6</v>
       </c>
       <c r="H8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I8" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="J8" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="K8" t="n">
         <v>32</v>
       </c>
       <c r="L8" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="M8" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="N8" t="n">
-        <v>42</v>
+        <v>2</v>
       </c>
       <c r="O8" t="n">
-        <v>145</v>
+        <v>153</v>
       </c>
       <c r="P8" t="n">
         <v>3</v>
@@ -1179,7 +1179,7 @@
         <v>3</v>
       </c>
       <c r="R8" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1203,16 +1203,16 @@
         <v>5</v>
       </c>
       <c r="Z8" t="n">
-        <v>37.09571428571429</v>
+        <v>37.12571428571429</v>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>1|7|20|32|39|46|42</t>
+          <t>5|14|17|32|36|49|2</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-07-01 08:43:56</t>
+          <t>2026-07-02 07:59:38</t>
         </is>
       </c>
     </row>
@@ -1243,28 +1243,28 @@
         <v>7</v>
       </c>
       <c r="H9" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="I9" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="J9" t="n">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="K9" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="L9" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="M9" t="n">
         <v>49</v>
       </c>
       <c r="N9" t="n">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="O9" t="n">
-        <v>171</v>
+        <v>141</v>
       </c>
       <c r="P9" t="n">
         <v>3</v>
@@ -1273,7 +1273,7 @@
         <v>3</v>
       </c>
       <c r="R9" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1297,16 +1297,16 @@
         <v>5</v>
       </c>
       <c r="Z9" t="n">
-        <v>36.56</v>
+        <v>36.59</v>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>8|18|27|32|37|49|25</t>
+          <t>4|5|16|31|36|49|38</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-07-01 08:43:56</t>
+          <t>2026-07-02 07:59:38</t>
         </is>
       </c>
     </row>
@@ -1340,25 +1340,25 @@
         <v>8</v>
       </c>
       <c r="I10" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="J10" t="n">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="K10" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="L10" t="n">
         <v>37</v>
       </c>
       <c r="M10" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="N10" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="O10" t="n">
-        <v>157</v>
+        <v>171</v>
       </c>
       <c r="P10" t="n">
         <v>3</v>
@@ -1367,7 +1367,7 @@
         <v>3</v>
       </c>
       <c r="R10" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1391,16 +1391,16 @@
         <v>5</v>
       </c>
       <c r="Z10" t="n">
-        <v>36.14333333333333</v>
+        <v>36.17333333333333</v>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>8|12|19|33|37|48|18</t>
+          <t>8|18|27|32|37|49|25</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-07-01 08:43:56</t>
+          <t>2026-07-02 07:59:38</t>
         </is>
       </c>
     </row>
@@ -1431,28 +1431,28 @@
         <v>9</v>
       </c>
       <c r="H11" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="I11" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="J11" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="K11" t="n">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="L11" t="n">
         <v>43</v>
       </c>
       <c r="M11" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="N11" t="n">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="O11" t="n">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="P11" t="n">
         <v>3</v>
@@ -1461,7 +1461,7 @@
         <v>3</v>
       </c>
       <c r="R11" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1485,16 +1485,16 @@
         <v>5</v>
       </c>
       <c r="Z11" t="n">
-        <v>35.81</v>
+        <v>35.84</v>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>12|14|27|31|43|48|2</t>
+          <t>8|13|22|39|43|46|29</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-07-01 08:43:56</t>
+          <t>2026-07-02 07:59:38</t>
         </is>
       </c>
     </row>
@@ -1525,28 +1525,28 @@
         <v>10</v>
       </c>
       <c r="H12" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I12" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="J12" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="K12" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="L12" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="M12" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="N12" t="n">
-        <v>13</v>
+        <v>51</v>
       </c>
       <c r="O12" t="n">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="P12" t="n">
         <v>3</v>
@@ -1555,7 +1555,7 @@
         <v>3</v>
       </c>
       <c r="R12" t="n">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1579,16 +1579,16 @@
         <v>5</v>
       </c>
       <c r="Z12" t="n">
-        <v>35.53727272727272</v>
+        <v>35.56727272727272</v>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>6|12|29|36|39|49|13</t>
+          <t>8|25|27|32|37|48|51</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-07-01 08:43:56</t>
+          <t>2026-07-02 07:59:38</t>
         </is>
       </c>
     </row>

--- a/data/exports/final_predictions/lotto_ensemble_predictions.xlsx
+++ b/data/exports/final_predictions/lotto_ensemble_predictions.xlsx
@@ -648,7 +648,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-07-02 07:59:38</t>
+          <t>2026-07-03 07:55:32</t>
         </is>
       </c>
     </row>
@@ -742,7 +742,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-07-02 07:59:38</t>
+          <t>2026-07-03 07:55:32</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-07-02 07:59:38</t>
+          <t>2026-07-03 07:55:32</t>
         </is>
       </c>
     </row>
@@ -930,7 +930,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-07-02 07:59:38</t>
+          <t>2026-07-03 07:55:32</t>
         </is>
       </c>
     </row>
@@ -1024,7 +1024,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-07-02 07:59:38</t>
+          <t>2026-07-03 07:55:32</t>
         </is>
       </c>
     </row>
@@ -1118,7 +1118,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-07-02 07:59:38</t>
+          <t>2026-07-03 07:55:32</t>
         </is>
       </c>
     </row>
@@ -1212,7 +1212,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-07-02 07:59:38</t>
+          <t>2026-07-03 07:55:32</t>
         </is>
       </c>
     </row>
@@ -1306,7 +1306,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-07-02 07:59:38</t>
+          <t>2026-07-03 07:55:32</t>
         </is>
       </c>
     </row>
@@ -1400,7 +1400,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-07-02 07:59:38</t>
+          <t>2026-07-03 07:55:32</t>
         </is>
       </c>
     </row>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-07-02 07:59:38</t>
+          <t>2026-07-03 07:55:32</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-07-02 07:59:38</t>
+          <t>2026-07-03 07:55:32</t>
         </is>
       </c>
     </row>
